--- a/resources/乔剪国战表格.xlsx
+++ b/resources/乔剪国战表格.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zwieb\Documents\GitHub\qiao-s-hanjin-cut\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4722693E-FA5B-477C-A385-33AA8CA66F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3AE0489-7CE9-4F94-9FA2-7AD2DFA8E7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31920" yWindow="1560" windowWidth="23550" windowHeight="14610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31920" yWindow="1560" windowWidth="23550" windowHeight="14610" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7878" uniqueCount="5938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7879" uniqueCount="5939">
   <si>
     <t>标准版</t>
   </si>
@@ -18125,12 +18125,16 @@
       <t>HAN119</t>
     </r>
   </si>
+  <si>
+    <t>太史慈</t>
+    <phoneticPr fontId="73" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="74">
+  <fonts count="75">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -18595,6 +18599,12 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="71">
@@ -19615,7 +19625,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="590">
+  <cellXfs count="591">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -21094,7 +21104,55 @@
     <xf numFmtId="0" fontId="44" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21102,6 +21160,22 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="14" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -21124,70 +21198,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="53" fillId="34" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="53" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="14" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -21197,7 +21232,13 @@
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -21206,50 +21247,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="53" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="34" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="49" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -21258,7 +21265,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="49" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="32" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="32" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -21268,7 +21281,7 @@
     <xf numFmtId="0" fontId="23" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="32" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -21279,9 +21292,6 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
@@ -21313,15 +21323,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="74" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -21642,7 +21655,7 @@
     <tabColor rgb="FFFFFFFF"/>
   </sheetPr>
   <dimension ref="A1:AM201"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
     <col min="2" max="24" width="13.140625" customWidth="1"/>
@@ -21687,14 +21700,14 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="1"/>
-      <c r="B2" s="510" t="s">
+      <c r="B2" s="516" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="511"/>
-      <c r="D2" s="511"/>
-      <c r="E2" s="511"/>
-      <c r="F2" s="511"/>
-      <c r="G2" s="512"/>
+      <c r="C2" s="527"/>
+      <c r="D2" s="527"/>
+      <c r="E2" s="527"/>
+      <c r="F2" s="527"/>
+      <c r="G2" s="528"/>
       <c r="H2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
@@ -21726,46 +21739,46 @@
       <c r="I3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="515" t="s">
+      <c r="J3" s="537" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="516"/>
-      <c r="L3" s="516"/>
+      <c r="K3" s="538"/>
+      <c r="L3" s="538"/>
       <c r="M3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="517" t="s">
+      <c r="N3" s="539" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="518"/>
-      <c r="P3" s="519"/>
+      <c r="O3" s="540"/>
+      <c r="P3" s="541"/>
       <c r="Q3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="S3" s="510" t="s">
+      <c r="S3" s="516" t="s">
         <v>12</v>
       </c>
-      <c r="T3" s="511"/>
-      <c r="U3" s="511"/>
-      <c r="V3" s="511"/>
-      <c r="W3" s="511"/>
-      <c r="X3" s="512"/>
-      <c r="Z3" s="510" t="s">
+      <c r="T3" s="527"/>
+      <c r="U3" s="527"/>
+      <c r="V3" s="527"/>
+      <c r="W3" s="527"/>
+      <c r="X3" s="528"/>
+      <c r="Z3" s="516" t="s">
         <v>13</v>
       </c>
-      <c r="AA3" s="511"/>
-      <c r="AB3" s="511"/>
-      <c r="AC3" s="511"/>
-      <c r="AD3" s="511"/>
-      <c r="AE3" s="512"/>
-      <c r="AG3" s="510" t="s">
+      <c r="AA3" s="527"/>
+      <c r="AB3" s="527"/>
+      <c r="AC3" s="527"/>
+      <c r="AD3" s="527"/>
+      <c r="AE3" s="528"/>
+      <c r="AG3" s="516" t="s">
         <v>14</v>
       </c>
-      <c r="AH3" s="533"/>
-      <c r="AI3" s="533"/>
-      <c r="AJ3" s="534"/>
-      <c r="AK3" s="534"/>
-      <c r="AL3" s="535"/>
+      <c r="AH3" s="517"/>
+      <c r="AI3" s="517"/>
+      <c r="AJ3" s="518"/>
+      <c r="AK3" s="518"/>
+      <c r="AL3" s="519"/>
     </row>
     <row r="4" spans="1:39" ht="18">
       <c r="A4" s="1"/>
@@ -22191,14 +22204,14 @@
       <c r="Q8" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="S8" s="510" t="s">
+      <c r="S8" s="516" t="s">
         <v>126</v>
       </c>
-      <c r="T8" s="511"/>
-      <c r="U8" s="511"/>
-      <c r="V8" s="511"/>
-      <c r="W8" s="511"/>
-      <c r="X8" s="512"/>
+      <c r="T8" s="527"/>
+      <c r="U8" s="527"/>
+      <c r="V8" s="527"/>
+      <c r="W8" s="527"/>
+      <c r="X8" s="528"/>
       <c r="Z8" s="37" t="s">
         <v>127</v>
       </c>
@@ -22217,14 +22230,14 @@
       <c r="AE8" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="AG8" s="530" t="s">
+      <c r="AG8" s="520" t="s">
         <v>131</v>
       </c>
-      <c r="AH8" s="536"/>
-      <c r="AI8" s="536"/>
-      <c r="AJ8" s="536"/>
-      <c r="AK8" s="536"/>
-      <c r="AL8" s="537"/>
+      <c r="AH8" s="521"/>
+      <c r="AI8" s="521"/>
+      <c r="AJ8" s="521"/>
+      <c r="AK8" s="521"/>
+      <c r="AL8" s="522"/>
     </row>
     <row r="9" spans="1:39" ht="17.25">
       <c r="A9" s="1"/>
@@ -22352,14 +22365,14 @@
         <v>25</v>
       </c>
       <c r="S10" s="63"/>
-      <c r="Z10" s="510" t="s">
+      <c r="Z10" s="516" t="s">
         <v>163</v>
       </c>
-      <c r="AA10" s="511"/>
-      <c r="AB10" s="511"/>
-      <c r="AC10" s="511"/>
-      <c r="AD10" s="511"/>
-      <c r="AE10" s="512"/>
+      <c r="AA10" s="527"/>
+      <c r="AB10" s="527"/>
+      <c r="AC10" s="527"/>
+      <c r="AD10" s="527"/>
+      <c r="AE10" s="528"/>
       <c r="AG10" s="30" t="s">
         <v>164</v>
       </c>
@@ -22416,14 +22429,14 @@
       <c r="O11" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="S11" s="510" t="s">
+      <c r="S11" s="516" t="s">
         <v>180</v>
       </c>
-      <c r="T11" s="511"/>
-      <c r="U11" s="511"/>
-      <c r="V11" s="511"/>
-      <c r="W11" s="511"/>
-      <c r="X11" s="512"/>
+      <c r="T11" s="527"/>
+      <c r="U11" s="527"/>
+      <c r="V11" s="527"/>
+      <c r="W11" s="527"/>
+      <c r="X11" s="528"/>
       <c r="Z11" s="3" t="s">
         <v>1</v>
       </c>
@@ -22608,14 +22621,14 @@
         <v>224</v>
       </c>
       <c r="AF13" s="71"/>
-      <c r="AG13" s="530" t="s">
+      <c r="AG13" s="520" t="s">
         <v>225</v>
       </c>
-      <c r="AH13" s="534"/>
-      <c r="AI13" s="534"/>
-      <c r="AJ13" s="534"/>
-      <c r="AK13" s="534"/>
-      <c r="AL13" s="535"/>
+      <c r="AH13" s="518"/>
+      <c r="AI13" s="518"/>
+      <c r="AJ13" s="518"/>
+      <c r="AK13" s="518"/>
+      <c r="AL13" s="519"/>
     </row>
     <row r="14" spans="1:39" ht="17.25">
       <c r="A14" s="1"/>
@@ -22721,14 +22734,14 @@
       <c r="O15" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="Z15" s="530" t="s">
+      <c r="Z15" s="520" t="s">
         <v>250</v>
       </c>
-      <c r="AA15" s="531"/>
-      <c r="AB15" s="531"/>
-      <c r="AC15" s="531"/>
-      <c r="AD15" s="531"/>
-      <c r="AE15" s="532"/>
+      <c r="AA15" s="523"/>
+      <c r="AB15" s="523"/>
+      <c r="AC15" s="523"/>
+      <c r="AD15" s="523"/>
+      <c r="AE15" s="524"/>
       <c r="AF15" s="78"/>
       <c r="AG15" s="30" t="s">
         <v>251</v>
@@ -22778,14 +22791,14 @@
       <c r="O16" s="66" t="s">
         <v>263</v>
       </c>
-      <c r="S16" s="510" t="s">
+      <c r="S16" s="516" t="s">
         <v>264</v>
       </c>
-      <c r="T16" s="511"/>
-      <c r="U16" s="511"/>
-      <c r="V16" s="511"/>
-      <c r="W16" s="511"/>
-      <c r="X16" s="512"/>
+      <c r="T16" s="527"/>
+      <c r="U16" s="527"/>
+      <c r="V16" s="527"/>
+      <c r="W16" s="527"/>
+      <c r="X16" s="528"/>
       <c r="Z16" s="81" t="s">
         <v>1</v>
       </c>
@@ -22880,14 +22893,14 @@
         <v>174</v>
       </c>
       <c r="AF17" s="69"/>
-      <c r="AG17" s="530" t="s">
+      <c r="AG17" s="520" t="s">
         <v>273</v>
       </c>
-      <c r="AH17" s="531"/>
-      <c r="AI17" s="531"/>
-      <c r="AJ17" s="531"/>
-      <c r="AK17" s="531"/>
-      <c r="AL17" s="532"/>
+      <c r="AH17" s="523"/>
+      <c r="AI17" s="523"/>
+      <c r="AJ17" s="523"/>
+      <c r="AK17" s="523"/>
+      <c r="AL17" s="524"/>
       <c r="AM17" s="79"/>
     </row>
     <row r="18" spans="1:39" ht="17.25">
@@ -23022,13 +23035,13 @@
     </row>
     <row r="20" spans="1:39" ht="18">
       <c r="A20" s="1"/>
-      <c r="B20" s="513"/>
-      <c r="C20" s="514"/>
-      <c r="D20" s="514"/>
-      <c r="E20" s="514"/>
-      <c r="F20" s="514"/>
-      <c r="G20" s="514"/>
-      <c r="H20" s="514"/>
+      <c r="B20" s="535"/>
+      <c r="C20" s="536"/>
+      <c r="D20" s="536"/>
+      <c r="E20" s="536"/>
+      <c r="F20" s="536"/>
+      <c r="G20" s="536"/>
+      <c r="H20" s="536"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -23038,14 +23051,14 @@
       <c r="O20" s="88"/>
       <c r="P20" s="91"/>
       <c r="Q20" s="92"/>
-      <c r="Z20" s="510" t="s">
+      <c r="Z20" s="516" t="s">
         <v>300</v>
       </c>
-      <c r="AA20" s="511"/>
-      <c r="AB20" s="511"/>
-      <c r="AC20" s="511"/>
-      <c r="AD20" s="511"/>
-      <c r="AE20" s="512"/>
+      <c r="AA20" s="527"/>
+      <c r="AB20" s="527"/>
+      <c r="AC20" s="527"/>
+      <c r="AD20" s="527"/>
+      <c r="AE20" s="528"/>
       <c r="AF20" s="78"/>
       <c r="AG20" s="30" t="s">
         <v>301</v>
@@ -23104,14 +23117,14 @@
       <c r="N21" s="93" t="s">
         <v>318</v>
       </c>
-      <c r="P21" s="510" t="s">
+      <c r="P21" s="516" t="s">
         <v>319</v>
       </c>
-      <c r="Q21" s="511"/>
-      <c r="R21" s="511"/>
-      <c r="S21" s="511"/>
-      <c r="T21" s="511"/>
-      <c r="U21" s="512"/>
+      <c r="Q21" s="527"/>
+      <c r="R21" s="527"/>
+      <c r="S21" s="527"/>
+      <c r="T21" s="527"/>
+      <c r="U21" s="528"/>
       <c r="V21" s="63"/>
       <c r="Z21" s="81" t="s">
         <v>1</v>
@@ -23294,14 +23307,14 @@
       <c r="W23" s="95" t="s">
         <v>357</v>
       </c>
-      <c r="AG23" s="530" t="s">
+      <c r="AG23" s="520" t="s">
         <v>358</v>
       </c>
-      <c r="AH23" s="531"/>
-      <c r="AI23" s="531"/>
-      <c r="AJ23" s="531"/>
-      <c r="AK23" s="531"/>
-      <c r="AL23" s="532"/>
+      <c r="AH23" s="523"/>
+      <c r="AI23" s="523"/>
+      <c r="AJ23" s="523"/>
+      <c r="AK23" s="523"/>
+      <c r="AL23" s="524"/>
     </row>
     <row r="24" spans="1:39" ht="18">
       <c r="A24" s="1"/>
@@ -23365,14 +23378,14 @@
       <c r="W24" s="110" t="s">
         <v>376</v>
       </c>
-      <c r="Z24" s="510" t="s">
+      <c r="Z24" s="516" t="s">
         <v>377</v>
       </c>
-      <c r="AA24" s="533"/>
-      <c r="AB24" s="533"/>
-      <c r="AC24" s="533"/>
-      <c r="AD24" s="533"/>
-      <c r="AE24" s="539"/>
+      <c r="AA24" s="517"/>
+      <c r="AB24" s="517"/>
+      <c r="AC24" s="517"/>
+      <c r="AD24" s="517"/>
+      <c r="AE24" s="526"/>
       <c r="AG24" s="81" t="s">
         <v>1</v>
       </c>
@@ -23723,14 +23736,14 @@
       <c r="W28" s="125" t="s">
         <v>468</v>
       </c>
-      <c r="Z28" s="510" t="s">
+      <c r="Z28" s="516" t="s">
         <v>469</v>
       </c>
-      <c r="AA28" s="533"/>
-      <c r="AB28" s="533"/>
-      <c r="AC28" s="533"/>
-      <c r="AD28" s="533"/>
-      <c r="AE28" s="539"/>
+      <c r="AA28" s="517"/>
+      <c r="AB28" s="517"/>
+      <c r="AC28" s="517"/>
+      <c r="AD28" s="517"/>
+      <c r="AE28" s="526"/>
       <c r="AG28" s="103"/>
       <c r="AH28" s="103"/>
       <c r="AI28" s="103"/>
@@ -24052,14 +24065,14 @@
       <c r="V32" s="46" t="s">
         <v>554</v>
       </c>
-      <c r="Z32" s="510" t="s">
+      <c r="Z32" s="516" t="s">
         <v>555</v>
       </c>
-      <c r="AA32" s="533"/>
-      <c r="AB32" s="533"/>
-      <c r="AC32" s="533"/>
-      <c r="AD32" s="533"/>
-      <c r="AE32" s="539"/>
+      <c r="AA32" s="517"/>
+      <c r="AB32" s="517"/>
+      <c r="AC32" s="517"/>
+      <c r="AD32" s="517"/>
+      <c r="AE32" s="526"/>
       <c r="AG32" s="36" t="s">
         <v>556</v>
       </c>
@@ -24528,14 +24541,14 @@
       <c r="U40" s="109" t="s">
         <v>677</v>
       </c>
-      <c r="Z40" s="510" t="s">
+      <c r="Z40" s="516" t="s">
         <v>678</v>
       </c>
-      <c r="AA40" s="533"/>
-      <c r="AB40" s="533"/>
-      <c r="AC40" s="534"/>
-      <c r="AD40" s="534"/>
-      <c r="AE40" s="535"/>
+      <c r="AA40" s="517"/>
+      <c r="AB40" s="517"/>
+      <c r="AC40" s="518"/>
+      <c r="AD40" s="518"/>
+      <c r="AE40" s="519"/>
       <c r="AG40" s="138" t="s">
         <v>679</v>
       </c>
@@ -24707,20 +24720,20 @@
     </row>
     <row r="45" spans="1:38" ht="17.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="524" t="s">
+      <c r="B45" s="510" t="s">
         <v>725</v>
       </c>
-      <c r="C45" s="525"/>
-      <c r="D45" s="525"/>
-      <c r="E45" s="525"/>
-      <c r="F45" s="526"/>
-      <c r="H45" s="524" t="s">
+      <c r="C45" s="511"/>
+      <c r="D45" s="511"/>
+      <c r="E45" s="511"/>
+      <c r="F45" s="512"/>
+      <c r="H45" s="510" t="s">
         <v>726</v>
       </c>
-      <c r="I45" s="525"/>
-      <c r="J45" s="525"/>
-      <c r="K45" s="525"/>
-      <c r="L45" s="526"/>
+      <c r="I45" s="511"/>
+      <c r="J45" s="511"/>
+      <c r="K45" s="511"/>
+      <c r="L45" s="512"/>
       <c r="P45" s="29" t="s">
         <v>727</v>
       </c>
@@ -24760,16 +24773,16 @@
     </row>
     <row r="46" spans="1:38" ht="18">
       <c r="A46" s="1"/>
-      <c r="B46" s="527"/>
-      <c r="C46" s="528"/>
-      <c r="D46" s="528"/>
-      <c r="E46" s="528"/>
-      <c r="F46" s="529"/>
-      <c r="H46" s="527"/>
-      <c r="I46" s="528"/>
-      <c r="J46" s="528"/>
-      <c r="K46" s="528"/>
-      <c r="L46" s="529"/>
+      <c r="B46" s="513"/>
+      <c r="C46" s="514"/>
+      <c r="D46" s="514"/>
+      <c r="E46" s="514"/>
+      <c r="F46" s="515"/>
+      <c r="H46" s="513"/>
+      <c r="I46" s="514"/>
+      <c r="J46" s="514"/>
+      <c r="K46" s="514"/>
+      <c r="L46" s="515"/>
       <c r="P46" s="29" t="s">
         <v>739</v>
       </c>
@@ -24806,14 +24819,14 @@
       <c r="AE46" s="100" t="s">
         <v>750</v>
       </c>
-      <c r="AG46" s="510" t="s">
+      <c r="AG46" s="516" t="s">
         <v>751</v>
       </c>
-      <c r="AH46" s="511"/>
-      <c r="AI46" s="511"/>
-      <c r="AJ46" s="511"/>
-      <c r="AK46" s="511"/>
-      <c r="AL46" s="512"/>
+      <c r="AH46" s="527"/>
+      <c r="AI46" s="527"/>
+      <c r="AJ46" s="527"/>
+      <c r="AK46" s="527"/>
+      <c r="AL46" s="528"/>
     </row>
     <row r="47" spans="1:38" ht="17.25">
       <c r="A47" s="1"/>
@@ -24856,20 +24869,20 @@
     </row>
     <row r="48" spans="1:38" ht="18">
       <c r="A48" s="1"/>
-      <c r="B48" s="520" t="s">
+      <c r="B48" s="533" t="s">
         <v>758</v>
       </c>
-      <c r="C48" s="521"/>
-      <c r="D48" s="521"/>
-      <c r="E48" s="521"/>
-      <c r="F48" s="521"/>
-      <c r="H48" s="520" t="s">
+      <c r="C48" s="534"/>
+      <c r="D48" s="534"/>
+      <c r="E48" s="534"/>
+      <c r="F48" s="534"/>
+      <c r="H48" s="533" t="s">
         <v>758</v>
       </c>
-      <c r="I48" s="521"/>
-      <c r="J48" s="521"/>
-      <c r="K48" s="521"/>
-      <c r="L48" s="521"/>
+      <c r="I48" s="534"/>
+      <c r="J48" s="534"/>
+      <c r="K48" s="534"/>
+      <c r="L48" s="534"/>
       <c r="P48" s="29" t="s">
         <v>759</v>
       </c>
@@ -24888,14 +24901,14 @@
       <c r="U48" s="29" t="s">
         <v>764</v>
       </c>
-      <c r="Z48" s="510" t="s">
+      <c r="Z48" s="516" t="s">
         <v>765</v>
       </c>
-      <c r="AA48" s="538"/>
-      <c r="AB48" s="536"/>
-      <c r="AC48" s="533"/>
-      <c r="AD48" s="538"/>
-      <c r="AE48" s="537"/>
+      <c r="AA48" s="525"/>
+      <c r="AB48" s="521"/>
+      <c r="AC48" s="517"/>
+      <c r="AD48" s="525"/>
+      <c r="AE48" s="522"/>
       <c r="AG48" s="29" t="s">
         <v>766</v>
       </c>
@@ -25446,13 +25459,13 @@
       <c r="L57" s="194" t="s">
         <v>869</v>
       </c>
-      <c r="P57" s="540" t="s">
+      <c r="P57" s="529" t="s">
         <v>871</v>
       </c>
-      <c r="Q57" s="541"/>
-      <c r="R57" s="541"/>
-      <c r="S57" s="541"/>
-      <c r="T57" s="541"/>
+      <c r="Q57" s="530"/>
+      <c r="R57" s="530"/>
+      <c r="S57" s="530"/>
+      <c r="T57" s="530"/>
     </row>
     <row r="58" spans="1:35" ht="15.75">
       <c r="A58" s="1"/>
@@ -25752,21 +25765,21 @@
     </row>
     <row r="64" spans="1:35" ht="15.75">
       <c r="A64" s="1"/>
-      <c r="B64" s="522" t="s">
+      <c r="B64" s="531" t="s">
         <v>895</v>
       </c>
-      <c r="C64" s="523"/>
-      <c r="D64" s="523"/>
-      <c r="E64" s="523"/>
-      <c r="F64" s="523"/>
+      <c r="C64" s="532"/>
+      <c r="D64" s="532"/>
+      <c r="E64" s="532"/>
+      <c r="F64" s="532"/>
       <c r="G64" s="1"/>
-      <c r="H64" s="522" t="s">
+      <c r="H64" s="531" t="s">
         <v>895</v>
       </c>
-      <c r="I64" s="523"/>
-      <c r="J64" s="523"/>
-      <c r="K64" s="523"/>
-      <c r="L64" s="523"/>
+      <c r="I64" s="532"/>
+      <c r="J64" s="532"/>
+      <c r="K64" s="532"/>
+      <c r="L64" s="532"/>
       <c r="M64" s="1"/>
       <c r="P64" s="214">
         <v>6</v>
@@ -26231,13 +26244,13 @@
         <v>869</v>
       </c>
       <c r="M73" s="1"/>
-      <c r="P73" s="522" t="s">
+      <c r="P73" s="531" t="s">
         <v>923</v>
       </c>
-      <c r="Q73" s="523"/>
-      <c r="R73" s="523"/>
-      <c r="S73" s="523"/>
-      <c r="T73" s="523"/>
+      <c r="Q73" s="532"/>
+      <c r="R73" s="532"/>
+      <c r="S73" s="532"/>
+      <c r="T73" s="532"/>
       <c r="AC73" s="1"/>
       <c r="AD73" s="1"/>
       <c r="AE73" s="1"/>
@@ -26498,29 +26511,29 @@
     </row>
     <row r="80" spans="1:34" ht="15.75">
       <c r="A80" s="1"/>
-      <c r="B80" s="522" t="s">
+      <c r="B80" s="531" t="s">
         <v>934</v>
       </c>
-      <c r="C80" s="523"/>
-      <c r="D80" s="523"/>
-      <c r="E80" s="523"/>
-      <c r="F80" s="523"/>
+      <c r="C80" s="532"/>
+      <c r="D80" s="532"/>
+      <c r="E80" s="532"/>
+      <c r="F80" s="532"/>
       <c r="G80" s="1"/>
-      <c r="H80" s="522" t="s">
+      <c r="H80" s="531" t="s">
         <v>934</v>
       </c>
-      <c r="I80" s="523"/>
-      <c r="J80" s="523"/>
-      <c r="K80" s="523"/>
-      <c r="L80" s="523"/>
+      <c r="I80" s="532"/>
+      <c r="J80" s="532"/>
+      <c r="K80" s="532"/>
+      <c r="L80" s="532"/>
       <c r="M80" s="1"/>
-      <c r="N80" s="524" t="s">
+      <c r="N80" s="510" t="s">
         <v>935</v>
       </c>
-      <c r="O80" s="525"/>
-      <c r="P80" s="525"/>
-      <c r="Q80" s="525"/>
-      <c r="R80" s="526"/>
+      <c r="O80" s="511"/>
+      <c r="P80" s="511"/>
+      <c r="Q80" s="511"/>
+      <c r="R80" s="512"/>
       <c r="S80" s="1"/>
       <c r="T80" s="1"/>
       <c r="AB80" s="1"/>
@@ -26561,11 +26574,11 @@
         <v>775</v>
       </c>
       <c r="M81" s="1"/>
-      <c r="N81" s="527"/>
-      <c r="O81" s="528"/>
-      <c r="P81" s="528"/>
-      <c r="Q81" s="528"/>
-      <c r="R81" s="529"/>
+      <c r="N81" s="513"/>
+      <c r="O81" s="514"/>
+      <c r="P81" s="514"/>
+      <c r="Q81" s="514"/>
+      <c r="R81" s="515"/>
       <c r="S81" s="1"/>
       <c r="T81" s="1"/>
       <c r="AB81" s="1"/>
@@ -27276,21 +27289,21 @@
     </row>
     <row r="96" spans="1:34" ht="17.25">
       <c r="A96" s="1"/>
-      <c r="B96" s="522" t="s">
+      <c r="B96" s="531" t="s">
         <v>923</v>
       </c>
-      <c r="C96" s="523"/>
-      <c r="D96" s="523"/>
-      <c r="E96" s="523"/>
-      <c r="F96" s="523"/>
+      <c r="C96" s="532"/>
+      <c r="D96" s="532"/>
+      <c r="E96" s="532"/>
+      <c r="F96" s="532"/>
       <c r="G96" s="1"/>
-      <c r="H96" s="522" t="s">
+      <c r="H96" s="531" t="s">
         <v>923</v>
       </c>
-      <c r="I96" s="523"/>
-      <c r="J96" s="523"/>
-      <c r="K96" s="523"/>
-      <c r="L96" s="523"/>
+      <c r="I96" s="532"/>
+      <c r="J96" s="532"/>
+      <c r="K96" s="532"/>
+      <c r="L96" s="532"/>
       <c r="M96" s="1"/>
       <c r="O96" s="11" t="s">
         <v>105</v>
@@ -30669,6 +30682,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="P21:U21"/>
+    <mergeCell ref="S3:X3"/>
+    <mergeCell ref="S8:X8"/>
+    <mergeCell ref="B96:F96"/>
+    <mergeCell ref="B45:F46"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="H45:L46"/>
+    <mergeCell ref="H48:L48"/>
+    <mergeCell ref="H64:L64"/>
+    <mergeCell ref="H80:L80"/>
+    <mergeCell ref="H96:L96"/>
+    <mergeCell ref="Z10:AE10"/>
+    <mergeCell ref="S11:X11"/>
+    <mergeCell ref="Z15:AE15"/>
+    <mergeCell ref="Z20:AE20"/>
+    <mergeCell ref="B64:F64"/>
     <mergeCell ref="N80:R81"/>
     <mergeCell ref="AG3:AL3"/>
     <mergeCell ref="AG8:AL8"/>
@@ -30685,27 +30719,6 @@
     <mergeCell ref="P57:T57"/>
     <mergeCell ref="P73:T73"/>
     <mergeCell ref="Z3:AE3"/>
-    <mergeCell ref="Z10:AE10"/>
-    <mergeCell ref="S11:X11"/>
-    <mergeCell ref="Z15:AE15"/>
-    <mergeCell ref="Z20:AE20"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B96:F96"/>
-    <mergeCell ref="B45:F46"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="H45:L46"/>
-    <mergeCell ref="H48:L48"/>
-    <mergeCell ref="H64:L64"/>
-    <mergeCell ref="H80:L80"/>
-    <mergeCell ref="H96:L96"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="P21:U21"/>
-    <mergeCell ref="S3:X3"/>
-    <mergeCell ref="S8:X8"/>
   </mergeCells>
   <phoneticPr fontId="73" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -31355,8 +31368,8 @@
     <col min="1" max="26" width="13.7109375" style="234"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="586" t="s">
+    <row r="1" spans="1:12" ht="15.75">
+      <c r="A1" s="589" t="s">
         <v>5785</v>
       </c>
       <c r="B1" s="587"/>
@@ -31370,8 +31383,8 @@
       <c r="J1" s="587"/>
       <c r="K1" s="587"/>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="586" t="s">
+    <row r="2" spans="1:12" ht="15.75">
+      <c r="A2" s="589" t="s">
         <v>5786</v>
       </c>
       <c r="B2" s="587"/>
@@ -31385,27 +31398,27 @@
       <c r="J2" s="587"/>
       <c r="K2" s="587"/>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" ht="15.75">
       <c r="B3" s="496"/>
-      <c r="C3" s="586" t="s">
+      <c r="C3" s="589" t="s">
         <v>5787</v>
       </c>
       <c r="D3" s="587"/>
       <c r="E3" s="587"/>
-      <c r="F3" s="586" t="s">
+      <c r="F3" s="589" t="s">
         <v>5788</v>
       </c>
       <c r="G3" s="587"/>
       <c r="H3" s="496" t="s">
         <v>5789</v>
       </c>
-      <c r="I3" s="586" t="s">
+      <c r="I3" s="589" t="s">
         <v>5790</v>
       </c>
       <c r="J3" s="587"/>
       <c r="K3" s="587"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" ht="47.25">
       <c r="B4" s="496" t="s">
         <v>5791</v>
       </c>
@@ -31438,7 +31451,7 @@
       </c>
       <c r="L4" s="496"/>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" ht="15.75">
       <c r="A5" s="234" t="s">
         <v>5799</v>
       </c>
@@ -31474,7 +31487,7 @@
       </c>
       <c r="L5" s="496"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" ht="15.75">
       <c r="A6" s="234" t="s">
         <v>5804</v>
       </c>
@@ -31502,7 +31515,7 @@
       </c>
       <c r="L6" s="496"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" ht="15.75">
       <c r="A7" s="234" t="s">
         <v>5806</v>
       </c>
@@ -31528,7 +31541,7 @@
       </c>
       <c r="L7" s="496"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" ht="15.75">
       <c r="A8" s="234" t="s">
         <v>5807</v>
       </c>
@@ -31580,7 +31593,7 @@
       </c>
       <c r="L9" s="496"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" ht="15.75">
       <c r="A10" s="234" t="s">
         <v>5809</v>
       </c>
@@ -31608,7 +31621,7 @@
       </c>
       <c r="L10" s="496"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" ht="15.75">
       <c r="A11" s="234" t="s">
         <v>5810</v>
       </c>
@@ -31638,7 +31651,7 @@
       </c>
       <c r="L11" s="496"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" ht="47.25">
       <c r="A12" s="499" t="s">
         <v>5811</v>
       </c>
@@ -31664,7 +31677,7 @@
       </c>
       <c r="L12" s="496"/>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" ht="15.75">
       <c r="A13" s="234" t="s">
         <v>5812</v>
       </c>
@@ -31686,7 +31699,7 @@
       <c r="K13" s="496"/>
       <c r="L13" s="496"/>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" ht="15.75">
       <c r="A14" s="234" t="s">
         <v>5813</v>
       </c>
@@ -31708,7 +31721,7 @@
       <c r="K14" s="496"/>
       <c r="L14" s="496"/>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" ht="15.75">
       <c r="A15" s="234" t="s">
         <v>5814</v>
       </c>
@@ -31730,7 +31743,7 @@
       <c r="K15" s="496"/>
       <c r="L15" s="496"/>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" ht="15.75">
       <c r="B16" s="496"/>
       <c r="C16" s="496"/>
       <c r="D16" s="496"/>
@@ -31743,23 +31756,23 @@
       <c r="K16" s="496"/>
       <c r="L16" s="496"/>
     </row>
-    <row r="17" spans="2:17">
-      <c r="H17" s="589" t="s">
+    <row r="17" spans="2:17" ht="15.75">
+      <c r="H17" s="588" t="s">
         <v>5815</v>
       </c>
-      <c r="I17" s="549"/>
+      <c r="I17" s="545"/>
       <c r="J17" s="587"/>
       <c r="K17" s="234" t="s">
         <v>5816</v>
       </c>
-      <c r="N17" s="588" t="s">
+      <c r="N17" s="586" t="s">
         <v>5817</v>
       </c>
       <c r="O17" s="587"/>
       <c r="P17" s="587"/>
       <c r="Q17" s="587"/>
     </row>
-    <row r="18" spans="2:17">
+    <row r="18" spans="2:17" ht="17.25">
       <c r="B18" s="500" t="s">
         <v>1</v>
       </c>
@@ -31803,7 +31816,7 @@
         <v>5825</v>
       </c>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" ht="17.25">
       <c r="B19" s="29" t="s">
         <v>274</v>
       </c>
@@ -31844,7 +31857,7 @@
         <v>5834</v>
       </c>
     </row>
-    <row r="20" spans="2:17">
+    <row r="20" spans="2:17" ht="17.25">
       <c r="B20" s="29" t="s">
         <v>324</v>
       </c>
@@ -31888,7 +31901,7 @@
         <v>5844</v>
       </c>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" ht="17.25">
       <c r="B21" s="29" t="s">
         <v>326</v>
       </c>
@@ -31914,7 +31927,7 @@
         <v>5848</v>
       </c>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" ht="17.25">
       <c r="B22" s="29" t="s">
         <v>357</v>
       </c>
@@ -31955,7 +31968,7 @@
         <v>5855</v>
       </c>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" ht="17.25">
       <c r="B23" s="29" t="s">
         <v>5856</v>
       </c>
@@ -31999,7 +32012,7 @@
         <v>5866</v>
       </c>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" ht="17.25">
       <c r="B24" s="29" t="s">
         <v>332</v>
       </c>
@@ -32041,7 +32054,7 @@
         <v>5876</v>
       </c>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" ht="17.25">
       <c r="B25" s="29" t="s">
         <v>154</v>
       </c>
@@ -32081,7 +32094,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" ht="17.25">
       <c r="B26" s="29" t="s">
         <v>578</v>
       </c>
@@ -32121,7 +32134,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:17" ht="17.25">
       <c r="B27" s="29" t="s">
         <v>359</v>
       </c>
@@ -32161,7 +32174,7 @@
         <v>5903</v>
       </c>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" ht="17.25">
       <c r="B28" s="29" t="s">
         <v>5351</v>
       </c>
@@ -32195,7 +32208,7 @@
         <v>5911</v>
       </c>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" ht="17.25">
       <c r="E29" s="29" t="s">
         <v>5912</v>
       </c>
@@ -32207,13 +32220,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
     <mergeCell ref="N17:Q17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
   </mergeCells>
   <phoneticPr fontId="73" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -33435,8 +33448,8 @@
       <c r="E11" s="548" t="s">
         <v>1088</v>
       </c>
-      <c r="F11" s="549"/>
-      <c r="G11" s="550"/>
+      <c r="F11" s="545"/>
+      <c r="G11" s="546"/>
       <c r="H11" s="255"/>
       <c r="I11" s="239" t="s">
         <v>1089</v>
@@ -33799,13 +33812,13 @@
       <c r="C19" s="246" t="s">
         <v>130</v>
       </c>
-      <c r="D19" s="545" t="s">
+      <c r="D19" s="543" t="s">
         <v>1128</v>
       </c>
-      <c r="E19" s="556"/>
-      <c r="F19" s="556"/>
-      <c r="G19" s="556"/>
-      <c r="H19" s="556"/>
+      <c r="E19" s="549"/>
+      <c r="F19" s="549"/>
+      <c r="G19" s="549"/>
+      <c r="H19" s="549"/>
       <c r="I19" s="239" t="s">
         <v>1129</v>
       </c>
@@ -33995,11 +34008,11 @@
       <c r="C25" s="265" t="s">
         <v>85</v>
       </c>
-      <c r="D25" s="552"/>
-      <c r="E25" s="558"/>
-      <c r="F25" s="558"/>
-      <c r="G25" s="558"/>
-      <c r="H25" s="558"/>
+      <c r="D25" s="542"/>
+      <c r="E25" s="547"/>
+      <c r="F25" s="547"/>
+      <c r="G25" s="547"/>
+      <c r="H25" s="547"/>
       <c r="I25" s="266" t="s">
         <v>1155</v>
       </c>
@@ -34037,10 +34050,10 @@
       <c r="D27" s="548" t="s">
         <v>1161</v>
       </c>
-      <c r="E27" s="549"/>
-      <c r="F27" s="549"/>
-      <c r="G27" s="549"/>
-      <c r="H27" s="550"/>
+      <c r="E27" s="545"/>
+      <c r="F27" s="545"/>
+      <c r="G27" s="545"/>
+      <c r="H27" s="546"/>
       <c r="I27" s="239" t="s">
         <v>1162</v>
       </c>
@@ -34227,8 +34240,8 @@
       <c r="E34" s="548" t="s">
         <v>1199</v>
       </c>
-      <c r="F34" s="549"/>
-      <c r="G34" s="550"/>
+      <c r="F34" s="545"/>
+      <c r="G34" s="546"/>
       <c r="H34" s="255"/>
       <c r="I34" s="239" t="s">
         <v>1200</v>
@@ -34267,10 +34280,10 @@
       <c r="D36" s="548" t="s">
         <v>1161</v>
       </c>
-      <c r="E36" s="549"/>
-      <c r="F36" s="549"/>
-      <c r="G36" s="549"/>
-      <c r="H36" s="550"/>
+      <c r="E36" s="545"/>
+      <c r="F36" s="545"/>
+      <c r="G36" s="545"/>
+      <c r="H36" s="546"/>
       <c r="I36" s="239" t="s">
         <v>1162</v>
       </c>
@@ -34458,8 +34471,8 @@
       <c r="E43" s="548" t="s">
         <v>1234</v>
       </c>
-      <c r="F43" s="549"/>
-      <c r="G43" s="550"/>
+      <c r="F43" s="545"/>
+      <c r="G43" s="546"/>
       <c r="H43" s="255"/>
       <c r="I43" s="239" t="s">
         <v>1235</v>
@@ -34561,10 +34574,10 @@
       <c r="D47" s="548" t="s">
         <v>1253</v>
       </c>
-      <c r="E47" s="549"/>
-      <c r="F47" s="549"/>
-      <c r="G47" s="549"/>
-      <c r="H47" s="550"/>
+      <c r="E47" s="545"/>
+      <c r="F47" s="545"/>
+      <c r="G47" s="545"/>
+      <c r="H47" s="546"/>
       <c r="I47" s="239" t="s">
         <v>1254</v>
       </c>
@@ -34611,10 +34624,10 @@
       <c r="D49" s="548" t="s">
         <v>1263</v>
       </c>
-      <c r="E49" s="549"/>
-      <c r="F49" s="549"/>
-      <c r="G49" s="549"/>
-      <c r="H49" s="550"/>
+      <c r="E49" s="545"/>
+      <c r="F49" s="545"/>
+      <c r="G49" s="545"/>
+      <c r="H49" s="546"/>
       <c r="I49" s="266" t="s">
         <v>1264</v>
       </c>
@@ -34864,10 +34877,10 @@
       <c r="D58" s="548" t="s">
         <v>1315</v>
       </c>
-      <c r="E58" s="549"/>
-      <c r="F58" s="549"/>
-      <c r="G58" s="549"/>
-      <c r="H58" s="550"/>
+      <c r="E58" s="545"/>
+      <c r="F58" s="545"/>
+      <c r="G58" s="545"/>
+      <c r="H58" s="546"/>
       <c r="I58" s="239" t="s">
         <v>1316</v>
       </c>
@@ -35019,10 +35032,10 @@
       <c r="D63" s="548" t="s">
         <v>1333</v>
       </c>
-      <c r="E63" s="549"/>
-      <c r="F63" s="549"/>
-      <c r="G63" s="549"/>
-      <c r="H63" s="550"/>
+      <c r="E63" s="545"/>
+      <c r="F63" s="545"/>
+      <c r="G63" s="545"/>
+      <c r="H63" s="546"/>
       <c r="I63" s="239" t="s">
         <v>1334</v>
       </c>
@@ -35336,8 +35349,8 @@
       <c r="E73" s="548" t="s">
         <v>1391</v>
       </c>
-      <c r="F73" s="549"/>
-      <c r="G73" s="550"/>
+      <c r="F73" s="545"/>
+      <c r="G73" s="546"/>
       <c r="H73" s="255"/>
       <c r="I73" s="239" t="s">
         <v>1392</v>
@@ -35670,11 +35683,11 @@
       <c r="C83" t="s">
         <v>85</v>
       </c>
-      <c r="D83" s="551"/>
-      <c r="E83" s="549"/>
-      <c r="F83" s="549"/>
-      <c r="G83" s="549"/>
-      <c r="H83" s="550"/>
+      <c r="D83" s="544"/>
+      <c r="E83" s="545"/>
+      <c r="F83" s="545"/>
+      <c r="G83" s="545"/>
+      <c r="H83" s="546"/>
       <c r="I83" s="266" t="s">
         <v>1155</v>
       </c>
@@ -35883,13 +35896,13 @@
       <c r="C90" t="s">
         <v>125</v>
       </c>
-      <c r="D90" s="551" t="s">
+      <c r="D90" s="544" t="s">
         <v>1476</v>
       </c>
-      <c r="E90" s="549"/>
-      <c r="F90" s="549"/>
-      <c r="G90" s="549"/>
-      <c r="H90" s="550"/>
+      <c r="E90" s="545"/>
+      <c r="F90" s="545"/>
+      <c r="G90" s="545"/>
+      <c r="H90" s="546"/>
       <c r="I90" s="239" t="s">
         <v>1477</v>
       </c>
@@ -35983,10 +35996,10 @@
         <v>1262</v>
       </c>
       <c r="D93" s="548"/>
-      <c r="E93" s="549"/>
-      <c r="F93" s="549"/>
-      <c r="G93" s="549"/>
-      <c r="H93" s="550"/>
+      <c r="E93" s="545"/>
+      <c r="F93" s="545"/>
+      <c r="G93" s="545"/>
+      <c r="H93" s="546"/>
       <c r="I93" s="266" t="s">
         <v>1264</v>
       </c>
@@ -36137,10 +36150,10 @@
         <v>1262</v>
       </c>
       <c r="D99" s="548"/>
-      <c r="E99" s="549"/>
-      <c r="F99" s="549"/>
-      <c r="G99" s="549"/>
-      <c r="H99" s="550"/>
+      <c r="E99" s="545"/>
+      <c r="F99" s="545"/>
+      <c r="G99" s="545"/>
+      <c r="H99" s="546"/>
       <c r="I99" s="266" t="s">
         <v>1264</v>
       </c>
@@ -36151,13 +36164,13 @@
       <c r="C100" t="s">
         <v>1514</v>
       </c>
-      <c r="D100" s="551" t="s">
+      <c r="D100" s="544" t="s">
         <v>1515</v>
       </c>
-      <c r="E100" s="549"/>
-      <c r="F100" s="549"/>
-      <c r="G100" s="549"/>
-      <c r="H100" s="550"/>
+      <c r="E100" s="545"/>
+      <c r="F100" s="545"/>
+      <c r="G100" s="545"/>
+      <c r="H100" s="546"/>
       <c r="I100" s="239" t="s">
         <v>1516</v>
       </c>
@@ -36328,11 +36341,11 @@
       <c r="C104" t="s">
         <v>1530</v>
       </c>
-      <c r="D104" s="551"/>
-      <c r="E104" s="549"/>
-      <c r="F104" s="549"/>
-      <c r="G104" s="549"/>
-      <c r="H104" s="550"/>
+      <c r="D104" s="544"/>
+      <c r="E104" s="545"/>
+      <c r="F104" s="545"/>
+      <c r="G104" s="545"/>
+      <c r="H104" s="546"/>
       <c r="I104" s="239" t="s">
         <v>1531</v>
       </c>
@@ -36675,11 +36688,11 @@
       <c r="C111" t="s">
         <v>1530</v>
       </c>
-      <c r="D111" s="551"/>
-      <c r="E111" s="549"/>
-      <c r="F111" s="549"/>
-      <c r="G111" s="549"/>
-      <c r="H111" s="550"/>
+      <c r="D111" s="544"/>
+      <c r="E111" s="545"/>
+      <c r="F111" s="545"/>
+      <c r="G111" s="545"/>
+      <c r="H111" s="546"/>
       <c r="I111" s="239" t="s">
         <v>1531</v>
       </c>
@@ -36965,8 +36978,8 @@
       <c r="E117" s="548" t="s">
         <v>1599</v>
       </c>
-      <c r="F117" s="549"/>
-      <c r="G117" s="550"/>
+      <c r="F117" s="545"/>
+      <c r="G117" s="546"/>
       <c r="H117" s="255"/>
       <c r="I117" s="239" t="s">
         <v>1600</v>
@@ -37070,16 +37083,16 @@
       <c r="A120" s="292" t="s">
         <v>307</v>
       </c>
-      <c r="B120" s="542"/>
-      <c r="C120" s="543"/>
-      <c r="D120" s="543"/>
-      <c r="E120" s="543"/>
-      <c r="F120" s="543"/>
-      <c r="G120" s="544"/>
-      <c r="H120" s="543"/>
-      <c r="I120" s="543"/>
-      <c r="J120" s="543"/>
-      <c r="K120" s="543"/>
+      <c r="B120" s="551"/>
+      <c r="C120" s="552"/>
+      <c r="D120" s="552"/>
+      <c r="E120" s="552"/>
+      <c r="F120" s="552"/>
+      <c r="G120" s="553"/>
+      <c r="H120" s="552"/>
+      <c r="I120" s="552"/>
+      <c r="J120" s="552"/>
+      <c r="K120" s="552"/>
       <c r="L120" s="292"/>
       <c r="M120" s="295"/>
       <c r="N120" s="292"/>
@@ -37325,10 +37338,10 @@
       <c r="D126" s="548" t="s">
         <v>1650</v>
       </c>
-      <c r="E126" s="549"/>
-      <c r="F126" s="549"/>
-      <c r="G126" s="549"/>
-      <c r="H126" s="550"/>
+      <c r="E126" s="545"/>
+      <c r="F126" s="545"/>
+      <c r="G126" s="545"/>
+      <c r="H126" s="546"/>
       <c r="I126" s="239" t="s">
         <v>1651</v>
       </c>
@@ -37647,10 +37660,10 @@
       <c r="D135" s="548" t="s">
         <v>1650</v>
       </c>
-      <c r="E135" s="549"/>
-      <c r="F135" s="549"/>
-      <c r="G135" s="549"/>
-      <c r="H135" s="550"/>
+      <c r="E135" s="545"/>
+      <c r="F135" s="545"/>
+      <c r="G135" s="545"/>
+      <c r="H135" s="546"/>
       <c r="I135" s="239" t="s">
         <v>1651</v>
       </c>
@@ -37722,12 +37735,12 @@
       <c r="C137" t="s">
         <v>1710</v>
       </c>
-      <c r="D137" s="546" t="s">
+      <c r="D137" s="557" t="s">
         <v>1711</v>
       </c>
-      <c r="E137" s="543"/>
-      <c r="F137" s="543"/>
-      <c r="G137" s="543"/>
+      <c r="E137" s="552"/>
+      <c r="F137" s="552"/>
+      <c r="G137" s="552"/>
       <c r="H137" s="300"/>
       <c r="I137" s="301"/>
       <c r="J137" s="301"/>
@@ -37757,13 +37770,13 @@
       <c r="C138" t="s">
         <v>803</v>
       </c>
-      <c r="D138" s="543" t="s">
+      <c r="D138" s="552" t="s">
         <v>1713</v>
       </c>
-      <c r="E138" s="543"/>
-      <c r="F138" s="543"/>
-      <c r="G138" s="545"/>
-      <c r="H138" s="543"/>
+      <c r="E138" s="552"/>
+      <c r="F138" s="552"/>
+      <c r="G138" s="543"/>
+      <c r="H138" s="552"/>
       <c r="I138" s="239" t="s">
         <v>1714</v>
       </c>
@@ -37772,16 +37785,16 @@
       <c r="A139" s="292" t="s">
         <v>308</v>
       </c>
-      <c r="B139" s="542"/>
-      <c r="C139" s="543"/>
-      <c r="D139" s="543"/>
-      <c r="E139" s="543"/>
-      <c r="F139" s="543"/>
-      <c r="G139" s="544"/>
-      <c r="H139" s="543"/>
-      <c r="I139" s="543"/>
-      <c r="J139" s="543"/>
-      <c r="K139" s="543"/>
+      <c r="B139" s="551"/>
+      <c r="C139" s="552"/>
+      <c r="D139" s="552"/>
+      <c r="E139" s="552"/>
+      <c r="F139" s="552"/>
+      <c r="G139" s="553"/>
+      <c r="H139" s="552"/>
+      <c r="I139" s="552"/>
+      <c r="J139" s="552"/>
+      <c r="K139" s="552"/>
       <c r="L139" s="302"/>
       <c r="M139" s="295"/>
       <c r="N139" s="302"/>
@@ -38014,13 +38027,13 @@
       <c r="C144" t="s">
         <v>127</v>
       </c>
-      <c r="D144" s="552" t="s">
+      <c r="D144" s="542" t="s">
         <v>1734</v>
       </c>
-      <c r="E144" s="549"/>
-      <c r="F144" s="549"/>
-      <c r="G144" s="549"/>
-      <c r="H144" s="550"/>
+      <c r="E144" s="545"/>
+      <c r="F144" s="545"/>
+      <c r="G144" s="545"/>
+      <c r="H144" s="546"/>
       <c r="I144" s="239" t="s">
         <v>1737</v>
       </c>
@@ -38276,10 +38289,10 @@
       <c r="D149" s="548" t="s">
         <v>1765</v>
       </c>
-      <c r="E149" s="549"/>
-      <c r="F149" s="549"/>
-      <c r="G149" s="549"/>
-      <c r="H149" s="550"/>
+      <c r="E149" s="545"/>
+      <c r="F149" s="545"/>
+      <c r="G149" s="545"/>
+      <c r="H149" s="546"/>
       <c r="I149" s="239" t="s">
         <v>1766</v>
       </c>
@@ -38527,22 +38540,22 @@
       <c r="C155" t="s">
         <v>1802</v>
       </c>
-      <c r="D155" s="547"/>
-      <c r="E155" s="543"/>
-      <c r="F155" s="543"/>
-      <c r="G155" s="543"/>
-      <c r="H155" s="547" t="s">
+      <c r="D155" s="558"/>
+      <c r="E155" s="552"/>
+      <c r="F155" s="552"/>
+      <c r="G155" s="552"/>
+      <c r="H155" s="558" t="s">
         <v>1803</v>
       </c>
-      <c r="I155" s="543"/>
-      <c r="J155" s="546" t="s">
+      <c r="I155" s="552"/>
+      <c r="J155" s="557" t="s">
         <v>1804</v>
       </c>
-      <c r="K155" s="543"/>
-      <c r="L155" s="546" t="s">
+      <c r="K155" s="552"/>
+      <c r="L155" s="557" t="s">
         <v>1805</v>
       </c>
-      <c r="M155" s="543"/>
+      <c r="M155" s="552"/>
       <c r="N155" s="303"/>
       <c r="O155" s="303"/>
       <c r="P155" s="303"/>
@@ -38572,13 +38585,13 @@
       <c r="C156" t="s">
         <v>948</v>
       </c>
-      <c r="D156" s="543" t="s">
+      <c r="D156" s="552" t="s">
         <v>1807</v>
       </c>
-      <c r="E156" s="543"/>
-      <c r="F156" s="543"/>
-      <c r="G156" s="545"/>
-      <c r="H156" s="543"/>
+      <c r="E156" s="552"/>
+      <c r="F156" s="552"/>
+      <c r="G156" s="543"/>
+      <c r="H156" s="552"/>
       <c r="I156" s="239" t="s">
         <v>1808</v>
       </c>
@@ -38611,13 +38624,13 @@
       <c r="C157" t="s">
         <v>125</v>
       </c>
-      <c r="D157" s="551" t="s">
+      <c r="D157" s="544" t="s">
         <v>1809</v>
       </c>
-      <c r="E157" s="549"/>
-      <c r="F157" s="549"/>
-      <c r="G157" s="549"/>
-      <c r="H157" s="550"/>
+      <c r="E157" s="545"/>
+      <c r="F157" s="545"/>
+      <c r="G157" s="545"/>
+      <c r="H157" s="546"/>
       <c r="I157" s="239" t="s">
         <v>1477</v>
       </c>
@@ -38646,16 +38659,16 @@
       <c r="A158" s="292" t="s">
         <v>309</v>
       </c>
-      <c r="B158" s="542"/>
-      <c r="C158" s="543"/>
-      <c r="D158" s="543"/>
-      <c r="E158" s="543"/>
-      <c r="F158" s="543"/>
-      <c r="G158" s="544"/>
-      <c r="H158" s="543"/>
-      <c r="I158" s="543"/>
-      <c r="J158" s="543"/>
-      <c r="K158" s="543"/>
+      <c r="B158" s="551"/>
+      <c r="C158" s="552"/>
+      <c r="D158" s="552"/>
+      <c r="E158" s="552"/>
+      <c r="F158" s="552"/>
+      <c r="G158" s="553"/>
+      <c r="H158" s="552"/>
+      <c r="I158" s="552"/>
+      <c r="J158" s="552"/>
+      <c r="K158" s="552"/>
       <c r="L158" s="302"/>
       <c r="M158" s="295"/>
       <c r="N158" s="302"/>
@@ -39242,13 +39255,13 @@
       <c r="C170" t="s">
         <v>1867</v>
       </c>
-      <c r="D170" s="551" t="s">
+      <c r="D170" s="544" t="s">
         <v>1868</v>
       </c>
-      <c r="E170" s="549"/>
-      <c r="F170" s="549"/>
-      <c r="G170" s="549"/>
-      <c r="H170" s="550"/>
+      <c r="E170" s="545"/>
+      <c r="F170" s="545"/>
+      <c r="G170" s="545"/>
+      <c r="H170" s="546"/>
       <c r="I170" s="239" t="s">
         <v>1869</v>
       </c>
@@ -39398,22 +39411,22 @@
       <c r="C174" t="s">
         <v>1889</v>
       </c>
-      <c r="D174" s="547"/>
-      <c r="E174" s="545"/>
-      <c r="F174" s="545"/>
-      <c r="G174" s="545"/>
-      <c r="H174" s="547" t="s">
+      <c r="D174" s="558"/>
+      <c r="E174" s="543"/>
+      <c r="F174" s="543"/>
+      <c r="G174" s="543"/>
+      <c r="H174" s="558" t="s">
         <v>1890</v>
       </c>
-      <c r="I174" s="552"/>
-      <c r="J174" s="546" t="s">
+      <c r="I174" s="542"/>
+      <c r="J174" s="557" t="s">
         <v>1891</v>
       </c>
-      <c r="K174" s="552"/>
-      <c r="L174" s="546" t="s">
+      <c r="K174" s="542"/>
+      <c r="L174" s="557" t="s">
         <v>1892</v>
       </c>
-      <c r="M174" s="552"/>
+      <c r="M174" s="542"/>
       <c r="N174" s="303"/>
       <c r="O174" s="303"/>
       <c r="P174" s="303"/>
@@ -39443,13 +39456,13 @@
       <c r="C175" t="s">
         <v>861</v>
       </c>
-      <c r="D175" s="543" t="s">
+      <c r="D175" s="552" t="s">
         <v>1894</v>
       </c>
-      <c r="E175" s="543"/>
-      <c r="F175" s="543"/>
-      <c r="G175" s="545"/>
-      <c r="H175" s="543"/>
+      <c r="E175" s="552"/>
+      <c r="F175" s="552"/>
+      <c r="G175" s="543"/>
+      <c r="H175" s="552"/>
       <c r="I175" s="239" t="s">
         <v>1895</v>
       </c>
@@ -39480,16 +39493,16 @@
       <c r="A176" s="292" t="s">
         <v>310</v>
       </c>
-      <c r="B176" s="542"/>
-      <c r="C176" s="543"/>
-      <c r="D176" s="543"/>
-      <c r="E176" s="543"/>
-      <c r="F176" s="543"/>
-      <c r="G176" s="544"/>
-      <c r="H176" s="543"/>
-      <c r="I176" s="543"/>
-      <c r="J176" s="543"/>
-      <c r="K176" s="543"/>
+      <c r="B176" s="551"/>
+      <c r="C176" s="552"/>
+      <c r="D176" s="552"/>
+      <c r="E176" s="552"/>
+      <c r="F176" s="552"/>
+      <c r="G176" s="553"/>
+      <c r="H176" s="552"/>
+      <c r="I176" s="552"/>
+      <c r="J176" s="552"/>
+      <c r="K176" s="552"/>
       <c r="L176" s="302"/>
       <c r="M176" s="295"/>
       <c r="N176" s="302"/>
@@ -39875,10 +39888,10 @@
       <c r="D184" s="548" t="s">
         <v>1935</v>
       </c>
-      <c r="E184" s="549"/>
-      <c r="F184" s="549"/>
-      <c r="G184" s="549"/>
-      <c r="H184" s="550"/>
+      <c r="E184" s="545"/>
+      <c r="F184" s="545"/>
+      <c r="G184" s="545"/>
+      <c r="H184" s="546"/>
       <c r="I184" s="239" t="s">
         <v>1936</v>
       </c>
@@ -40182,8 +40195,8 @@
       <c r="E190" s="548" t="s">
         <v>1969</v>
       </c>
-      <c r="F190" s="549"/>
-      <c r="G190" s="550"/>
+      <c r="F190" s="545"/>
+      <c r="G190" s="546"/>
       <c r="H190" s="255"/>
       <c r="I190" s="239" t="s">
         <v>1970</v>
@@ -40308,14 +40321,14 @@
       <c r="C194" t="s">
         <v>1993</v>
       </c>
-      <c r="D194" s="546" t="s">
+      <c r="D194" s="557" t="s">
         <v>1994</v>
       </c>
-      <c r="E194" s="549"/>
-      <c r="F194" s="549"/>
-      <c r="G194" s="549"/>
-      <c r="H194" s="549"/>
-      <c r="I194" s="550"/>
+      <c r="E194" s="545"/>
+      <c r="F194" s="545"/>
+      <c r="G194" s="545"/>
+      <c r="H194" s="545"/>
+      <c r="I194" s="546"/>
       <c r="J194" s="301"/>
       <c r="K194" s="301"/>
       <c r="L194" s="301"/>
@@ -40343,13 +40356,13 @@
       <c r="C195" t="s">
         <v>890</v>
       </c>
-      <c r="D195" s="543" t="s">
+      <c r="D195" s="552" t="s">
         <v>1996</v>
       </c>
-      <c r="E195" s="543"/>
-      <c r="F195" s="543"/>
-      <c r="G195" s="545"/>
-      <c r="H195" s="543"/>
+      <c r="E195" s="552"/>
+      <c r="F195" s="552"/>
+      <c r="G195" s="543"/>
+      <c r="H195" s="552"/>
       <c r="I195" s="239" t="s">
         <v>1997</v>
       </c>
@@ -40380,16 +40393,16 @@
       <c r="A196" s="292" t="s">
         <v>1998</v>
       </c>
-      <c r="B196" s="542"/>
-      <c r="C196" s="543"/>
-      <c r="D196" s="543"/>
-      <c r="E196" s="543"/>
-      <c r="F196" s="543"/>
-      <c r="G196" s="544"/>
-      <c r="H196" s="543"/>
-      <c r="I196" s="543"/>
-      <c r="J196" s="543"/>
-      <c r="K196" s="543"/>
+      <c r="B196" s="551"/>
+      <c r="C196" s="552"/>
+      <c r="D196" s="552"/>
+      <c r="E196" s="552"/>
+      <c r="F196" s="552"/>
+      <c r="G196" s="553"/>
+      <c r="H196" s="552"/>
+      <c r="I196" s="552"/>
+      <c r="J196" s="552"/>
+      <c r="K196" s="552"/>
       <c r="L196" s="302"/>
       <c r="M196" s="295"/>
       <c r="N196" s="302"/>
@@ -41069,17 +41082,17 @@
       <c r="D218" s="548" t="s">
         <v>2124</v>
       </c>
-      <c r="E218" s="549"/>
-      <c r="F218" s="549"/>
-      <c r="G218" s="550"/>
-      <c r="H218" s="551" t="s">
+      <c r="E218" s="545"/>
+      <c r="F218" s="545"/>
+      <c r="G218" s="546"/>
+      <c r="H218" s="544" t="s">
         <v>2125</v>
       </c>
-      <c r="I218" s="550"/>
-      <c r="J218" s="553" t="s">
+      <c r="I218" s="546"/>
+      <c r="J218" s="555" t="s">
         <v>2126</v>
       </c>
-      <c r="K218" s="554"/>
+      <c r="K218" s="556"/>
       <c r="L218" s="239"/>
       <c r="M218" s="246"/>
     </row>
@@ -41091,19 +41104,19 @@
       <c r="C219" s="246" t="s">
         <v>2128</v>
       </c>
-      <c r="D219" s="545" t="s">
+      <c r="D219" s="543" t="s">
         <v>2129</v>
       </c>
-      <c r="E219" s="557"/>
-      <c r="F219" s="557"/>
-      <c r="H219" s="552" t="s">
+      <c r="E219" s="550"/>
+      <c r="F219" s="550"/>
+      <c r="H219" s="542" t="s">
         <v>2130</v>
       </c>
-      <c r="I219" s="557"/>
-      <c r="J219" s="552" t="s">
+      <c r="I219" s="550"/>
+      <c r="J219" s="542" t="s">
         <v>2131</v>
       </c>
-      <c r="K219" s="557"/>
+      <c r="K219" s="550"/>
       <c r="L219" s="246"/>
       <c r="M219" s="289"/>
       <c r="N219" s="246"/>
@@ -41138,17 +41151,17 @@
       <c r="D220" s="548" t="s">
         <v>2134</v>
       </c>
-      <c r="E220" s="549"/>
-      <c r="F220" s="549"/>
-      <c r="G220" s="550"/>
-      <c r="H220" s="551" t="s">
+      <c r="E220" s="545"/>
+      <c r="F220" s="545"/>
+      <c r="G220" s="546"/>
+      <c r="H220" s="544" t="s">
         <v>2135</v>
       </c>
-      <c r="I220" s="550"/>
-      <c r="J220" s="553" t="s">
+      <c r="I220" s="546"/>
+      <c r="J220" s="555" t="s">
         <v>2136</v>
       </c>
-      <c r="K220" s="554"/>
+      <c r="K220" s="556"/>
       <c r="L220" s="239"/>
       <c r="M220" s="246"/>
     </row>
@@ -41163,17 +41176,17 @@
       <c r="D221" s="548" t="s">
         <v>2139</v>
       </c>
-      <c r="E221" s="549"/>
-      <c r="F221" s="549"/>
-      <c r="G221" s="550"/>
-      <c r="H221" s="551" t="s">
+      <c r="E221" s="545"/>
+      <c r="F221" s="545"/>
+      <c r="G221" s="546"/>
+      <c r="H221" s="544" t="s">
         <v>2140</v>
       </c>
-      <c r="I221" s="550"/>
-      <c r="J221" s="553" t="s">
+      <c r="I221" s="546"/>
+      <c r="J221" s="555" t="s">
         <v>2141</v>
       </c>
-      <c r="K221" s="554"/>
+      <c r="K221" s="556"/>
       <c r="L221" s="239"/>
       <c r="M221" s="246"/>
     </row>
@@ -41188,17 +41201,17 @@
       <c r="D222" s="548" t="s">
         <v>2144</v>
       </c>
-      <c r="E222" s="549"/>
-      <c r="F222" s="549"/>
-      <c r="G222" s="550"/>
-      <c r="H222" s="551" t="s">
+      <c r="E222" s="545"/>
+      <c r="F222" s="545"/>
+      <c r="G222" s="546"/>
+      <c r="H222" s="544" t="s">
         <v>2145</v>
       </c>
-      <c r="I222" s="550"/>
-      <c r="J222" s="553" t="s">
+      <c r="I222" s="546"/>
+      <c r="J222" s="555" t="s">
         <v>2146</v>
       </c>
-      <c r="K222" s="554"/>
+      <c r="K222" s="556"/>
       <c r="L222" s="239"/>
       <c r="M222" s="246"/>
     </row>
@@ -41213,17 +41226,17 @@
       <c r="D223" s="548" t="s">
         <v>2149</v>
       </c>
-      <c r="E223" s="549"/>
-      <c r="F223" s="549"/>
-      <c r="G223" s="550"/>
-      <c r="H223" s="551" t="s">
+      <c r="E223" s="545"/>
+      <c r="F223" s="545"/>
+      <c r="G223" s="546"/>
+      <c r="H223" s="544" t="s">
         <v>2150</v>
       </c>
-      <c r="I223" s="550"/>
-      <c r="J223" s="553" t="s">
+      <c r="I223" s="546"/>
+      <c r="J223" s="555" t="s">
         <v>2151</v>
       </c>
-      <c r="K223" s="554"/>
+      <c r="K223" s="556"/>
       <c r="L223" s="239"/>
       <c r="M223" s="246"/>
     </row>
@@ -41235,19 +41248,19 @@
       <c r="C224" s="246" t="s">
         <v>2153</v>
       </c>
-      <c r="D224" s="545" t="s">
+      <c r="D224" s="543" t="s">
         <v>2154</v>
       </c>
-      <c r="E224" s="545"/>
-      <c r="F224" s="557"/>
-      <c r="H224" s="552" t="s">
+      <c r="E224" s="543"/>
+      <c r="F224" s="550"/>
+      <c r="H224" s="542" t="s">
         <v>2155</v>
       </c>
-      <c r="I224" s="545"/>
-      <c r="J224" s="552" t="s">
+      <c r="I224" s="543"/>
+      <c r="J224" s="542" t="s">
         <v>2156</v>
       </c>
-      <c r="K224" s="545"/>
+      <c r="K224" s="543"/>
       <c r="L224" s="246"/>
       <c r="M224" s="313"/>
       <c r="N224" s="246"/>
@@ -41275,16 +41288,16 @@
       <c r="A225" s="292" t="s">
         <v>2157</v>
       </c>
-      <c r="B225" s="542"/>
-      <c r="C225" s="543"/>
-      <c r="D225" s="543"/>
-      <c r="E225" s="543"/>
-      <c r="F225" s="543"/>
-      <c r="G225" s="544"/>
-      <c r="H225" s="543"/>
-      <c r="I225" s="543"/>
-      <c r="J225" s="543"/>
-      <c r="K225" s="543"/>
+      <c r="B225" s="551"/>
+      <c r="C225" s="552"/>
+      <c r="D225" s="552"/>
+      <c r="E225" s="552"/>
+      <c r="F225" s="552"/>
+      <c r="G225" s="553"/>
+      <c r="H225" s="552"/>
+      <c r="I225" s="552"/>
+      <c r="J225" s="552"/>
+      <c r="K225" s="552"/>
       <c r="L225" s="302"/>
       <c r="M225" s="295"/>
       <c r="N225" s="302"/>
@@ -42304,16 +42317,16 @@
       <c r="A254" s="292" t="s">
         <v>314</v>
       </c>
-      <c r="B254" s="542"/>
-      <c r="C254" s="543"/>
-      <c r="D254" s="543"/>
-      <c r="E254" s="543"/>
-      <c r="F254" s="543"/>
-      <c r="G254" s="544"/>
-      <c r="H254" s="543"/>
-      <c r="I254" s="543"/>
-      <c r="J254" s="543"/>
-      <c r="K254" s="543"/>
+      <c r="B254" s="551"/>
+      <c r="C254" s="552"/>
+      <c r="D254" s="552"/>
+      <c r="E254" s="552"/>
+      <c r="F254" s="552"/>
+      <c r="G254" s="553"/>
+      <c r="H254" s="552"/>
+      <c r="I254" s="552"/>
+      <c r="J254" s="552"/>
+      <c r="K254" s="552"/>
       <c r="L254" s="302"/>
       <c r="M254" s="295"/>
       <c r="N254" s="302"/>
@@ -42950,16 +42963,16 @@
       <c r="A267" s="292" t="s">
         <v>2386</v>
       </c>
-      <c r="B267" s="542"/>
-      <c r="C267" s="543"/>
-      <c r="D267" s="543"/>
-      <c r="E267" s="543"/>
-      <c r="F267" s="543"/>
-      <c r="G267" s="544"/>
-      <c r="H267" s="543"/>
-      <c r="I267" s="543"/>
-      <c r="J267" s="543"/>
-      <c r="K267" s="543"/>
+      <c r="B267" s="551"/>
+      <c r="C267" s="552"/>
+      <c r="D267" s="552"/>
+      <c r="E267" s="552"/>
+      <c r="F267" s="552"/>
+      <c r="G267" s="553"/>
+      <c r="H267" s="552"/>
+      <c r="I267" s="552"/>
+      <c r="J267" s="552"/>
+      <c r="K267" s="552"/>
       <c r="L267" s="302"/>
       <c r="M267" s="295"/>
       <c r="N267" s="302"/>
@@ -43274,16 +43287,16 @@
       <c r="A274" s="292" t="s">
         <v>2425</v>
       </c>
-      <c r="B274" s="555"/>
-      <c r="C274" s="549"/>
-      <c r="D274" s="549"/>
-      <c r="E274" s="549"/>
-      <c r="F274" s="549"/>
-      <c r="G274" s="549"/>
-      <c r="H274" s="549"/>
-      <c r="I274" s="549"/>
-      <c r="J274" s="549"/>
-      <c r="K274" s="550"/>
+      <c r="B274" s="554"/>
+      <c r="C274" s="545"/>
+      <c r="D274" s="545"/>
+      <c r="E274" s="545"/>
+      <c r="F274" s="545"/>
+      <c r="G274" s="545"/>
+      <c r="H274" s="545"/>
+      <c r="I274" s="545"/>
+      <c r="J274" s="545"/>
+      <c r="K274" s="546"/>
       <c r="L274" s="292"/>
       <c r="M274" s="295"/>
       <c r="N274" s="292"/>
@@ -43555,16 +43568,16 @@
       <c r="A280" s="292" t="s">
         <v>315</v>
       </c>
-      <c r="B280" s="542"/>
-      <c r="C280" s="543"/>
-      <c r="D280" s="543"/>
-      <c r="E280" s="543"/>
-      <c r="F280" s="543"/>
-      <c r="G280" s="544"/>
-      <c r="H280" s="543"/>
-      <c r="I280" s="543"/>
-      <c r="J280" s="543"/>
-      <c r="K280" s="543"/>
+      <c r="B280" s="551"/>
+      <c r="C280" s="552"/>
+      <c r="D280" s="552"/>
+      <c r="E280" s="552"/>
+      <c r="F280" s="552"/>
+      <c r="G280" s="553"/>
+      <c r="H280" s="552"/>
+      <c r="I280" s="552"/>
+      <c r="J280" s="552"/>
+      <c r="K280" s="552"/>
       <c r="L280" s="302"/>
       <c r="M280" s="295"/>
       <c r="N280" s="302"/>
@@ -43988,13 +44001,13 @@
       <c r="C289" s="246" t="s">
         <v>576</v>
       </c>
-      <c r="D289" s="552" t="s">
+      <c r="D289" s="542" t="s">
         <v>2497</v>
       </c>
-      <c r="E289" s="556"/>
-      <c r="F289" s="556"/>
-      <c r="G289" s="556"/>
-      <c r="H289" s="556"/>
+      <c r="E289" s="549"/>
+      <c r="F289" s="549"/>
+      <c r="G289" s="549"/>
+      <c r="H289" s="549"/>
       <c r="I289" s="318"/>
       <c r="J289" s="128"/>
       <c r="K289" s="318"/>
@@ -44118,16 +44131,16 @@
       <c r="A292" s="292" t="s">
         <v>2506</v>
       </c>
-      <c r="B292" s="542"/>
-      <c r="C292" s="543"/>
-      <c r="D292" s="543"/>
-      <c r="E292" s="543"/>
-      <c r="F292" s="543"/>
-      <c r="G292" s="544"/>
-      <c r="H292" s="543"/>
-      <c r="I292" s="543"/>
-      <c r="J292" s="543"/>
-      <c r="K292" s="543"/>
+      <c r="B292" s="551"/>
+      <c r="C292" s="552"/>
+      <c r="D292" s="552"/>
+      <c r="E292" s="552"/>
+      <c r="F292" s="552"/>
+      <c r="G292" s="553"/>
+      <c r="H292" s="552"/>
+      <c r="I292" s="552"/>
+      <c r="J292" s="552"/>
+      <c r="K292" s="552"/>
       <c r="L292" s="302"/>
       <c r="M292" s="295"/>
       <c r="N292" s="302"/>
@@ -44254,16 +44267,16 @@
       <c r="A295" s="292" t="s">
         <v>2518</v>
       </c>
-      <c r="B295" s="542"/>
-      <c r="C295" s="543"/>
-      <c r="D295" s="543"/>
-      <c r="E295" s="543"/>
-      <c r="F295" s="543"/>
-      <c r="G295" s="544"/>
-      <c r="H295" s="543"/>
-      <c r="I295" s="543"/>
-      <c r="J295" s="543"/>
-      <c r="K295" s="543"/>
+      <c r="B295" s="551"/>
+      <c r="C295" s="552"/>
+      <c r="D295" s="552"/>
+      <c r="E295" s="552"/>
+      <c r="F295" s="552"/>
+      <c r="G295" s="553"/>
+      <c r="H295" s="552"/>
+      <c r="I295" s="552"/>
+      <c r="J295" s="552"/>
+      <c r="K295" s="552"/>
       <c r="L295" s="302"/>
       <c r="M295" s="295"/>
       <c r="N295" s="302"/>
@@ -44497,7 +44510,9 @@
       <c r="E300" s="238">
         <v>696</v>
       </c>
-      <c r="F300" s="246"/>
+      <c r="F300" s="590" t="s">
+        <v>5938</v>
+      </c>
       <c r="G300" s="246"/>
       <c r="H300" s="246" t="s">
         <v>2542</v>
@@ -44978,13 +44993,13 @@
       <c r="C312" t="s">
         <v>1867</v>
       </c>
-      <c r="D312" s="552" t="s">
+      <c r="D312" s="542" t="s">
         <v>2597</v>
       </c>
-      <c r="E312" s="545"/>
-      <c r="F312" s="545"/>
-      <c r="G312" s="545"/>
-      <c r="H312" s="545"/>
+      <c r="E312" s="543"/>
+      <c r="F312" s="543"/>
+      <c r="G312" s="543"/>
+      <c r="H312" s="543"/>
       <c r="I312" s="239" t="s">
         <v>1869</v>
       </c>
@@ -45038,39 +45053,31 @@
     </row>
   </sheetData>
   <mergeCells count="77">
-    <mergeCell ref="D312:H312"/>
-    <mergeCell ref="D83:H83"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D93:H93"/>
-    <mergeCell ref="D99:H99"/>
-    <mergeCell ref="D111:H111"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E73:G73"/>
-    <mergeCell ref="D135:H135"/>
-    <mergeCell ref="E117:G117"/>
-    <mergeCell ref="D104:H104"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D219:F219"/>
-    <mergeCell ref="H219:I219"/>
-    <mergeCell ref="J219:K219"/>
-    <mergeCell ref="B295:K295"/>
-    <mergeCell ref="D224:F224"/>
-    <mergeCell ref="H224:I224"/>
-    <mergeCell ref="J224:K224"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="E190:G190"/>
-    <mergeCell ref="D170:H170"/>
-    <mergeCell ref="B274:K274"/>
-    <mergeCell ref="B280:K280"/>
-    <mergeCell ref="B292:K292"/>
-    <mergeCell ref="D184:H184"/>
-    <mergeCell ref="D157:H157"/>
-    <mergeCell ref="D289:H289"/>
-    <mergeCell ref="D218:G218"/>
-    <mergeCell ref="H218:I218"/>
+    <mergeCell ref="D138:H138"/>
+    <mergeCell ref="B139:K139"/>
+    <mergeCell ref="J155:K155"/>
+    <mergeCell ref="L155:M155"/>
+    <mergeCell ref="D156:H156"/>
+    <mergeCell ref="H155:I155"/>
+    <mergeCell ref="D155:G155"/>
+    <mergeCell ref="B196:K196"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D58:H58"/>
+    <mergeCell ref="D63:H63"/>
+    <mergeCell ref="D90:H90"/>
+    <mergeCell ref="D100:H100"/>
+    <mergeCell ref="D126:H126"/>
+    <mergeCell ref="D137:G137"/>
+    <mergeCell ref="D144:H144"/>
+    <mergeCell ref="D149:H149"/>
+    <mergeCell ref="B158:K158"/>
+    <mergeCell ref="D175:H175"/>
+    <mergeCell ref="L174:M174"/>
+    <mergeCell ref="J174:K174"/>
+    <mergeCell ref="H174:I174"/>
+    <mergeCell ref="D174:G174"/>
+    <mergeCell ref="D194:I194"/>
     <mergeCell ref="J218:K218"/>
     <mergeCell ref="B254:K254"/>
     <mergeCell ref="B267:K267"/>
@@ -45087,34 +45094,42 @@
     <mergeCell ref="D223:G223"/>
     <mergeCell ref="H223:I223"/>
     <mergeCell ref="J223:K223"/>
+    <mergeCell ref="J219:K219"/>
+    <mergeCell ref="B295:K295"/>
+    <mergeCell ref="D224:F224"/>
+    <mergeCell ref="H224:I224"/>
+    <mergeCell ref="J224:K224"/>
+    <mergeCell ref="B274:K274"/>
+    <mergeCell ref="B280:K280"/>
+    <mergeCell ref="B292:K292"/>
+    <mergeCell ref="D289:H289"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="D135:H135"/>
+    <mergeCell ref="E117:G117"/>
+    <mergeCell ref="D104:H104"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="B120:K120"/>
+    <mergeCell ref="D312:H312"/>
+    <mergeCell ref="D83:H83"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D93:H93"/>
+    <mergeCell ref="D99:H99"/>
+    <mergeCell ref="D111:H111"/>
+    <mergeCell ref="D219:F219"/>
+    <mergeCell ref="H219:I219"/>
+    <mergeCell ref="E190:G190"/>
+    <mergeCell ref="D170:H170"/>
+    <mergeCell ref="D184:H184"/>
+    <mergeCell ref="D157:H157"/>
+    <mergeCell ref="D218:G218"/>
+    <mergeCell ref="H218:I218"/>
     <mergeCell ref="B176:K176"/>
     <mergeCell ref="D195:H195"/>
-    <mergeCell ref="L174:M174"/>
-    <mergeCell ref="J174:K174"/>
-    <mergeCell ref="H174:I174"/>
-    <mergeCell ref="D174:G174"/>
-    <mergeCell ref="D194:I194"/>
-    <mergeCell ref="D156:H156"/>
-    <mergeCell ref="H155:I155"/>
-    <mergeCell ref="D155:G155"/>
-    <mergeCell ref="B196:K196"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D58:H58"/>
-    <mergeCell ref="D63:H63"/>
-    <mergeCell ref="D90:H90"/>
-    <mergeCell ref="D100:H100"/>
-    <mergeCell ref="D126:H126"/>
-    <mergeCell ref="D137:G137"/>
-    <mergeCell ref="D144:H144"/>
-    <mergeCell ref="D149:H149"/>
-    <mergeCell ref="B158:K158"/>
-    <mergeCell ref="D175:H175"/>
-    <mergeCell ref="B120:K120"/>
-    <mergeCell ref="D138:H138"/>
-    <mergeCell ref="B139:K139"/>
-    <mergeCell ref="J155:K155"/>
-    <mergeCell ref="L155:M155"/>
   </mergeCells>
   <phoneticPr fontId="73" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -45168,18 +45183,18 @@
       <c r="A2" s="292" t="s">
         <v>311</v>
       </c>
-      <c r="B2" s="555" t="s">
+      <c r="B2" s="554" t="s">
         <v>2605</v>
       </c>
-      <c r="C2" s="549"/>
-      <c r="D2" s="549"/>
-      <c r="E2" s="549"/>
-      <c r="F2" s="549"/>
-      <c r="G2" s="544"/>
-      <c r="H2" s="549"/>
-      <c r="I2" s="549"/>
-      <c r="J2" s="549"/>
-      <c r="K2" s="550"/>
+      <c r="C2" s="545"/>
+      <c r="D2" s="545"/>
+      <c r="E2" s="545"/>
+      <c r="F2" s="545"/>
+      <c r="G2" s="553"/>
+      <c r="H2" s="545"/>
+      <c r="I2" s="545"/>
+      <c r="J2" s="545"/>
+      <c r="K2" s="546"/>
       <c r="M2" s="295"/>
     </row>
     <row r="3" spans="1:33" ht="56.25" customHeight="1">
@@ -45585,10 +45600,10 @@
       <c r="D16" s="548" t="s">
         <v>2690</v>
       </c>
-      <c r="E16" s="549"/>
-      <c r="F16" s="549"/>
-      <c r="G16" s="545"/>
-      <c r="H16" s="550"/>
+      <c r="E16" s="545"/>
+      <c r="F16" s="545"/>
+      <c r="G16" s="543"/>
+      <c r="H16" s="546"/>
       <c r="I16" s="239" t="s">
         <v>2691</v>
       </c>
@@ -45602,10 +45617,10 @@
       <c r="D17" s="548" t="s">
         <v>1128</v>
       </c>
-      <c r="E17" s="549"/>
-      <c r="F17" s="549"/>
-      <c r="G17" s="545"/>
-      <c r="H17" s="550"/>
+      <c r="E17" s="545"/>
+      <c r="F17" s="545"/>
+      <c r="G17" s="543"/>
+      <c r="H17" s="546"/>
       <c r="I17" s="239" t="s">
         <v>1129</v>
       </c>
@@ -45619,10 +45634,10 @@
       <c r="D18" s="548" t="s">
         <v>1161</v>
       </c>
-      <c r="E18" s="549"/>
-      <c r="F18" s="549"/>
-      <c r="G18" s="545"/>
-      <c r="H18" s="550"/>
+      <c r="E18" s="545"/>
+      <c r="F18" s="545"/>
+      <c r="G18" s="543"/>
+      <c r="H18" s="546"/>
       <c r="I18" s="239" t="s">
         <v>1162</v>
       </c>
@@ -45633,13 +45648,13 @@
       <c r="C19" t="s">
         <v>630</v>
       </c>
-      <c r="D19" s="552" t="s">
+      <c r="D19" s="542" t="s">
         <v>2692</v>
       </c>
-      <c r="E19" s="557"/>
-      <c r="F19" s="557"/>
-      <c r="G19" s="557"/>
-      <c r="H19" s="557"/>
+      <c r="E19" s="550"/>
+      <c r="F19" s="550"/>
+      <c r="G19" s="550"/>
+      <c r="H19" s="550"/>
       <c r="I19" s="249" t="s">
         <v>2693</v>
       </c>
@@ -45655,10 +45670,10 @@
       <c r="D20" s="548" t="s">
         <v>1333</v>
       </c>
-      <c r="E20" s="549"/>
-      <c r="F20" s="549"/>
-      <c r="G20" s="545"/>
-      <c r="H20" s="550"/>
+      <c r="E20" s="545"/>
+      <c r="F20" s="545"/>
+      <c r="G20" s="543"/>
+      <c r="H20" s="546"/>
       <c r="I20" s="249" t="s">
         <v>2694</v>
       </c>
@@ -45694,10 +45709,10 @@
       <c r="D21" s="548" t="s">
         <v>2695</v>
       </c>
-      <c r="E21" s="549"/>
-      <c r="F21" s="549"/>
-      <c r="G21" s="545"/>
-      <c r="H21" s="550"/>
+      <c r="E21" s="545"/>
+      <c r="F21" s="545"/>
+      <c r="G21" s="543"/>
+      <c r="H21" s="546"/>
       <c r="I21" s="249" t="s">
         <v>2696</v>
       </c>
@@ -45730,13 +45745,13 @@
       <c r="C22" t="s">
         <v>672</v>
       </c>
-      <c r="D22" s="559" t="s">
+      <c r="D22" s="566" t="s">
         <v>1650</v>
       </c>
-      <c r="E22" s="549"/>
-      <c r="F22" s="549"/>
-      <c r="G22" s="545"/>
-      <c r="H22" s="550"/>
+      <c r="E22" s="545"/>
+      <c r="F22" s="545"/>
+      <c r="G22" s="543"/>
+      <c r="H22" s="546"/>
       <c r="I22" s="249" t="s">
         <v>2697</v>
       </c>
@@ -45767,18 +45782,18 @@
       <c r="A23" s="292" t="s">
         <v>312</v>
       </c>
-      <c r="B23" s="555" t="s">
+      <c r="B23" s="554" t="s">
         <v>2698</v>
       </c>
-      <c r="C23" s="549"/>
-      <c r="D23" s="549"/>
-      <c r="E23" s="549"/>
-      <c r="F23" s="549"/>
-      <c r="G23" s="544"/>
-      <c r="H23" s="549"/>
-      <c r="I23" s="549"/>
-      <c r="J23" s="549"/>
-      <c r="K23" s="550"/>
+      <c r="C23" s="545"/>
+      <c r="D23" s="545"/>
+      <c r="E23" s="545"/>
+      <c r="F23" s="545"/>
+      <c r="G23" s="553"/>
+      <c r="H23" s="545"/>
+      <c r="I23" s="545"/>
+      <c r="J23" s="545"/>
+      <c r="K23" s="546"/>
       <c r="L23" s="302"/>
       <c r="M23" s="295"/>
       <c r="N23" s="330"/>
@@ -46436,22 +46451,22 @@
       <c r="C37" t="s">
         <v>2783</v>
       </c>
-      <c r="D37" s="565"/>
-      <c r="E37" s="549"/>
-      <c r="F37" s="549"/>
-      <c r="G37" s="550"/>
-      <c r="H37" s="563" t="s">
+      <c r="D37" s="564"/>
+      <c r="E37" s="545"/>
+      <c r="F37" s="545"/>
+      <c r="G37" s="546"/>
+      <c r="H37" s="561" t="s">
         <v>2784</v>
       </c>
-      <c r="I37" s="550"/>
-      <c r="J37" s="546" t="s">
+      <c r="I37" s="546"/>
+      <c r="J37" s="557" t="s">
         <v>2785</v>
       </c>
-      <c r="K37" s="550"/>
-      <c r="L37" s="546" t="s">
+      <c r="K37" s="546"/>
+      <c r="L37" s="557" t="s">
         <v>2786</v>
       </c>
-      <c r="M37" s="550"/>
+      <c r="M37" s="546"/>
       <c r="N37" s="63"/>
       <c r="O37" s="63"/>
       <c r="P37" s="63"/>
@@ -46484,10 +46499,10 @@
       <c r="D38" s="548" t="s">
         <v>2788</v>
       </c>
-      <c r="E38" s="549"/>
-      <c r="F38" s="549"/>
-      <c r="G38" s="545"/>
-      <c r="H38" s="550"/>
+      <c r="E38" s="545"/>
+      <c r="F38" s="545"/>
+      <c r="G38" s="543"/>
+      <c r="H38" s="546"/>
       <c r="I38" s="239" t="s">
         <v>2789</v>
       </c>
@@ -46500,13 +46515,13 @@
       <c r="C39" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="551" t="s">
+      <c r="D39" s="544" t="s">
         <v>2790</v>
       </c>
-      <c r="E39" s="549"/>
-      <c r="F39" s="549"/>
-      <c r="G39" s="545"/>
-      <c r="H39" s="550"/>
+      <c r="E39" s="545"/>
+      <c r="F39" s="545"/>
+      <c r="G39" s="543"/>
+      <c r="H39" s="546"/>
       <c r="M39" s="267"/>
       <c r="N39" s="63"/>
       <c r="O39" s="63"/>
@@ -46535,13 +46550,13 @@
       <c r="C40" t="s">
         <v>81</v>
       </c>
-      <c r="D40" s="551" t="s">
+      <c r="D40" s="544" t="s">
         <v>2791</v>
       </c>
-      <c r="E40" s="549"/>
-      <c r="F40" s="549"/>
-      <c r="G40" s="545"/>
-      <c r="H40" s="550"/>
+      <c r="E40" s="545"/>
+      <c r="F40" s="545"/>
+      <c r="G40" s="543"/>
+      <c r="H40" s="546"/>
       <c r="M40" s="267"/>
       <c r="N40" s="63"/>
       <c r="O40" s="63"/>
@@ -46570,13 +46585,13 @@
       <c r="C41" t="s">
         <v>631</v>
       </c>
-      <c r="D41" s="551" t="s">
+      <c r="D41" s="544" t="s">
         <v>1936</v>
       </c>
-      <c r="E41" s="549"/>
-      <c r="F41" s="549"/>
-      <c r="G41" s="549"/>
-      <c r="H41" s="550"/>
+      <c r="E41" s="545"/>
+      <c r="F41" s="545"/>
+      <c r="G41" s="545"/>
+      <c r="H41" s="546"/>
       <c r="I41" s="249"/>
       <c r="K41" s="249"/>
       <c r="M41" s="249"/>
@@ -46587,13 +46602,13 @@
       <c r="C42" t="s">
         <v>128</v>
       </c>
-      <c r="D42" s="561" t="s">
+      <c r="D42" s="559" t="s">
         <v>2792</v>
       </c>
-      <c r="E42" s="549"/>
-      <c r="F42" s="549"/>
-      <c r="G42" s="549"/>
-      <c r="H42" s="550"/>
+      <c r="E42" s="545"/>
+      <c r="F42" s="545"/>
+      <c r="G42" s="545"/>
+      <c r="H42" s="546"/>
       <c r="I42" s="249"/>
       <c r="K42" s="249"/>
       <c r="M42" s="249"/>
@@ -46624,13 +46639,13 @@
       <c r="C43" t="s">
         <v>663</v>
       </c>
-      <c r="D43" s="551" t="s">
+      <c r="D43" s="544" t="s">
         <v>2793</v>
       </c>
-      <c r="E43" s="549"/>
-      <c r="F43" s="549"/>
-      <c r="G43" s="545"/>
-      <c r="H43" s="550"/>
+      <c r="E43" s="545"/>
+      <c r="F43" s="545"/>
+      <c r="G43" s="543"/>
+      <c r="H43" s="546"/>
       <c r="I43" s="249"/>
       <c r="K43" s="249"/>
       <c r="M43" s="249"/>
@@ -46661,13 +46676,13 @@
       <c r="C44" t="s">
         <v>129</v>
       </c>
-      <c r="D44" s="560" t="s">
+      <c r="D44" s="565" t="s">
         <v>2794</v>
       </c>
-      <c r="E44" s="549"/>
-      <c r="F44" s="549"/>
-      <c r="G44" s="545"/>
-      <c r="H44" s="550"/>
+      <c r="E44" s="545"/>
+      <c r="F44" s="545"/>
+      <c r="G44" s="543"/>
+      <c r="H44" s="546"/>
       <c r="I44" s="249"/>
       <c r="K44" s="249"/>
       <c r="M44" s="249"/>
@@ -46696,18 +46711,18 @@
       <c r="A45" s="292" t="s">
         <v>313</v>
       </c>
-      <c r="B45" s="555" t="s">
+      <c r="B45" s="554" t="s">
         <v>2795</v>
       </c>
-      <c r="C45" s="549"/>
-      <c r="D45" s="549"/>
-      <c r="E45" s="549"/>
-      <c r="F45" s="549"/>
-      <c r="G45" s="544"/>
-      <c r="H45" s="549"/>
-      <c r="I45" s="549"/>
-      <c r="J45" s="549"/>
-      <c r="K45" s="550"/>
+      <c r="C45" s="545"/>
+      <c r="D45" s="545"/>
+      <c r="E45" s="545"/>
+      <c r="F45" s="545"/>
+      <c r="G45" s="553"/>
+      <c r="H45" s="545"/>
+      <c r="I45" s="545"/>
+      <c r="J45" s="545"/>
+      <c r="K45" s="546"/>
       <c r="L45" s="302"/>
       <c r="M45" s="295"/>
       <c r="N45" s="330"/>
@@ -46796,18 +46811,18 @@
       <c r="C47" t="s">
         <v>2805</v>
       </c>
-      <c r="D47" s="561"/>
-      <c r="E47" s="549"/>
-      <c r="F47" s="549"/>
-      <c r="G47" s="550"/>
-      <c r="H47" s="564" t="s">
+      <c r="D47" s="559"/>
+      <c r="E47" s="545"/>
+      <c r="F47" s="545"/>
+      <c r="G47" s="546"/>
+      <c r="H47" s="563" t="s">
         <v>2806</v>
       </c>
-      <c r="I47" s="549"/>
-      <c r="J47" s="549"/>
-      <c r="K47" s="549"/>
-      <c r="L47" s="549"/>
-      <c r="M47" s="550"/>
+      <c r="I47" s="545"/>
+      <c r="J47" s="545"/>
+      <c r="K47" s="545"/>
+      <c r="L47" s="545"/>
+      <c r="M47" s="546"/>
       <c r="N47" s="128"/>
       <c r="O47" s="128"/>
       <c r="P47" s="128"/>
@@ -46840,10 +46855,10 @@
       <c r="D48" s="548" t="s">
         <v>2808</v>
       </c>
-      <c r="E48" s="549"/>
-      <c r="F48" s="549"/>
-      <c r="G48" s="545"/>
-      <c r="H48" s="550"/>
+      <c r="E48" s="545"/>
+      <c r="F48" s="545"/>
+      <c r="G48" s="543"/>
+      <c r="H48" s="546"/>
       <c r="I48" s="239" t="s">
         <v>2809</v>
       </c>
@@ -46986,18 +47001,18 @@
       <c r="C51" t="s">
         <v>2825</v>
       </c>
-      <c r="D51" s="545"/>
-      <c r="E51" s="549"/>
-      <c r="F51" s="549"/>
-      <c r="G51" s="550"/>
-      <c r="H51" s="561" t="s">
+      <c r="D51" s="543"/>
+      <c r="E51" s="545"/>
+      <c r="F51" s="545"/>
+      <c r="G51" s="546"/>
+      <c r="H51" s="559" t="s">
         <v>2826</v>
       </c>
-      <c r="I51" s="549"/>
-      <c r="J51" s="549"/>
-      <c r="K51" s="549"/>
-      <c r="L51" s="549"/>
-      <c r="M51" s="550"/>
+      <c r="I51" s="545"/>
+      <c r="J51" s="545"/>
+      <c r="K51" s="545"/>
+      <c r="L51" s="545"/>
+      <c r="M51" s="546"/>
       <c r="N51" s="128"/>
       <c r="O51" s="128"/>
       <c r="P51" s="128"/>
@@ -47030,10 +47045,10 @@
       <c r="D52" s="548" t="s">
         <v>2827</v>
       </c>
-      <c r="E52" s="549"/>
-      <c r="F52" s="549"/>
-      <c r="G52" s="545"/>
-      <c r="H52" s="550"/>
+      <c r="E52" s="545"/>
+      <c r="F52" s="545"/>
+      <c r="G52" s="543"/>
+      <c r="H52" s="546"/>
       <c r="I52" s="239" t="s">
         <v>2828</v>
       </c>
@@ -47176,22 +47191,22 @@
       <c r="C55" t="s">
         <v>2844</v>
       </c>
-      <c r="D55" s="563"/>
-      <c r="E55" s="549"/>
-      <c r="F55" s="549"/>
-      <c r="G55" s="550"/>
-      <c r="H55" s="561" t="s">
+      <c r="D55" s="561"/>
+      <c r="E55" s="545"/>
+      <c r="F55" s="545"/>
+      <c r="G55" s="546"/>
+      <c r="H55" s="559" t="s">
         <v>2845</v>
       </c>
-      <c r="I55" s="552"/>
+      <c r="I55" s="542"/>
       <c r="J55" s="562" t="s">
         <v>2846</v>
       </c>
-      <c r="K55" s="552"/>
-      <c r="L55" s="552" t="s">
+      <c r="K55" s="542"/>
+      <c r="L55" s="542" t="s">
         <v>2847</v>
       </c>
-      <c r="M55" s="552"/>
+      <c r="M55" s="542"/>
       <c r="N55" s="128"/>
       <c r="O55" s="128"/>
       <c r="P55" s="128"/>
@@ -47224,10 +47239,10 @@
       <c r="D56" s="548" t="s">
         <v>2848</v>
       </c>
-      <c r="E56" s="549"/>
-      <c r="F56" s="549"/>
-      <c r="G56" s="545"/>
-      <c r="H56" s="550"/>
+      <c r="E56" s="545"/>
+      <c r="F56" s="545"/>
+      <c r="G56" s="543"/>
+      <c r="H56" s="546"/>
       <c r="I56" s="239" t="s">
         <v>2849</v>
       </c>
@@ -47367,22 +47382,22 @@
       <c r="C59" t="s">
         <v>2863</v>
       </c>
-      <c r="D59" s="563"/>
-      <c r="E59" s="549"/>
-      <c r="F59" s="549"/>
-      <c r="G59" s="550"/>
-      <c r="H59" s="561" t="s">
+      <c r="D59" s="561"/>
+      <c r="E59" s="545"/>
+      <c r="F59" s="545"/>
+      <c r="G59" s="546"/>
+      <c r="H59" s="559" t="s">
         <v>2864</v>
       </c>
-      <c r="I59" s="566"/>
+      <c r="I59" s="560"/>
       <c r="J59" s="562" t="s">
         <v>2865</v>
       </c>
-      <c r="K59" s="566"/>
-      <c r="L59" s="552" t="s">
+      <c r="K59" s="560"/>
+      <c r="L59" s="542" t="s">
         <v>2866</v>
       </c>
-      <c r="M59" s="566"/>
+      <c r="M59" s="560"/>
       <c r="N59" s="128"/>
       <c r="O59" s="128"/>
       <c r="P59" s="128"/>
@@ -47415,10 +47430,10 @@
       <c r="D60" s="548" t="s">
         <v>2867</v>
       </c>
-      <c r="E60" s="549"/>
-      <c r="F60" s="549"/>
-      <c r="G60" s="545"/>
-      <c r="H60" s="550"/>
+      <c r="E60" s="545"/>
+      <c r="F60" s="545"/>
+      <c r="G60" s="543"/>
+      <c r="H60" s="546"/>
       <c r="I60" s="239" t="s">
         <v>2868</v>
       </c>
@@ -47562,20 +47577,20 @@
       <c r="C63" t="s">
         <v>2884</v>
       </c>
-      <c r="D63" s="563"/>
-      <c r="E63" s="549"/>
-      <c r="F63" s="549"/>
-      <c r="G63" s="550"/>
-      <c r="H63" s="561" t="s">
+      <c r="D63" s="561"/>
+      <c r="E63" s="545"/>
+      <c r="F63" s="545"/>
+      <c r="G63" s="546"/>
+      <c r="H63" s="559" t="s">
         <v>2885</v>
       </c>
-      <c r="I63" s="566"/>
+      <c r="I63" s="560"/>
       <c r="J63" s="562" t="s">
         <v>2886</v>
       </c>
-      <c r="K63" s="566"/>
-      <c r="L63" s="552"/>
-      <c r="M63" s="566"/>
+      <c r="K63" s="560"/>
+      <c r="L63" s="542"/>
+      <c r="M63" s="560"/>
       <c r="N63" s="128"/>
       <c r="O63" s="128"/>
       <c r="P63" s="128"/>
@@ -47608,10 +47623,10 @@
       <c r="D64" s="548" t="s">
         <v>2888</v>
       </c>
-      <c r="E64" s="549"/>
-      <c r="F64" s="549"/>
-      <c r="G64" s="545"/>
-      <c r="H64" s="550"/>
+      <c r="E64" s="545"/>
+      <c r="F64" s="545"/>
+      <c r="G64" s="543"/>
+      <c r="H64" s="546"/>
       <c r="I64" s="239" t="s">
         <v>2889</v>
       </c>
@@ -47753,22 +47768,22 @@
       <c r="C67" t="s">
         <v>2904</v>
       </c>
-      <c r="D67" s="563"/>
-      <c r="E67" s="549"/>
-      <c r="F67" s="549"/>
-      <c r="G67" s="550"/>
-      <c r="H67" s="561" t="s">
+      <c r="D67" s="561"/>
+      <c r="E67" s="545"/>
+      <c r="F67" s="545"/>
+      <c r="G67" s="546"/>
+      <c r="H67" s="559" t="s">
         <v>2905</v>
       </c>
-      <c r="I67" s="566"/>
+      <c r="I67" s="560"/>
       <c r="J67" s="562" t="s">
         <v>2906</v>
       </c>
-      <c r="K67" s="566"/>
-      <c r="L67" s="552" t="s">
+      <c r="K67" s="560"/>
+      <c r="L67" s="542" t="s">
         <v>2907</v>
       </c>
-      <c r="M67" s="566"/>
+      <c r="M67" s="560"/>
       <c r="N67" s="128"/>
       <c r="O67" s="128"/>
       <c r="P67" s="128"/>
@@ -47801,10 +47816,10 @@
       <c r="D68" s="548" t="s">
         <v>2909</v>
       </c>
-      <c r="E68" s="549"/>
-      <c r="F68" s="549"/>
-      <c r="G68" s="545"/>
-      <c r="H68" s="550"/>
+      <c r="E68" s="545"/>
+      <c r="F68" s="545"/>
+      <c r="G68" s="543"/>
+      <c r="H68" s="546"/>
       <c r="I68" s="239" t="s">
         <v>2910</v>
       </c>
@@ -47950,18 +47965,18 @@
       <c r="C71" t="s">
         <v>2927</v>
       </c>
-      <c r="D71" s="563"/>
-      <c r="E71" s="549"/>
-      <c r="F71" s="549"/>
-      <c r="G71" s="550"/>
-      <c r="H71" s="561" t="s">
+      <c r="D71" s="561"/>
+      <c r="E71" s="545"/>
+      <c r="F71" s="545"/>
+      <c r="G71" s="546"/>
+      <c r="H71" s="559" t="s">
         <v>2928</v>
       </c>
-      <c r="I71" s="566"/>
+      <c r="I71" s="560"/>
       <c r="J71" s="562" t="s">
         <v>2929</v>
       </c>
-      <c r="K71" s="566"/>
+      <c r="K71" s="560"/>
       <c r="L71" s="332"/>
       <c r="M71" s="333"/>
       <c r="N71" s="128"/>
@@ -47996,10 +48011,10 @@
       <c r="D72" s="548" t="s">
         <v>2931</v>
       </c>
-      <c r="E72" s="549"/>
-      <c r="F72" s="549"/>
-      <c r="G72" s="545"/>
-      <c r="H72" s="550"/>
+      <c r="E72" s="545"/>
+      <c r="F72" s="545"/>
+      <c r="G72" s="543"/>
+      <c r="H72" s="546"/>
       <c r="I72" s="239" t="s">
         <v>2932</v>
       </c>
@@ -48032,18 +48047,18 @@
       <c r="A73" s="292" t="s">
         <v>10</v>
       </c>
-      <c r="B73" s="555" t="s">
+      <c r="B73" s="554" t="s">
         <v>2933</v>
       </c>
-      <c r="C73" s="549"/>
-      <c r="D73" s="549"/>
-      <c r="E73" s="549"/>
-      <c r="F73" s="549"/>
-      <c r="G73" s="544"/>
-      <c r="H73" s="549"/>
-      <c r="I73" s="549"/>
-      <c r="J73" s="549"/>
-      <c r="K73" s="550"/>
+      <c r="C73" s="545"/>
+      <c r="D73" s="545"/>
+      <c r="E73" s="545"/>
+      <c r="F73" s="545"/>
+      <c r="G73" s="553"/>
+      <c r="H73" s="545"/>
+      <c r="I73" s="545"/>
+      <c r="J73" s="545"/>
+      <c r="K73" s="546"/>
       <c r="L73" s="302"/>
       <c r="M73" s="295"/>
       <c r="N73" s="330"/>
@@ -48677,10 +48692,10 @@
         <v>105</v>
       </c>
       <c r="D95" s="548"/>
-      <c r="E95" s="549"/>
-      <c r="F95" s="549"/>
-      <c r="G95" s="545"/>
-      <c r="H95" s="550"/>
+      <c r="E95" s="545"/>
+      <c r="F95" s="545"/>
+      <c r="G95" s="543"/>
+      <c r="H95" s="546"/>
       <c r="I95" s="239" t="s">
         <v>1254</v>
       </c>
@@ -48714,11 +48729,11 @@
       <c r="C96" t="s">
         <v>144</v>
       </c>
-      <c r="D96" s="551"/>
-      <c r="E96" s="549"/>
-      <c r="F96" s="549"/>
-      <c r="G96" s="545"/>
-      <c r="H96" s="550"/>
+      <c r="D96" s="544"/>
+      <c r="E96" s="545"/>
+      <c r="F96" s="545"/>
+      <c r="G96" s="543"/>
+      <c r="H96" s="546"/>
       <c r="I96" s="239" t="s">
         <v>3072</v>
       </c>
@@ -48755,10 +48770,10 @@
       <c r="D97" s="548" t="s">
         <v>1765</v>
       </c>
-      <c r="E97" s="549"/>
-      <c r="F97" s="549"/>
-      <c r="G97" s="549"/>
-      <c r="H97" s="550"/>
+      <c r="E97" s="545"/>
+      <c r="F97" s="545"/>
+      <c r="G97" s="545"/>
+      <c r="H97" s="546"/>
       <c r="I97" s="239" t="s">
         <v>3073</v>
       </c>
@@ -48793,13 +48808,13 @@
       <c r="C98" t="s">
         <v>125</v>
       </c>
-      <c r="D98" s="552" t="s">
+      <c r="D98" s="542" t="s">
         <v>1809</v>
       </c>
-      <c r="E98" s="545"/>
-      <c r="F98" s="545"/>
-      <c r="G98" s="545"/>
-      <c r="H98" s="545"/>
+      <c r="E98" s="543"/>
+      <c r="F98" s="543"/>
+      <c r="G98" s="543"/>
+      <c r="H98" s="543"/>
       <c r="I98" s="249" t="s">
         <v>1477</v>
       </c>
@@ -49077,22 +49092,22 @@
       <c r="C108" t="s">
         <v>3121</v>
       </c>
-      <c r="D108" s="563"/>
-      <c r="E108" s="549"/>
-      <c r="F108" s="549"/>
-      <c r="G108" s="550"/>
-      <c r="H108" s="561" t="s">
+      <c r="D108" s="561"/>
+      <c r="E108" s="545"/>
+      <c r="F108" s="545"/>
+      <c r="G108" s="546"/>
+      <c r="H108" s="559" t="s">
         <v>3122</v>
       </c>
-      <c r="I108" s="566"/>
+      <c r="I108" s="560"/>
       <c r="J108" s="562" t="s">
         <v>3123</v>
       </c>
-      <c r="K108" s="566"/>
-      <c r="L108" s="552" t="s">
+      <c r="K108" s="560"/>
+      <c r="L108" s="542" t="s">
         <v>3124</v>
       </c>
-      <c r="M108" s="566"/>
+      <c r="M108" s="560"/>
       <c r="N108" s="128"/>
       <c r="O108" s="128"/>
       <c r="P108" s="128"/>
@@ -49125,10 +49140,10 @@
       <c r="D109" s="548" t="s">
         <v>3126</v>
       </c>
-      <c r="E109" s="549"/>
-      <c r="F109" s="549"/>
-      <c r="G109" s="545"/>
-      <c r="H109" s="550"/>
+      <c r="E109" s="545"/>
+      <c r="F109" s="545"/>
+      <c r="G109" s="543"/>
+      <c r="H109" s="546"/>
       <c r="I109" s="239" t="s">
         <v>3127</v>
       </c>
@@ -49159,6 +49174,51 @@
     </row>
   </sheetData>
   <mergeCells count="61">
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="B23:K23"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="B45:K45"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="D47:G47"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="D60:H60"/>
+    <mergeCell ref="D56:H56"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="D68:H68"/>
+    <mergeCell ref="D63:G63"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="J63:K63"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="D64:H64"/>
+    <mergeCell ref="J108:K108"/>
+    <mergeCell ref="L108:M108"/>
+    <mergeCell ref="D71:G71"/>
+    <mergeCell ref="D72:H72"/>
+    <mergeCell ref="B73:K73"/>
+    <mergeCell ref="D95:H95"/>
+    <mergeCell ref="D96:H96"/>
+    <mergeCell ref="J71:K71"/>
     <mergeCell ref="D109:H109"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="D41:H41"/>
@@ -49167,59 +49227,14 @@
     <mergeCell ref="D97:H97"/>
     <mergeCell ref="D108:G108"/>
     <mergeCell ref="H108:I108"/>
-    <mergeCell ref="J108:K108"/>
-    <mergeCell ref="L108:M108"/>
-    <mergeCell ref="D71:G71"/>
-    <mergeCell ref="D72:H72"/>
-    <mergeCell ref="B73:K73"/>
-    <mergeCell ref="D95:H95"/>
-    <mergeCell ref="D96:H96"/>
-    <mergeCell ref="J71:K71"/>
     <mergeCell ref="D67:G67"/>
     <mergeCell ref="H67:I67"/>
-    <mergeCell ref="J67:K67"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="D68:H68"/>
-    <mergeCell ref="D63:G63"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="J63:K63"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="D64:H64"/>
     <mergeCell ref="D59:G59"/>
     <mergeCell ref="H59:I59"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="D60:H60"/>
-    <mergeCell ref="D56:H56"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="H55:I55"/>
     <mergeCell ref="H51:M51"/>
-    <mergeCell ref="D55:G55"/>
     <mergeCell ref="D51:G51"/>
     <mergeCell ref="L37:M37"/>
     <mergeCell ref="D38:H38"/>
-    <mergeCell ref="B45:K45"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="D47:G47"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="B23:K23"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D22:H22"/>
   </mergeCells>
   <phoneticPr fontId="73" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -49273,14 +49288,14 @@
       <c r="A2" s="292" t="s">
         <v>3128</v>
       </c>
-      <c r="B2" s="555" t="s">
+      <c r="B2" s="554" t="s">
         <v>3129</v>
       </c>
-      <c r="C2" s="549"/>
-      <c r="D2" s="549"/>
-      <c r="E2" s="549"/>
-      <c r="F2" s="549"/>
-      <c r="G2" s="550"/>
+      <c r="C2" s="545"/>
+      <c r="D2" s="545"/>
+      <c r="E2" s="545"/>
+      <c r="F2" s="545"/>
+      <c r="G2" s="546"/>
       <c r="M2" s="295"/>
     </row>
     <row r="3" spans="1:33" ht="56.25" customHeight="1">
@@ -49290,18 +49305,18 @@
       <c r="B3" s="337" t="s">
         <v>3131</v>
       </c>
-      <c r="C3" s="570" t="s">
+      <c r="C3" s="567" t="s">
         <v>3132</v>
       </c>
-      <c r="D3" s="549"/>
-      <c r="E3" s="549"/>
-      <c r="F3" s="549"/>
-      <c r="G3" s="549"/>
-      <c r="H3" s="549"/>
-      <c r="I3" s="549"/>
-      <c r="J3" s="549"/>
-      <c r="K3" s="549"/>
-      <c r="L3" s="550"/>
+      <c r="D3" s="545"/>
+      <c r="E3" s="545"/>
+      <c r="F3" s="545"/>
+      <c r="G3" s="545"/>
+      <c r="H3" s="545"/>
+      <c r="I3" s="545"/>
+      <c r="J3" s="545"/>
+      <c r="K3" s="545"/>
+      <c r="L3" s="546"/>
       <c r="M3" s="338"/>
       <c r="Y3" s="337"/>
       <c r="Z3" s="337"/>
@@ -49320,18 +49335,18 @@
       <c r="B4" s="337" t="s">
         <v>3134</v>
       </c>
-      <c r="C4" s="570" t="s">
+      <c r="C4" s="567" t="s">
         <v>3135</v>
       </c>
-      <c r="D4" s="549"/>
-      <c r="E4" s="549"/>
-      <c r="F4" s="549"/>
-      <c r="G4" s="549"/>
-      <c r="H4" s="549"/>
-      <c r="I4" s="549"/>
-      <c r="J4" s="549"/>
-      <c r="K4" s="549"/>
-      <c r="L4" s="550"/>
+      <c r="D4" s="545"/>
+      <c r="E4" s="545"/>
+      <c r="F4" s="545"/>
+      <c r="G4" s="545"/>
+      <c r="H4" s="545"/>
+      <c r="I4" s="545"/>
+      <c r="J4" s="545"/>
+      <c r="K4" s="545"/>
+      <c r="L4" s="546"/>
       <c r="M4" s="338"/>
       <c r="Y4" s="337"/>
       <c r="Z4" s="337"/>
@@ -49406,18 +49421,18 @@
       <c r="B7" s="337" t="s">
         <v>3149</v>
       </c>
-      <c r="C7" s="570" t="s">
+      <c r="C7" s="567" t="s">
         <v>3150</v>
       </c>
-      <c r="D7" s="549"/>
-      <c r="E7" s="549"/>
-      <c r="F7" s="549"/>
-      <c r="G7" s="549"/>
-      <c r="H7" s="549"/>
-      <c r="I7" s="549"/>
-      <c r="J7" s="549"/>
-      <c r="K7" s="549"/>
-      <c r="L7" s="550"/>
+      <c r="D7" s="545"/>
+      <c r="E7" s="545"/>
+      <c r="F7" s="545"/>
+      <c r="G7" s="545"/>
+      <c r="H7" s="545"/>
+      <c r="I7" s="545"/>
+      <c r="J7" s="545"/>
+      <c r="K7" s="545"/>
+      <c r="L7" s="546"/>
       <c r="M7" s="338"/>
       <c r="N7" s="337"/>
       <c r="O7" s="337"/>
@@ -49537,18 +49552,18 @@
       <c r="B11" s="337" t="s">
         <v>3170</v>
       </c>
-      <c r="C11" s="570" t="s">
+      <c r="C11" s="567" t="s">
         <v>3171</v>
       </c>
-      <c r="D11" s="549"/>
-      <c r="E11" s="549"/>
-      <c r="F11" s="549"/>
-      <c r="G11" s="549"/>
-      <c r="H11" s="549"/>
-      <c r="I11" s="549"/>
-      <c r="J11" s="549"/>
-      <c r="K11" s="549"/>
-      <c r="L11" s="550"/>
+      <c r="D11" s="545"/>
+      <c r="E11" s="545"/>
+      <c r="F11" s="545"/>
+      <c r="G11" s="545"/>
+      <c r="H11" s="545"/>
+      <c r="I11" s="545"/>
+      <c r="J11" s="545"/>
+      <c r="K11" s="545"/>
+      <c r="L11" s="546"/>
       <c r="M11" s="338"/>
       <c r="N11" s="337"/>
       <c r="O11" s="337"/>
@@ -49782,18 +49797,18 @@
       <c r="B16" s="337" t="s">
         <v>3195</v>
       </c>
-      <c r="C16" s="570" t="s">
+      <c r="C16" s="567" t="s">
         <v>3196</v>
       </c>
-      <c r="D16" s="549"/>
-      <c r="E16" s="549"/>
-      <c r="F16" s="549"/>
-      <c r="G16" s="549"/>
-      <c r="H16" s="549"/>
-      <c r="I16" s="549"/>
-      <c r="J16" s="549"/>
-      <c r="K16" s="549"/>
-      <c r="L16" s="550"/>
+      <c r="D16" s="545"/>
+      <c r="E16" s="545"/>
+      <c r="F16" s="545"/>
+      <c r="G16" s="545"/>
+      <c r="H16" s="545"/>
+      <c r="I16" s="545"/>
+      <c r="J16" s="545"/>
+      <c r="K16" s="545"/>
+      <c r="L16" s="546"/>
       <c r="M16" s="338"/>
       <c r="Y16" s="337"/>
       <c r="Z16" s="337"/>
@@ -49930,18 +49945,18 @@
       <c r="B21" s="337" t="s">
         <v>3222</v>
       </c>
-      <c r="C21" s="570" t="s">
+      <c r="C21" s="567" t="s">
         <v>3223</v>
       </c>
-      <c r="D21" s="549"/>
-      <c r="E21" s="549"/>
-      <c r="F21" s="549"/>
-      <c r="G21" s="549"/>
-      <c r="H21" s="549"/>
-      <c r="I21" s="549"/>
-      <c r="J21" s="549"/>
-      <c r="K21" s="549"/>
-      <c r="L21" s="550"/>
+      <c r="D21" s="545"/>
+      <c r="E21" s="545"/>
+      <c r="F21" s="545"/>
+      <c r="G21" s="545"/>
+      <c r="H21" s="545"/>
+      <c r="I21" s="545"/>
+      <c r="J21" s="545"/>
+      <c r="K21" s="545"/>
+      <c r="L21" s="546"/>
       <c r="M21" s="338"/>
       <c r="Y21" s="337"/>
       <c r="Z21" s="337"/>
@@ -50026,18 +50041,18 @@
       <c r="B24" s="337" t="s">
         <v>3239</v>
       </c>
-      <c r="C24" s="570" t="s">
+      <c r="C24" s="567" t="s">
         <v>3240</v>
       </c>
-      <c r="D24" s="549"/>
-      <c r="E24" s="549"/>
-      <c r="F24" s="549"/>
-      <c r="G24" s="549"/>
-      <c r="H24" s="549"/>
-      <c r="I24" s="549"/>
-      <c r="J24" s="549"/>
-      <c r="K24" s="549"/>
-      <c r="L24" s="550"/>
+      <c r="D24" s="545"/>
+      <c r="E24" s="545"/>
+      <c r="F24" s="545"/>
+      <c r="G24" s="545"/>
+      <c r="H24" s="545"/>
+      <c r="I24" s="545"/>
+      <c r="J24" s="545"/>
+      <c r="K24" s="545"/>
+      <c r="L24" s="546"/>
       <c r="M24" s="338"/>
       <c r="Y24" s="337"/>
       <c r="Z24" s="337"/>
@@ -50112,18 +50127,18 @@
       <c r="B27" s="337" t="s">
         <v>3254</v>
       </c>
-      <c r="C27" s="570" t="s">
+      <c r="C27" s="567" t="s">
         <v>3255</v>
       </c>
-      <c r="D27" s="549"/>
-      <c r="E27" s="549"/>
-      <c r="F27" s="549"/>
-      <c r="G27" s="549"/>
-      <c r="H27" s="549"/>
-      <c r="I27" s="549"/>
-      <c r="J27" s="549"/>
-      <c r="K27" s="549"/>
-      <c r="L27" s="550"/>
+      <c r="D27" s="545"/>
+      <c r="E27" s="545"/>
+      <c r="F27" s="545"/>
+      <c r="G27" s="545"/>
+      <c r="H27" s="545"/>
+      <c r="I27" s="545"/>
+      <c r="J27" s="545"/>
+      <c r="K27" s="545"/>
+      <c r="L27" s="546"/>
       <c r="M27" s="338"/>
       <c r="Y27" s="337"/>
       <c r="Z27" s="337"/>
@@ -50260,18 +50275,18 @@
       <c r="B32" s="337" t="s">
         <v>3280</v>
       </c>
-      <c r="C32" s="570" t="s">
+      <c r="C32" s="567" t="s">
         <v>3281</v>
       </c>
-      <c r="D32" s="549"/>
-      <c r="E32" s="549"/>
-      <c r="F32" s="549"/>
-      <c r="G32" s="549"/>
-      <c r="H32" s="549"/>
-      <c r="I32" s="549"/>
-      <c r="J32" s="549"/>
-      <c r="K32" s="549"/>
-      <c r="L32" s="550"/>
+      <c r="D32" s="545"/>
+      <c r="E32" s="545"/>
+      <c r="F32" s="545"/>
+      <c r="G32" s="545"/>
+      <c r="H32" s="545"/>
+      <c r="I32" s="545"/>
+      <c r="J32" s="545"/>
+      <c r="K32" s="545"/>
+      <c r="L32" s="546"/>
       <c r="M32" s="338"/>
       <c r="Y32" s="337"/>
       <c r="Z32" s="337"/>
@@ -50408,18 +50423,18 @@
       <c r="B37" s="337" t="s">
         <v>3308</v>
       </c>
-      <c r="C37" s="570" t="s">
+      <c r="C37" s="567" t="s">
         <v>3309</v>
       </c>
-      <c r="D37" s="549"/>
-      <c r="E37" s="549"/>
-      <c r="F37" s="549"/>
-      <c r="G37" s="549"/>
-      <c r="H37" s="549"/>
-      <c r="I37" s="549"/>
-      <c r="J37" s="549"/>
-      <c r="K37" s="549"/>
-      <c r="L37" s="550"/>
+      <c r="D37" s="545"/>
+      <c r="E37" s="545"/>
+      <c r="F37" s="545"/>
+      <c r="G37" s="545"/>
+      <c r="H37" s="545"/>
+      <c r="I37" s="545"/>
+      <c r="J37" s="545"/>
+      <c r="K37" s="545"/>
+      <c r="L37" s="546"/>
       <c r="M37" s="338"/>
       <c r="Y37" s="337"/>
       <c r="Z37" s="337"/>
@@ -50520,18 +50535,18 @@
       <c r="B41" s="337" t="s">
         <v>3328</v>
       </c>
-      <c r="C41" s="570" t="s">
+      <c r="C41" s="567" t="s">
         <v>3329</v>
       </c>
-      <c r="D41" s="549"/>
-      <c r="E41" s="549"/>
-      <c r="F41" s="549"/>
-      <c r="G41" s="549"/>
-      <c r="H41" s="549"/>
-      <c r="I41" s="549"/>
-      <c r="J41" s="549"/>
-      <c r="K41" s="549"/>
-      <c r="L41" s="550"/>
+      <c r="D41" s="545"/>
+      <c r="E41" s="545"/>
+      <c r="F41" s="545"/>
+      <c r="G41" s="545"/>
+      <c r="H41" s="545"/>
+      <c r="I41" s="545"/>
+      <c r="J41" s="545"/>
+      <c r="K41" s="545"/>
+      <c r="L41" s="546"/>
       <c r="M41" s="338"/>
       <c r="Y41" s="337"/>
       <c r="Z41" s="337"/>
@@ -50672,18 +50687,18 @@
       <c r="B46" s="337" t="s">
         <v>3355</v>
       </c>
-      <c r="C46" s="570" t="s">
+      <c r="C46" s="567" t="s">
         <v>3356</v>
       </c>
-      <c r="D46" s="549"/>
-      <c r="E46" s="549"/>
-      <c r="F46" s="549"/>
-      <c r="G46" s="549"/>
-      <c r="H46" s="549"/>
-      <c r="I46" s="549"/>
-      <c r="J46" s="549"/>
-      <c r="K46" s="549"/>
-      <c r="L46" s="550"/>
+      <c r="D46" s="545"/>
+      <c r="E46" s="545"/>
+      <c r="F46" s="545"/>
+      <c r="G46" s="545"/>
+      <c r="H46" s="545"/>
+      <c r="I46" s="545"/>
+      <c r="J46" s="545"/>
+      <c r="K46" s="545"/>
+      <c r="L46" s="546"/>
       <c r="M46" s="338"/>
       <c r="Y46" s="337"/>
       <c r="Z46" s="337"/>
@@ -50812,18 +50827,18 @@
       <c r="B51" s="337" t="s">
         <v>3379</v>
       </c>
-      <c r="C51" s="570" t="s">
+      <c r="C51" s="567" t="s">
         <v>3380</v>
       </c>
-      <c r="D51" s="549"/>
-      <c r="E51" s="549"/>
-      <c r="F51" s="549"/>
-      <c r="G51" s="549"/>
-      <c r="H51" s="549"/>
-      <c r="I51" s="549"/>
-      <c r="J51" s="549"/>
-      <c r="K51" s="549"/>
-      <c r="L51" s="550"/>
+      <c r="D51" s="545"/>
+      <c r="E51" s="545"/>
+      <c r="F51" s="545"/>
+      <c r="G51" s="545"/>
+      <c r="H51" s="545"/>
+      <c r="I51" s="545"/>
+      <c r="J51" s="545"/>
+      <c r="K51" s="545"/>
+      <c r="L51" s="546"/>
       <c r="M51" s="338"/>
       <c r="N51" s="337"/>
       <c r="O51" s="337"/>
@@ -50933,18 +50948,18 @@
       <c r="B54" s="337" t="s">
         <v>3393</v>
       </c>
-      <c r="C54" s="570" t="s">
+      <c r="C54" s="567" t="s">
         <v>3394</v>
       </c>
-      <c r="D54" s="549"/>
-      <c r="E54" s="549"/>
-      <c r="F54" s="549"/>
-      <c r="G54" s="549"/>
-      <c r="H54" s="549"/>
-      <c r="I54" s="549"/>
-      <c r="J54" s="549"/>
-      <c r="K54" s="549"/>
-      <c r="L54" s="550"/>
+      <c r="D54" s="545"/>
+      <c r="E54" s="545"/>
+      <c r="F54" s="545"/>
+      <c r="G54" s="545"/>
+      <c r="H54" s="545"/>
+      <c r="I54" s="545"/>
+      <c r="J54" s="545"/>
+      <c r="K54" s="545"/>
+      <c r="L54" s="546"/>
       <c r="M54" s="338"/>
       <c r="Y54" s="337"/>
       <c r="Z54" s="337"/>
@@ -51074,18 +51089,18 @@
       <c r="B59" s="337" t="s">
         <v>3417</v>
       </c>
-      <c r="C59" s="567" t="s">
+      <c r="C59" s="568" t="s">
         <v>3418</v>
       </c>
-      <c r="D59" s="545"/>
-      <c r="E59" s="545"/>
-      <c r="F59" s="545"/>
-      <c r="G59" s="545"/>
-      <c r="H59" s="544"/>
-      <c r="I59" s="552"/>
-      <c r="J59" s="545"/>
-      <c r="K59" s="552"/>
-      <c r="L59" s="545"/>
+      <c r="D59" s="543"/>
+      <c r="E59" s="543"/>
+      <c r="F59" s="543"/>
+      <c r="G59" s="543"/>
+      <c r="H59" s="553"/>
+      <c r="I59" s="542"/>
+      <c r="J59" s="543"/>
+      <c r="K59" s="542"/>
+      <c r="L59" s="543"/>
       <c r="M59" s="338"/>
       <c r="N59" s="128"/>
       <c r="O59" s="128"/>
@@ -51312,18 +51327,18 @@
       <c r="B65" s="337" t="s">
         <v>3453</v>
       </c>
-      <c r="C65" s="570" t="s">
+      <c r="C65" s="567" t="s">
         <v>3454</v>
       </c>
-      <c r="D65" s="549"/>
-      <c r="E65" s="549"/>
-      <c r="F65" s="549"/>
-      <c r="G65" s="549"/>
-      <c r="H65" s="549"/>
-      <c r="I65" s="549"/>
-      <c r="J65" s="549"/>
-      <c r="K65" s="549"/>
-      <c r="L65" s="550"/>
+      <c r="D65" s="545"/>
+      <c r="E65" s="545"/>
+      <c r="F65" s="545"/>
+      <c r="G65" s="545"/>
+      <c r="H65" s="545"/>
+      <c r="I65" s="545"/>
+      <c r="J65" s="545"/>
+      <c r="K65" s="545"/>
+      <c r="L65" s="546"/>
       <c r="M65" s="338"/>
       <c r="Y65" s="337"/>
       <c r="Z65" s="337"/>
@@ -51403,18 +51418,18 @@
       <c r="B68" s="337" t="s">
         <v>3468</v>
       </c>
-      <c r="C68" s="570" t="s">
+      <c r="C68" s="567" t="s">
         <v>3469</v>
       </c>
-      <c r="D68" s="549"/>
-      <c r="E68" s="549"/>
-      <c r="F68" s="549"/>
-      <c r="G68" s="549"/>
-      <c r="H68" s="549"/>
-      <c r="I68" s="549"/>
-      <c r="J68" s="549"/>
-      <c r="K68" s="549"/>
-      <c r="L68" s="550"/>
+      <c r="D68" s="545"/>
+      <c r="E68" s="545"/>
+      <c r="F68" s="545"/>
+      <c r="G68" s="545"/>
+      <c r="H68" s="545"/>
+      <c r="I68" s="545"/>
+      <c r="J68" s="545"/>
+      <c r="K68" s="545"/>
+      <c r="L68" s="546"/>
       <c r="M68" s="338"/>
       <c r="Y68" s="337"/>
       <c r="Z68" s="337"/>
@@ -51518,18 +51533,18 @@
       <c r="B72" s="337" t="s">
         <v>3488</v>
       </c>
-      <c r="C72" s="570" t="s">
+      <c r="C72" s="567" t="s">
         <v>3489</v>
       </c>
-      <c r="D72" s="549"/>
-      <c r="E72" s="549"/>
-      <c r="F72" s="549"/>
-      <c r="G72" s="549"/>
-      <c r="H72" s="549"/>
-      <c r="I72" s="549"/>
-      <c r="J72" s="549"/>
-      <c r="K72" s="549"/>
-      <c r="L72" s="550"/>
+      <c r="D72" s="545"/>
+      <c r="E72" s="545"/>
+      <c r="F72" s="545"/>
+      <c r="G72" s="545"/>
+      <c r="H72" s="545"/>
+      <c r="I72" s="545"/>
+      <c r="J72" s="545"/>
+      <c r="K72" s="545"/>
+      <c r="L72" s="546"/>
       <c r="M72" s="338"/>
       <c r="Y72" s="337"/>
       <c r="Z72" s="337"/>
@@ -51661,18 +51676,18 @@
       <c r="B77" s="337" t="s">
         <v>3513</v>
       </c>
-      <c r="C77" s="570" t="s">
+      <c r="C77" s="567" t="s">
         <v>3514</v>
       </c>
-      <c r="D77" s="549"/>
-      <c r="E77" s="549"/>
-      <c r="F77" s="549"/>
-      <c r="G77" s="549"/>
-      <c r="H77" s="549"/>
-      <c r="I77" s="549"/>
-      <c r="J77" s="549"/>
-      <c r="K77" s="549"/>
-      <c r="L77" s="550"/>
+      <c r="D77" s="545"/>
+      <c r="E77" s="545"/>
+      <c r="F77" s="545"/>
+      <c r="G77" s="545"/>
+      <c r="H77" s="545"/>
+      <c r="I77" s="545"/>
+      <c r="J77" s="545"/>
+      <c r="K77" s="545"/>
+      <c r="L77" s="546"/>
       <c r="M77" s="338"/>
       <c r="N77" s="337"/>
       <c r="O77" s="337"/>
@@ -51853,18 +51868,18 @@
       <c r="B81" s="337" t="s">
         <v>3532</v>
       </c>
-      <c r="C81" s="570" t="s">
+      <c r="C81" s="567" t="s">
         <v>3533</v>
       </c>
-      <c r="D81" s="549"/>
-      <c r="E81" s="549"/>
-      <c r="F81" s="549"/>
-      <c r="G81" s="549"/>
-      <c r="H81" s="549"/>
-      <c r="I81" s="549"/>
-      <c r="J81" s="549"/>
-      <c r="K81" s="549"/>
-      <c r="L81" s="550"/>
+      <c r="D81" s="545"/>
+      <c r="E81" s="545"/>
+      <c r="F81" s="545"/>
+      <c r="G81" s="545"/>
+      <c r="H81" s="545"/>
+      <c r="I81" s="545"/>
+      <c r="J81" s="545"/>
+      <c r="K81" s="545"/>
+      <c r="L81" s="546"/>
       <c r="M81" s="338"/>
       <c r="Y81" s="337"/>
       <c r="Z81" s="337"/>
@@ -51931,15 +51946,15 @@
       <c r="B84" s="337" t="s">
         <v>3543</v>
       </c>
-      <c r="C84" s="570" t="s">
+      <c r="C84" s="567" t="s">
         <v>3544</v>
       </c>
-      <c r="D84" s="549"/>
-      <c r="E84" s="549"/>
-      <c r="F84" s="549"/>
-      <c r="G84" s="549"/>
-      <c r="H84" s="549"/>
-      <c r="I84" s="550"/>
+      <c r="D84" s="545"/>
+      <c r="E84" s="545"/>
+      <c r="F84" s="545"/>
+      <c r="G84" s="545"/>
+      <c r="H84" s="545"/>
+      <c r="I84" s="546"/>
       <c r="J84" s="337"/>
       <c r="K84" s="338"/>
       <c r="L84" s="337"/>
@@ -52076,18 +52091,18 @@
       <c r="B89" s="337" t="s">
         <v>3569</v>
       </c>
-      <c r="C89" s="570" t="s">
+      <c r="C89" s="567" t="s">
         <v>3570</v>
       </c>
-      <c r="D89" s="549"/>
-      <c r="E89" s="549"/>
-      <c r="F89" s="549"/>
-      <c r="G89" s="549"/>
-      <c r="H89" s="549"/>
-      <c r="I89" s="549"/>
-      <c r="J89" s="549"/>
-      <c r="K89" s="549"/>
-      <c r="L89" s="550"/>
+      <c r="D89" s="545"/>
+      <c r="E89" s="545"/>
+      <c r="F89" s="545"/>
+      <c r="G89" s="545"/>
+      <c r="H89" s="545"/>
+      <c r="I89" s="545"/>
+      <c r="J89" s="545"/>
+      <c r="K89" s="545"/>
+      <c r="L89" s="546"/>
       <c r="M89" s="338"/>
       <c r="Y89" s="337"/>
       <c r="Z89" s="337"/>
@@ -52185,18 +52200,18 @@
       <c r="B93" s="337" t="s">
         <v>3588</v>
       </c>
-      <c r="C93" s="567" t="s">
+      <c r="C93" s="568" t="s">
         <v>3589</v>
       </c>
-      <c r="D93" s="568"/>
-      <c r="E93" s="569"/>
-      <c r="F93" s="568"/>
-      <c r="G93" s="566"/>
-      <c r="H93" s="544"/>
-      <c r="I93" s="566"/>
-      <c r="J93" s="568"/>
-      <c r="K93" s="566"/>
-      <c r="L93" s="568"/>
+      <c r="D93" s="569"/>
+      <c r="E93" s="570"/>
+      <c r="F93" s="569"/>
+      <c r="G93" s="560"/>
+      <c r="H93" s="553"/>
+      <c r="I93" s="560"/>
+      <c r="J93" s="569"/>
+      <c r="K93" s="560"/>
+      <c r="L93" s="569"/>
       <c r="M93" s="338"/>
       <c r="N93" s="128"/>
       <c r="O93" s="128"/>
@@ -52312,18 +52327,18 @@
       <c r="B96" s="337" t="s">
         <v>3599</v>
       </c>
-      <c r="C96" s="570" t="s">
+      <c r="C96" s="567" t="s">
         <v>3600</v>
       </c>
-      <c r="D96" s="549"/>
-      <c r="E96" s="549"/>
-      <c r="F96" s="549"/>
-      <c r="G96" s="549"/>
-      <c r="H96" s="549"/>
-      <c r="I96" s="549"/>
-      <c r="J96" s="549"/>
-      <c r="K96" s="549"/>
-      <c r="L96" s="550"/>
+      <c r="D96" s="545"/>
+      <c r="E96" s="545"/>
+      <c r="F96" s="545"/>
+      <c r="G96" s="545"/>
+      <c r="H96" s="545"/>
+      <c r="I96" s="545"/>
+      <c r="J96" s="545"/>
+      <c r="K96" s="545"/>
+      <c r="L96" s="546"/>
       <c r="M96" s="338"/>
       <c r="Y96" s="337"/>
       <c r="Z96" s="337"/>
@@ -52442,18 +52457,18 @@
       <c r="B99" s="337" t="s">
         <v>3614</v>
       </c>
-      <c r="C99" s="567" t="s">
+      <c r="C99" s="568" t="s">
         <v>3615</v>
       </c>
-      <c r="D99" s="568"/>
-      <c r="E99" s="569"/>
-      <c r="F99" s="568"/>
-      <c r="G99" s="566"/>
-      <c r="H99" s="544"/>
-      <c r="I99" s="566"/>
-      <c r="J99" s="568"/>
-      <c r="K99" s="566"/>
-      <c r="L99" s="568"/>
+      <c r="D99" s="569"/>
+      <c r="E99" s="570"/>
+      <c r="F99" s="569"/>
+      <c r="G99" s="560"/>
+      <c r="H99" s="553"/>
+      <c r="I99" s="560"/>
+      <c r="J99" s="569"/>
+      <c r="K99" s="560"/>
+      <c r="L99" s="569"/>
       <c r="M99" s="338"/>
       <c r="N99" s="128"/>
       <c r="O99" s="128"/>
@@ -52687,18 +52702,18 @@
       <c r="B104" s="337" t="s">
         <v>3639</v>
       </c>
-      <c r="C104" s="567" t="s">
+      <c r="C104" s="568" t="s">
         <v>3640</v>
       </c>
-      <c r="D104" s="568"/>
-      <c r="E104" s="569"/>
-      <c r="F104" s="568"/>
-      <c r="G104" s="566"/>
-      <c r="H104" s="544"/>
-      <c r="I104" s="566"/>
-      <c r="J104" s="568"/>
-      <c r="K104" s="566"/>
-      <c r="L104" s="568"/>
+      <c r="D104" s="569"/>
+      <c r="E104" s="570"/>
+      <c r="F104" s="569"/>
+      <c r="G104" s="560"/>
+      <c r="H104" s="553"/>
+      <c r="I104" s="560"/>
+      <c r="J104" s="569"/>
+      <c r="K104" s="560"/>
+      <c r="L104" s="569"/>
       <c r="M104" s="338"/>
       <c r="N104" s="128"/>
       <c r="O104" s="128"/>
@@ -52930,15 +52945,15 @@
       <c r="B109" s="337" t="s">
         <v>3663</v>
       </c>
-      <c r="C109" s="570" t="s">
+      <c r="C109" s="567" t="s">
         <v>3664</v>
       </c>
-      <c r="D109" s="549"/>
-      <c r="E109" s="549"/>
-      <c r="F109" s="549"/>
-      <c r="G109" s="549"/>
-      <c r="H109" s="549"/>
-      <c r="I109" s="550"/>
+      <c r="D109" s="545"/>
+      <c r="E109" s="545"/>
+      <c r="F109" s="545"/>
+      <c r="G109" s="545"/>
+      <c r="H109" s="545"/>
+      <c r="I109" s="546"/>
       <c r="J109" s="337"/>
       <c r="K109" s="338"/>
       <c r="L109" s="337"/>
@@ -53045,15 +53060,15 @@
       <c r="B113" s="337" t="s">
         <v>3682</v>
       </c>
-      <c r="C113" s="570" t="s">
+      <c r="C113" s="567" t="s">
         <v>3683</v>
       </c>
-      <c r="D113" s="549"/>
-      <c r="E113" s="549"/>
-      <c r="F113" s="549"/>
-      <c r="G113" s="549"/>
-      <c r="H113" s="549"/>
-      <c r="I113" s="550"/>
+      <c r="D113" s="545"/>
+      <c r="E113" s="545"/>
+      <c r="F113" s="545"/>
+      <c r="G113" s="545"/>
+      <c r="H113" s="545"/>
+      <c r="I113" s="546"/>
       <c r="J113" s="337"/>
       <c r="K113" s="338"/>
       <c r="L113" s="337"/>
@@ -53243,15 +53258,15 @@
       <c r="B120" s="337" t="s">
         <v>3719</v>
       </c>
-      <c r="C120" s="570" t="s">
+      <c r="C120" s="567" t="s">
         <v>3720</v>
       </c>
-      <c r="D120" s="549"/>
-      <c r="E120" s="549"/>
-      <c r="F120" s="549"/>
-      <c r="G120" s="549"/>
-      <c r="H120" s="549"/>
-      <c r="I120" s="550"/>
+      <c r="D120" s="545"/>
+      <c r="E120" s="545"/>
+      <c r="F120" s="545"/>
+      <c r="G120" s="545"/>
+      <c r="H120" s="545"/>
+      <c r="I120" s="546"/>
       <c r="J120" s="337"/>
       <c r="K120" s="338"/>
       <c r="L120" s="337"/>
@@ -53505,15 +53520,15 @@
       <c r="B129" s="337" t="s">
         <v>3769</v>
       </c>
-      <c r="C129" s="570" t="s">
+      <c r="C129" s="567" t="s">
         <v>3770</v>
       </c>
-      <c r="D129" s="549"/>
-      <c r="E129" s="549"/>
-      <c r="F129" s="549"/>
-      <c r="G129" s="549"/>
-      <c r="H129" s="549"/>
-      <c r="I129" s="550"/>
+      <c r="D129" s="545"/>
+      <c r="E129" s="545"/>
+      <c r="F129" s="545"/>
+      <c r="G129" s="545"/>
+      <c r="H129" s="545"/>
+      <c r="I129" s="546"/>
       <c r="J129" s="337"/>
       <c r="K129" s="338"/>
       <c r="L129" s="337"/>
@@ -53734,18 +53749,18 @@
       <c r="B137" s="337" t="s">
         <v>3811</v>
       </c>
-      <c r="C137" s="570" t="s">
+      <c r="C137" s="567" t="s">
         <v>3812</v>
       </c>
-      <c r="D137" s="549"/>
-      <c r="E137" s="549"/>
-      <c r="F137" s="549"/>
-      <c r="G137" s="549"/>
-      <c r="H137" s="549"/>
-      <c r="I137" s="549"/>
-      <c r="J137" s="549"/>
-      <c r="K137" s="549"/>
-      <c r="L137" s="550"/>
+      <c r="D137" s="545"/>
+      <c r="E137" s="545"/>
+      <c r="F137" s="545"/>
+      <c r="G137" s="545"/>
+      <c r="H137" s="545"/>
+      <c r="I137" s="545"/>
+      <c r="J137" s="545"/>
+      <c r="K137" s="545"/>
+      <c r="L137" s="546"/>
       <c r="M137" s="338"/>
       <c r="N137" s="337"/>
       <c r="O137" s="337"/>
@@ -53797,18 +53812,18 @@
       <c r="B139" s="337" t="s">
         <v>3818</v>
       </c>
-      <c r="C139" s="567" t="s">
+      <c r="C139" s="568" t="s">
         <v>3819</v>
       </c>
-      <c r="D139" s="568"/>
-      <c r="E139" s="569"/>
-      <c r="F139" s="568"/>
-      <c r="G139" s="566"/>
-      <c r="H139" s="544"/>
-      <c r="I139" s="566"/>
-      <c r="J139" s="568"/>
-      <c r="K139" s="566"/>
-      <c r="L139" s="568"/>
+      <c r="D139" s="569"/>
+      <c r="E139" s="570"/>
+      <c r="F139" s="569"/>
+      <c r="G139" s="560"/>
+      <c r="H139" s="553"/>
+      <c r="I139" s="560"/>
+      <c r="J139" s="569"/>
+      <c r="K139" s="560"/>
+      <c r="L139" s="569"/>
       <c r="M139" s="338"/>
       <c r="N139" s="128"/>
       <c r="O139" s="128"/>
@@ -54009,15 +54024,15 @@
       <c r="B145" s="337" t="s">
         <v>3841</v>
       </c>
-      <c r="C145" s="570" t="s">
+      <c r="C145" s="567" t="s">
         <v>3842</v>
       </c>
-      <c r="D145" s="549"/>
-      <c r="E145" s="549"/>
-      <c r="F145" s="549"/>
-      <c r="G145" s="549"/>
-      <c r="H145" s="549"/>
-      <c r="I145" s="550"/>
+      <c r="D145" s="545"/>
+      <c r="E145" s="545"/>
+      <c r="F145" s="545"/>
+      <c r="G145" s="545"/>
+      <c r="H145" s="545"/>
+      <c r="I145" s="546"/>
       <c r="J145" s="337"/>
       <c r="K145" s="338"/>
       <c r="L145" s="337"/>
@@ -54093,16 +54108,16 @@
         <v>3855</v>
       </c>
       <c r="B148" s="337"/>
-      <c r="C148" s="567"/>
-      <c r="D148" s="568"/>
-      <c r="E148" s="569"/>
-      <c r="F148" s="568"/>
-      <c r="G148" s="566"/>
-      <c r="H148" s="544"/>
-      <c r="I148" s="566"/>
-      <c r="J148" s="568"/>
-      <c r="K148" s="566"/>
-      <c r="L148" s="568"/>
+      <c r="C148" s="568"/>
+      <c r="D148" s="569"/>
+      <c r="E148" s="570"/>
+      <c r="F148" s="569"/>
+      <c r="G148" s="560"/>
+      <c r="H148" s="553"/>
+      <c r="I148" s="560"/>
+      <c r="J148" s="569"/>
+      <c r="K148" s="560"/>
+      <c r="L148" s="569"/>
       <c r="M148" s="338"/>
       <c r="N148" s="128"/>
       <c r="O148" s="128"/>
@@ -55105,13 +55120,13 @@
       <c r="C180" t="s">
         <v>970</v>
       </c>
-      <c r="D180" s="551" t="s">
+      <c r="D180" s="544" t="s">
         <v>4030</v>
       </c>
-      <c r="E180" s="549"/>
-      <c r="F180" s="549"/>
-      <c r="G180" s="549"/>
-      <c r="H180" s="550"/>
+      <c r="E180" s="545"/>
+      <c r="F180" s="545"/>
+      <c r="G180" s="545"/>
+      <c r="H180" s="546"/>
     </row>
     <row r="181" spans="1:33" ht="56.25" customHeight="1">
       <c r="A181" s="264"/>
@@ -55406,11 +55421,20 @@
   </sheetData>
   <autoFilter ref="A1:M188" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <mergeCells count="36">
-    <mergeCell ref="C54:L54"/>
-    <mergeCell ref="C51:L51"/>
-    <mergeCell ref="C65:L65"/>
-    <mergeCell ref="C68:L68"/>
-    <mergeCell ref="C72:L72"/>
+    <mergeCell ref="C93:L93"/>
+    <mergeCell ref="C99:L99"/>
+    <mergeCell ref="C104:L104"/>
+    <mergeCell ref="C139:L139"/>
+    <mergeCell ref="C77:L77"/>
+    <mergeCell ref="C81:L81"/>
+    <mergeCell ref="C84:I84"/>
+    <mergeCell ref="C89:L89"/>
+    <mergeCell ref="C137:L137"/>
+    <mergeCell ref="C96:L96"/>
+    <mergeCell ref="C109:I109"/>
+    <mergeCell ref="C113:I113"/>
+    <mergeCell ref="C120:I120"/>
+    <mergeCell ref="C129:I129"/>
     <mergeCell ref="C148:L148"/>
     <mergeCell ref="D180:H180"/>
     <mergeCell ref="B2:G2"/>
@@ -55427,21 +55451,12 @@
     <mergeCell ref="C37:L37"/>
     <mergeCell ref="C41:L41"/>
     <mergeCell ref="C46:L46"/>
+    <mergeCell ref="C54:L54"/>
+    <mergeCell ref="C51:L51"/>
+    <mergeCell ref="C65:L65"/>
+    <mergeCell ref="C68:L68"/>
+    <mergeCell ref="C72:L72"/>
     <mergeCell ref="C59:L59"/>
-    <mergeCell ref="C93:L93"/>
-    <mergeCell ref="C99:L99"/>
-    <mergeCell ref="C104:L104"/>
-    <mergeCell ref="C139:L139"/>
-    <mergeCell ref="C77:L77"/>
-    <mergeCell ref="C81:L81"/>
-    <mergeCell ref="C84:I84"/>
-    <mergeCell ref="C89:L89"/>
-    <mergeCell ref="C137:L137"/>
-    <mergeCell ref="C96:L96"/>
-    <mergeCell ref="C109:I109"/>
-    <mergeCell ref="C113:I113"/>
-    <mergeCell ref="C120:I120"/>
-    <mergeCell ref="C129:I129"/>
   </mergeCells>
   <phoneticPr fontId="73" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55495,12 +55510,12 @@
       <c r="A2" s="292" t="s">
         <v>4078</v>
       </c>
-      <c r="B2" s="542"/>
-      <c r="C2" s="543"/>
-      <c r="D2" s="543"/>
-      <c r="E2" s="543"/>
-      <c r="F2" s="543"/>
-      <c r="G2" s="543"/>
+      <c r="B2" s="551"/>
+      <c r="C2" s="552"/>
+      <c r="D2" s="552"/>
+      <c r="E2" s="552"/>
+      <c r="F2" s="552"/>
+      <c r="G2" s="552"/>
       <c r="M2" s="295"/>
     </row>
     <row r="3" spans="1:24" ht="66.75" customHeight="1">
@@ -56582,12 +56597,12 @@
       <c r="A33" s="292" t="s">
         <v>4239</v>
       </c>
-      <c r="B33" s="542"/>
-      <c r="C33" s="543"/>
-      <c r="D33" s="543"/>
-      <c r="E33" s="543"/>
-      <c r="F33" s="543"/>
-      <c r="G33" s="543"/>
+      <c r="B33" s="551"/>
+      <c r="C33" s="552"/>
+      <c r="D33" s="552"/>
+      <c r="E33" s="552"/>
+      <c r="F33" s="552"/>
+      <c r="G33" s="552"/>
       <c r="H33" s="292"/>
       <c r="I33" s="292"/>
       <c r="J33" s="292"/>
@@ -57276,13 +57291,13 @@
       <c r="C47" t="s">
         <v>4312</v>
       </c>
-      <c r="D47" s="551" t="s">
+      <c r="D47" s="544" t="s">
         <v>4313</v>
       </c>
-      <c r="E47" s="549"/>
-      <c r="F47" s="549"/>
-      <c r="G47" s="549"/>
-      <c r="H47" s="550"/>
+      <c r="E47" s="545"/>
+      <c r="F47" s="545"/>
+      <c r="G47" s="545"/>
+      <c r="H47" s="546"/>
     </row>
     <row r="48" spans="1:33" ht="56.25" customHeight="1">
       <c r="A48" s="298"/>
@@ -58157,12 +58172,12 @@
       <c r="A65" s="292" t="s">
         <v>765</v>
       </c>
-      <c r="B65" s="542"/>
-      <c r="C65" s="543"/>
-      <c r="D65" s="543"/>
-      <c r="E65" s="543"/>
-      <c r="F65" s="543"/>
-      <c r="G65" s="543"/>
+      <c r="B65" s="551"/>
+      <c r="C65" s="552"/>
+      <c r="D65" s="552"/>
+      <c r="E65" s="552"/>
+      <c r="F65" s="552"/>
+      <c r="G65" s="552"/>
       <c r="H65" s="292"/>
       <c r="I65" s="292"/>
       <c r="J65" s="292"/>
@@ -58335,13 +58350,13 @@
       <c r="C69" s="372" t="s">
         <v>4434</v>
       </c>
-      <c r="D69" s="574" t="s">
+      <c r="D69" s="571" t="s">
         <v>4435</v>
       </c>
-      <c r="E69" s="545"/>
-      <c r="F69" s="545"/>
-      <c r="G69" s="545"/>
-      <c r="H69" s="545"/>
+      <c r="E69" s="543"/>
+      <c r="F69" s="543"/>
+      <c r="G69" s="543"/>
+      <c r="H69" s="543"/>
       <c r="I69" s="362"/>
       <c r="J69" s="372"/>
       <c r="K69" s="362"/>
@@ -59788,16 +59803,16 @@
     <row r="100" spans="1:33" ht="56.25" customHeight="1">
       <c r="A100" s="420"/>
       <c r="B100" s="420"/>
-      <c r="C100" s="571"/>
-      <c r="D100" s="568"/>
-      <c r="E100" s="569"/>
-      <c r="F100" s="568"/>
-      <c r="G100" s="566"/>
-      <c r="H100" s="544"/>
-      <c r="I100" s="566"/>
-      <c r="J100" s="568"/>
-      <c r="K100" s="566"/>
-      <c r="L100" s="568"/>
+      <c r="C100" s="572"/>
+      <c r="D100" s="569"/>
+      <c r="E100" s="570"/>
+      <c r="F100" s="569"/>
+      <c r="G100" s="560"/>
+      <c r="H100" s="553"/>
+      <c r="I100" s="560"/>
+      <c r="J100" s="569"/>
+      <c r="K100" s="560"/>
+      <c r="L100" s="569"/>
       <c r="M100" s="421"/>
       <c r="Y100" s="422"/>
       <c r="Z100" s="422"/>
@@ -59860,16 +59875,16 @@
     <row r="103" spans="1:33" ht="56.25" customHeight="1">
       <c r="A103" s="420"/>
       <c r="B103" s="420"/>
-      <c r="C103" s="571"/>
-      <c r="D103" s="568"/>
-      <c r="E103" s="569"/>
-      <c r="F103" s="568"/>
-      <c r="G103" s="566"/>
-      <c r="H103" s="544"/>
-      <c r="I103" s="566"/>
-      <c r="J103" s="568"/>
-      <c r="K103" s="566"/>
-      <c r="L103" s="568"/>
+      <c r="C103" s="572"/>
+      <c r="D103" s="569"/>
+      <c r="E103" s="570"/>
+      <c r="F103" s="569"/>
+      <c r="G103" s="560"/>
+      <c r="H103" s="553"/>
+      <c r="I103" s="560"/>
+      <c r="J103" s="569"/>
+      <c r="K103" s="560"/>
+      <c r="L103" s="569"/>
       <c r="M103" s="421"/>
       <c r="Y103" s="422"/>
       <c r="Z103" s="422"/>
@@ -59947,16 +59962,16 @@
     <row r="107" spans="1:33" ht="56.25" customHeight="1">
       <c r="A107" s="420"/>
       <c r="B107" s="420"/>
-      <c r="C107" s="571"/>
-      <c r="D107" s="568"/>
-      <c r="E107" s="569"/>
-      <c r="F107" s="568"/>
-      <c r="G107" s="566"/>
-      <c r="H107" s="544"/>
-      <c r="I107" s="566"/>
-      <c r="J107" s="568"/>
-      <c r="K107" s="566"/>
-      <c r="L107" s="568"/>
+      <c r="C107" s="572"/>
+      <c r="D107" s="569"/>
+      <c r="E107" s="570"/>
+      <c r="F107" s="569"/>
+      <c r="G107" s="560"/>
+      <c r="H107" s="553"/>
+      <c r="I107" s="560"/>
+      <c r="J107" s="569"/>
+      <c r="K107" s="560"/>
+      <c r="L107" s="569"/>
       <c r="M107" s="421"/>
       <c r="Y107" s="422"/>
       <c r="Z107" s="422"/>
@@ -60067,16 +60082,16 @@
     <row r="112" spans="1:33" ht="56.25" customHeight="1">
       <c r="A112" s="420"/>
       <c r="B112" s="420"/>
-      <c r="C112" s="571"/>
-      <c r="D112" s="568"/>
-      <c r="E112" s="569"/>
-      <c r="F112" s="568"/>
-      <c r="G112" s="566"/>
-      <c r="H112" s="544"/>
-      <c r="I112" s="566"/>
-      <c r="J112" s="568"/>
-      <c r="K112" s="566"/>
-      <c r="L112" s="568"/>
+      <c r="C112" s="572"/>
+      <c r="D112" s="569"/>
+      <c r="E112" s="570"/>
+      <c r="F112" s="569"/>
+      <c r="G112" s="560"/>
+      <c r="H112" s="553"/>
+      <c r="I112" s="560"/>
+      <c r="J112" s="569"/>
+      <c r="K112" s="560"/>
+      <c r="L112" s="569"/>
       <c r="M112" s="421"/>
       <c r="Y112" s="422"/>
       <c r="Z112" s="422"/>
@@ -60160,16 +60175,16 @@
     <row r="117" spans="1:33" ht="56.25" customHeight="1">
       <c r="A117" s="420"/>
       <c r="B117" s="420"/>
-      <c r="C117" s="571"/>
-      <c r="D117" s="568"/>
-      <c r="E117" s="569"/>
-      <c r="F117" s="568"/>
-      <c r="G117" s="566"/>
-      <c r="H117" s="544"/>
-      <c r="I117" s="566"/>
-      <c r="J117" s="568"/>
-      <c r="K117" s="566"/>
-      <c r="L117" s="568"/>
+      <c r="C117" s="572"/>
+      <c r="D117" s="569"/>
+      <c r="E117" s="570"/>
+      <c r="F117" s="569"/>
+      <c r="G117" s="560"/>
+      <c r="H117" s="553"/>
+      <c r="I117" s="560"/>
+      <c r="J117" s="569"/>
+      <c r="K117" s="560"/>
+      <c r="L117" s="569"/>
       <c r="M117" s="421"/>
       <c r="Y117" s="422"/>
       <c r="Z117" s="422"/>
@@ -60244,16 +60259,16 @@
     <row r="122" spans="1:33" ht="56.25" customHeight="1">
       <c r="A122" s="420"/>
       <c r="B122" s="420"/>
-      <c r="C122" s="571"/>
-      <c r="D122" s="568"/>
-      <c r="E122" s="569"/>
-      <c r="F122" s="568"/>
-      <c r="G122" s="566"/>
-      <c r="H122" s="544"/>
-      <c r="I122" s="566"/>
-      <c r="J122" s="568"/>
-      <c r="K122" s="566"/>
-      <c r="L122" s="568"/>
+      <c r="C122" s="572"/>
+      <c r="D122" s="569"/>
+      <c r="E122" s="570"/>
+      <c r="F122" s="569"/>
+      <c r="G122" s="560"/>
+      <c r="H122" s="553"/>
+      <c r="I122" s="560"/>
+      <c r="J122" s="569"/>
+      <c r="K122" s="560"/>
+      <c r="L122" s="569"/>
       <c r="M122" s="421"/>
       <c r="Y122" s="422"/>
       <c r="Z122" s="422"/>
@@ -60268,16 +60283,16 @@
     <row r="123" spans="1:33" ht="56.25" customHeight="1">
       <c r="A123" s="420"/>
       <c r="B123" s="420"/>
-      <c r="C123" s="571"/>
-      <c r="D123" s="568"/>
-      <c r="E123" s="569"/>
-      <c r="F123" s="568"/>
-      <c r="G123" s="566"/>
-      <c r="H123" s="544"/>
-      <c r="I123" s="566"/>
-      <c r="J123" s="568"/>
-      <c r="K123" s="566"/>
-      <c r="L123" s="568"/>
+      <c r="C123" s="572"/>
+      <c r="D123" s="569"/>
+      <c r="E123" s="570"/>
+      <c r="F123" s="569"/>
+      <c r="G123" s="560"/>
+      <c r="H123" s="553"/>
+      <c r="I123" s="560"/>
+      <c r="J123" s="569"/>
+      <c r="K123" s="560"/>
+      <c r="L123" s="569"/>
       <c r="M123" s="421"/>
       <c r="Y123" s="422"/>
       <c r="Z123" s="422"/>
@@ -60361,16 +60376,16 @@
     <row r="128" spans="1:33" ht="56.25" customHeight="1">
       <c r="A128" s="420"/>
       <c r="B128" s="420"/>
-      <c r="C128" s="571"/>
-      <c r="D128" s="568"/>
-      <c r="E128" s="569"/>
-      <c r="F128" s="568"/>
-      <c r="G128" s="566"/>
-      <c r="H128" s="544"/>
-      <c r="I128" s="566"/>
-      <c r="J128" s="568"/>
-      <c r="K128" s="566"/>
-      <c r="L128" s="568"/>
+      <c r="C128" s="572"/>
+      <c r="D128" s="569"/>
+      <c r="E128" s="570"/>
+      <c r="F128" s="569"/>
+      <c r="G128" s="560"/>
+      <c r="H128" s="553"/>
+      <c r="I128" s="560"/>
+      <c r="J128" s="569"/>
+      <c r="K128" s="560"/>
+      <c r="L128" s="569"/>
       <c r="M128" s="421"/>
       <c r="Y128" s="422"/>
       <c r="Z128" s="422"/>
@@ -60424,16 +60439,16 @@
     <row r="131" spans="1:33" ht="56.25" customHeight="1">
       <c r="A131" s="420"/>
       <c r="B131" s="420"/>
-      <c r="C131" s="571"/>
-      <c r="D131" s="568"/>
-      <c r="E131" s="569"/>
-      <c r="F131" s="568"/>
-      <c r="G131" s="566"/>
-      <c r="H131" s="544"/>
-      <c r="I131" s="566"/>
-      <c r="J131" s="568"/>
-      <c r="K131" s="566"/>
-      <c r="L131" s="568"/>
+      <c r="C131" s="572"/>
+      <c r="D131" s="569"/>
+      <c r="E131" s="570"/>
+      <c r="F131" s="569"/>
+      <c r="G131" s="560"/>
+      <c r="H131" s="553"/>
+      <c r="I131" s="560"/>
+      <c r="J131" s="569"/>
+      <c r="K131" s="560"/>
+      <c r="L131" s="569"/>
       <c r="M131" s="421"/>
       <c r="Y131" s="422"/>
       <c r="Z131" s="422"/>
@@ -60508,16 +60523,16 @@
     <row r="136" spans="1:33" ht="56.25" customHeight="1">
       <c r="A136" s="420"/>
       <c r="B136" s="420"/>
-      <c r="C136" s="571"/>
-      <c r="D136" s="568"/>
-      <c r="E136" s="569"/>
-      <c r="F136" s="568"/>
-      <c r="G136" s="566"/>
-      <c r="H136" s="544"/>
-      <c r="I136" s="566"/>
-      <c r="J136" s="568"/>
-      <c r="K136" s="566"/>
-      <c r="L136" s="568"/>
+      <c r="C136" s="572"/>
+      <c r="D136" s="569"/>
+      <c r="E136" s="570"/>
+      <c r="F136" s="569"/>
+      <c r="G136" s="560"/>
+      <c r="H136" s="553"/>
+      <c r="I136" s="560"/>
+      <c r="J136" s="569"/>
+      <c r="K136" s="560"/>
+      <c r="L136" s="569"/>
       <c r="M136" s="421"/>
       <c r="Y136" s="422"/>
       <c r="Z136" s="422"/>
@@ -60592,16 +60607,16 @@
     <row r="141" spans="1:33" ht="56.25" customHeight="1">
       <c r="A141" s="420"/>
       <c r="B141" s="420"/>
-      <c r="C141" s="571"/>
-      <c r="D141" s="568"/>
-      <c r="E141" s="569"/>
-      <c r="F141" s="568"/>
-      <c r="G141" s="566"/>
-      <c r="H141" s="544"/>
-      <c r="I141" s="566"/>
-      <c r="J141" s="568"/>
-      <c r="K141" s="566"/>
-      <c r="L141" s="568"/>
+      <c r="C141" s="572"/>
+      <c r="D141" s="569"/>
+      <c r="E141" s="570"/>
+      <c r="F141" s="569"/>
+      <c r="G141" s="560"/>
+      <c r="H141" s="553"/>
+      <c r="I141" s="560"/>
+      <c r="J141" s="569"/>
+      <c r="K141" s="560"/>
+      <c r="L141" s="569"/>
       <c r="M141" s="421"/>
       <c r="Y141" s="422"/>
       <c r="Z141" s="422"/>
@@ -60676,16 +60691,16 @@
     <row r="146" spans="1:33" ht="56.25" customHeight="1">
       <c r="A146" s="420"/>
       <c r="B146" s="420"/>
-      <c r="C146" s="571"/>
-      <c r="D146" s="568"/>
-      <c r="E146" s="569"/>
-      <c r="F146" s="568"/>
-      <c r="G146" s="566"/>
-      <c r="H146" s="544"/>
-      <c r="I146" s="566"/>
-      <c r="J146" s="568"/>
-      <c r="K146" s="566"/>
-      <c r="L146" s="568"/>
+      <c r="C146" s="572"/>
+      <c r="D146" s="569"/>
+      <c r="E146" s="570"/>
+      <c r="F146" s="569"/>
+      <c r="G146" s="560"/>
+      <c r="H146" s="553"/>
+      <c r="I146" s="560"/>
+      <c r="J146" s="569"/>
+      <c r="K146" s="560"/>
+      <c r="L146" s="569"/>
       <c r="M146" s="421"/>
       <c r="Y146" s="422"/>
       <c r="Z146" s="422"/>
@@ -60745,16 +60760,16 @@
     <row r="150" spans="1:33" ht="56.25" customHeight="1">
       <c r="A150" s="420"/>
       <c r="B150" s="420"/>
-      <c r="C150" s="571"/>
-      <c r="D150" s="568"/>
-      <c r="E150" s="569"/>
-      <c r="F150" s="568"/>
-      <c r="G150" s="566"/>
-      <c r="H150" s="544"/>
-      <c r="I150" s="566"/>
-      <c r="J150" s="568"/>
-      <c r="K150" s="566"/>
-      <c r="L150" s="568"/>
+      <c r="C150" s="572"/>
+      <c r="D150" s="569"/>
+      <c r="E150" s="570"/>
+      <c r="F150" s="569"/>
+      <c r="G150" s="560"/>
+      <c r="H150" s="553"/>
+      <c r="I150" s="560"/>
+      <c r="J150" s="569"/>
+      <c r="K150" s="560"/>
+      <c r="L150" s="569"/>
       <c r="M150" s="421"/>
       <c r="Y150" s="422"/>
       <c r="Z150" s="422"/>
@@ -60823,16 +60838,16 @@
     <row r="154" spans="1:33" ht="56.25" customHeight="1">
       <c r="A154" s="420"/>
       <c r="B154" s="420"/>
-      <c r="C154" s="571"/>
-      <c r="D154" s="543"/>
-      <c r="E154" s="543"/>
-      <c r="F154" s="543"/>
-      <c r="G154" s="543"/>
-      <c r="H154" s="543"/>
-      <c r="I154" s="543"/>
-      <c r="J154" s="543"/>
-      <c r="K154" s="543"/>
-      <c r="L154" s="543"/>
+      <c r="C154" s="572"/>
+      <c r="D154" s="552"/>
+      <c r="E154" s="552"/>
+      <c r="F154" s="552"/>
+      <c r="G154" s="552"/>
+      <c r="H154" s="552"/>
+      <c r="I154" s="552"/>
+      <c r="J154" s="552"/>
+      <c r="K154" s="552"/>
+      <c r="L154" s="552"/>
       <c r="M154" s="421"/>
       <c r="N154" s="420"/>
       <c r="O154" s="420"/>
@@ -60903,16 +60918,16 @@
     <row r="158" spans="1:33" ht="56.25" customHeight="1">
       <c r="A158" s="420"/>
       <c r="B158" s="420"/>
-      <c r="C158" s="571"/>
-      <c r="D158" s="543"/>
-      <c r="E158" s="543"/>
-      <c r="F158" s="543"/>
-      <c r="G158" s="543"/>
-      <c r="H158" s="543"/>
-      <c r="I158" s="543"/>
-      <c r="J158" s="543"/>
-      <c r="K158" s="543"/>
-      <c r="L158" s="543"/>
+      <c r="C158" s="572"/>
+      <c r="D158" s="552"/>
+      <c r="E158" s="552"/>
+      <c r="F158" s="552"/>
+      <c r="G158" s="552"/>
+      <c r="H158" s="552"/>
+      <c r="I158" s="552"/>
+      <c r="J158" s="552"/>
+      <c r="K158" s="552"/>
+      <c r="L158" s="552"/>
       <c r="M158" s="421"/>
       <c r="N158" s="420"/>
       <c r="O158" s="420"/>
@@ -61008,16 +61023,16 @@
     <row r="161" spans="1:33" ht="56.25" customHeight="1">
       <c r="A161" s="420"/>
       <c r="B161" s="420"/>
-      <c r="C161" s="571"/>
-      <c r="D161" s="568"/>
-      <c r="E161" s="569"/>
-      <c r="F161" s="568"/>
-      <c r="G161" s="566"/>
-      <c r="H161" s="544"/>
-      <c r="I161" s="566"/>
-      <c r="J161" s="568"/>
-      <c r="K161" s="566"/>
-      <c r="L161" s="568"/>
+      <c r="C161" s="572"/>
+      <c r="D161" s="569"/>
+      <c r="E161" s="570"/>
+      <c r="F161" s="569"/>
+      <c r="G161" s="560"/>
+      <c r="H161" s="553"/>
+      <c r="I161" s="560"/>
+      <c r="J161" s="569"/>
+      <c r="K161" s="560"/>
+      <c r="L161" s="569"/>
       <c r="M161" s="421"/>
       <c r="Y161" s="422"/>
       <c r="Z161" s="422"/>
@@ -61107,16 +61122,16 @@
     <row r="167" spans="1:33" ht="56.25" customHeight="1">
       <c r="A167" s="420"/>
       <c r="B167" s="420"/>
-      <c r="C167" s="571"/>
-      <c r="D167" s="568"/>
-      <c r="E167" s="569"/>
-      <c r="F167" s="568"/>
-      <c r="G167" s="566"/>
-      <c r="H167" s="544"/>
-      <c r="I167" s="566"/>
-      <c r="J167" s="568"/>
-      <c r="K167" s="566"/>
-      <c r="L167" s="568"/>
+      <c r="C167" s="572"/>
+      <c r="D167" s="569"/>
+      <c r="E167" s="570"/>
+      <c r="F167" s="569"/>
+      <c r="G167" s="560"/>
+      <c r="H167" s="553"/>
+      <c r="I167" s="560"/>
+      <c r="J167" s="569"/>
+      <c r="K167" s="560"/>
+      <c r="L167" s="569"/>
       <c r="M167" s="421"/>
       <c r="Y167" s="422"/>
       <c r="Z167" s="422"/>
@@ -61161,16 +61176,16 @@
     <row r="170" spans="1:33" ht="56.25" customHeight="1">
       <c r="A170" s="420"/>
       <c r="B170" s="420"/>
-      <c r="C170" s="571"/>
-      <c r="D170" s="568"/>
-      <c r="E170" s="569"/>
-      <c r="F170" s="568"/>
-      <c r="G170" s="566"/>
-      <c r="H170" s="544"/>
-      <c r="I170" s="566"/>
-      <c r="J170" s="568"/>
-      <c r="K170" s="566"/>
-      <c r="L170" s="568"/>
+      <c r="C170" s="572"/>
+      <c r="D170" s="569"/>
+      <c r="E170" s="570"/>
+      <c r="F170" s="569"/>
+      <c r="G170" s="560"/>
+      <c r="H170" s="553"/>
+      <c r="I170" s="560"/>
+      <c r="J170" s="569"/>
+      <c r="K170" s="560"/>
+      <c r="L170" s="569"/>
       <c r="M170" s="421"/>
       <c r="Y170" s="422"/>
       <c r="Z170" s="422"/>
@@ -61520,10 +61535,10 @@
       <c r="B192" s="328"/>
       <c r="C192" s="328"/>
       <c r="D192" s="562"/>
-      <c r="E192" s="543"/>
-      <c r="F192" s="543"/>
-      <c r="G192" s="543"/>
-      <c r="H192" s="543"/>
+      <c r="E192" s="552"/>
+      <c r="F192" s="552"/>
+      <c r="G192" s="552"/>
+      <c r="H192" s="552"/>
       <c r="I192" s="318"/>
       <c r="J192" s="328"/>
       <c r="K192" s="318"/>
@@ -61548,13 +61563,13 @@
     <row r="194" spans="1:33" ht="56.25" customHeight="1">
       <c r="A194" s="420"/>
       <c r="B194" s="420"/>
-      <c r="C194" s="571"/>
-      <c r="D194" s="543"/>
-      <c r="E194" s="543"/>
-      <c r="F194" s="543"/>
-      <c r="G194" s="543"/>
-      <c r="H194" s="543"/>
-      <c r="I194" s="543"/>
+      <c r="C194" s="572"/>
+      <c r="D194" s="552"/>
+      <c r="E194" s="552"/>
+      <c r="F194" s="552"/>
+      <c r="G194" s="552"/>
+      <c r="H194" s="552"/>
+      <c r="I194" s="552"/>
       <c r="J194" s="424"/>
       <c r="K194" s="430"/>
       <c r="L194" s="424"/>
@@ -61611,13 +61626,13 @@
     <row r="197" spans="1:33" ht="56.25" customHeight="1">
       <c r="A197" s="420"/>
       <c r="B197" s="420"/>
-      <c r="C197" s="571"/>
-      <c r="D197" s="543"/>
-      <c r="E197" s="543"/>
-      <c r="F197" s="543"/>
-      <c r="G197" s="543"/>
-      <c r="H197" s="543"/>
-      <c r="I197" s="543"/>
+      <c r="C197" s="572"/>
+      <c r="D197" s="552"/>
+      <c r="E197" s="552"/>
+      <c r="F197" s="552"/>
+      <c r="G197" s="552"/>
+      <c r="H197" s="552"/>
+      <c r="I197" s="552"/>
       <c r="J197" s="424"/>
       <c r="K197" s="430"/>
       <c r="L197" s="424"/>
@@ -61731,13 +61746,13 @@
     <row r="202" spans="1:33" ht="56.25" customHeight="1">
       <c r="A202" s="420"/>
       <c r="B202" s="420"/>
-      <c r="C202" s="571"/>
-      <c r="D202" s="543"/>
-      <c r="E202" s="543"/>
-      <c r="F202" s="543"/>
-      <c r="G202" s="543"/>
-      <c r="H202" s="543"/>
-      <c r="I202" s="543"/>
+      <c r="C202" s="572"/>
+      <c r="D202" s="552"/>
+      <c r="E202" s="552"/>
+      <c r="F202" s="552"/>
+      <c r="G202" s="552"/>
+      <c r="H202" s="552"/>
+      <c r="I202" s="552"/>
       <c r="J202" s="424"/>
       <c r="K202" s="430"/>
       <c r="L202" s="424"/>
@@ -61879,13 +61894,13 @@
     <row r="208" spans="1:33" ht="56.25" customHeight="1">
       <c r="A208" s="420"/>
       <c r="B208" s="420"/>
-      <c r="C208" s="571"/>
-      <c r="D208" s="543"/>
-      <c r="E208" s="543"/>
-      <c r="F208" s="543"/>
-      <c r="G208" s="543"/>
-      <c r="H208" s="543"/>
-      <c r="I208" s="543"/>
+      <c r="C208" s="572"/>
+      <c r="D208" s="552"/>
+      <c r="E208" s="552"/>
+      <c r="F208" s="552"/>
+      <c r="G208" s="552"/>
+      <c r="H208" s="552"/>
+      <c r="I208" s="552"/>
       <c r="J208" s="424"/>
       <c r="K208" s="430"/>
       <c r="L208" s="424"/>
@@ -62038,13 +62053,13 @@
     <row r="214" spans="1:33" ht="56.25" customHeight="1">
       <c r="A214" s="420"/>
       <c r="B214" s="420"/>
-      <c r="C214" s="571"/>
-      <c r="D214" s="543"/>
-      <c r="E214" s="543"/>
-      <c r="F214" s="543"/>
-      <c r="G214" s="543"/>
-      <c r="H214" s="543"/>
-      <c r="I214" s="543"/>
+      <c r="C214" s="572"/>
+      <c r="D214" s="552"/>
+      <c r="E214" s="552"/>
+      <c r="F214" s="552"/>
+      <c r="G214" s="552"/>
+      <c r="H214" s="552"/>
+      <c r="I214" s="552"/>
       <c r="J214" s="424"/>
       <c r="K214" s="430"/>
       <c r="L214" s="424"/>
@@ -62167,13 +62182,13 @@
     <row r="218" spans="1:33" ht="56.25" customHeight="1">
       <c r="A218" s="421"/>
       <c r="B218" s="420"/>
-      <c r="C218" s="571"/>
-      <c r="D218" s="543"/>
-      <c r="E218" s="543"/>
-      <c r="F218" s="543"/>
-      <c r="G218" s="543"/>
-      <c r="H218" s="543"/>
-      <c r="I218" s="543"/>
+      <c r="C218" s="572"/>
+      <c r="D218" s="552"/>
+      <c r="E218" s="552"/>
+      <c r="F218" s="552"/>
+      <c r="G218" s="552"/>
+      <c r="H218" s="552"/>
+      <c r="I218" s="552"/>
       <c r="J218" s="424"/>
       <c r="K218" s="430"/>
       <c r="L218" s="424"/>
@@ -62299,10 +62314,10 @@
       <c r="C222" s="328"/>
       <c r="D222" s="431"/>
       <c r="E222" s="562"/>
-      <c r="F222" s="543"/>
-      <c r="G222" s="543"/>
-      <c r="H222" s="543"/>
-      <c r="I222" s="543"/>
+      <c r="F222" s="552"/>
+      <c r="G222" s="552"/>
+      <c r="H222" s="552"/>
+      <c r="I222" s="552"/>
       <c r="J222" s="328"/>
       <c r="K222" s="425"/>
       <c r="L222" s="328"/>
@@ -62310,16 +62325,16 @@
     </row>
     <row r="223" spans="1:33" ht="45" customHeight="1">
       <c r="A223" s="328"/>
-      <c r="B223" s="572"/>
-      <c r="C223" s="573"/>
-      <c r="D223" s="573"/>
-      <c r="E223" s="573"/>
-      <c r="F223" s="573"/>
-      <c r="G223" s="544"/>
-      <c r="H223" s="573"/>
-      <c r="I223" s="573"/>
-      <c r="J223" s="573"/>
-      <c r="K223" s="573"/>
+      <c r="B223" s="573"/>
+      <c r="C223" s="574"/>
+      <c r="D223" s="574"/>
+      <c r="E223" s="574"/>
+      <c r="F223" s="574"/>
+      <c r="G223" s="553"/>
+      <c r="H223" s="574"/>
+      <c r="I223" s="574"/>
+      <c r="J223" s="574"/>
+      <c r="K223" s="574"/>
       <c r="L223" s="328"/>
       <c r="M223" s="318"/>
       <c r="N223" s="328"/>
@@ -62626,38 +62641,38 @@
     <row r="296" ht="56.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D69:H69"/>
-    <mergeCell ref="C208:I208"/>
-    <mergeCell ref="C214:I214"/>
-    <mergeCell ref="C218:I218"/>
-    <mergeCell ref="E222:I222"/>
-    <mergeCell ref="B223:K223"/>
+    <mergeCell ref="C100:L100"/>
+    <mergeCell ref="C103:L103"/>
+    <mergeCell ref="C107:L107"/>
+    <mergeCell ref="C112:L112"/>
+    <mergeCell ref="C117:L117"/>
+    <mergeCell ref="C122:L122"/>
+    <mergeCell ref="C123:L123"/>
+    <mergeCell ref="C128:L128"/>
+    <mergeCell ref="C131:L131"/>
+    <mergeCell ref="C136:L136"/>
+    <mergeCell ref="C141:L141"/>
+    <mergeCell ref="C146:L146"/>
+    <mergeCell ref="C161:L161"/>
+    <mergeCell ref="C167:L167"/>
+    <mergeCell ref="C170:L170"/>
+    <mergeCell ref="C150:L150"/>
     <mergeCell ref="D192:H192"/>
     <mergeCell ref="C194:I194"/>
     <mergeCell ref="C154:L154"/>
     <mergeCell ref="C197:I197"/>
     <mergeCell ref="C202:I202"/>
     <mergeCell ref="C158:L158"/>
-    <mergeCell ref="C141:L141"/>
-    <mergeCell ref="C146:L146"/>
-    <mergeCell ref="C161:L161"/>
-    <mergeCell ref="C167:L167"/>
-    <mergeCell ref="C170:L170"/>
-    <mergeCell ref="C150:L150"/>
-    <mergeCell ref="C122:L122"/>
-    <mergeCell ref="C123:L123"/>
-    <mergeCell ref="C128:L128"/>
-    <mergeCell ref="C131:L131"/>
-    <mergeCell ref="C136:L136"/>
-    <mergeCell ref="C100:L100"/>
-    <mergeCell ref="C103:L103"/>
-    <mergeCell ref="C107:L107"/>
-    <mergeCell ref="C112:L112"/>
-    <mergeCell ref="C117:L117"/>
+    <mergeCell ref="C208:I208"/>
+    <mergeCell ref="C214:I214"/>
+    <mergeCell ref="C218:I218"/>
+    <mergeCell ref="E222:I222"/>
+    <mergeCell ref="B223:K223"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D69:H69"/>
   </mergeCells>
   <phoneticPr fontId="73" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -62711,14 +62726,14 @@
       <c r="A2" s="292" t="s">
         <v>4589</v>
       </c>
-      <c r="B2" s="542" t="s">
+      <c r="B2" s="551" t="s">
         <v>4590</v>
       </c>
-      <c r="C2" s="543"/>
-      <c r="D2" s="543"/>
-      <c r="E2" s="543"/>
-      <c r="F2" s="543"/>
-      <c r="G2" s="542"/>
+      <c r="C2" s="552"/>
+      <c r="D2" s="552"/>
+      <c r="E2" s="552"/>
+      <c r="F2" s="552"/>
+      <c r="G2" s="551"/>
       <c r="H2" s="575"/>
       <c r="I2" s="575"/>
       <c r="J2" s="575"/>
@@ -63343,12 +63358,12 @@
       <c r="A22" s="292" t="s">
         <v>4689</v>
       </c>
-      <c r="B22" s="555"/>
-      <c r="C22" s="549"/>
-      <c r="D22" s="549"/>
-      <c r="E22" s="549"/>
-      <c r="F22" s="549"/>
-      <c r="G22" s="550"/>
+      <c r="B22" s="554"/>
+      <c r="C22" s="545"/>
+      <c r="D22" s="545"/>
+      <c r="E22" s="545"/>
+      <c r="F22" s="545"/>
+      <c r="G22" s="546"/>
       <c r="H22" s="292"/>
       <c r="I22" s="292"/>
       <c r="J22" s="292"/>
@@ -64094,12 +64109,12 @@
       <c r="A39" s="292" t="s">
         <v>264</v>
       </c>
-      <c r="B39" s="555"/>
-      <c r="C39" s="549"/>
-      <c r="D39" s="549"/>
-      <c r="E39" s="549"/>
-      <c r="F39" s="549"/>
-      <c r="G39" s="550"/>
+      <c r="B39" s="554"/>
+      <c r="C39" s="545"/>
+      <c r="D39" s="545"/>
+      <c r="E39" s="545"/>
+      <c r="F39" s="545"/>
+      <c r="G39" s="546"/>
       <c r="H39" s="292"/>
       <c r="I39" s="292"/>
       <c r="J39" s="292"/>
@@ -64423,12 +64438,12 @@
       <c r="A46" s="292" t="s">
         <v>300</v>
       </c>
-      <c r="B46" s="555"/>
-      <c r="C46" s="549"/>
-      <c r="D46" s="549"/>
-      <c r="E46" s="549"/>
-      <c r="F46" s="549"/>
-      <c r="G46" s="550"/>
+      <c r="B46" s="554"/>
+      <c r="C46" s="545"/>
+      <c r="D46" s="545"/>
+      <c r="E46" s="545"/>
+      <c r="F46" s="545"/>
+      <c r="G46" s="546"/>
       <c r="H46" s="292"/>
       <c r="I46" s="292"/>
       <c r="J46" s="292"/>
@@ -64740,12 +64755,12 @@
       <c r="A53" s="292" t="s">
         <v>4826</v>
       </c>
-      <c r="B53" s="555"/>
-      <c r="C53" s="549"/>
-      <c r="D53" s="549"/>
-      <c r="E53" s="549"/>
-      <c r="F53" s="549"/>
-      <c r="G53" s="550"/>
+      <c r="B53" s="554"/>
+      <c r="C53" s="545"/>
+      <c r="D53" s="545"/>
+      <c r="E53" s="545"/>
+      <c r="F53" s="545"/>
+      <c r="G53" s="546"/>
       <c r="H53" s="292"/>
       <c r="I53" s="292"/>
       <c r="J53" s="292"/>
@@ -65057,12 +65072,12 @@
       <c r="A60" s="292" t="s">
         <v>4860</v>
       </c>
-      <c r="B60" s="555"/>
-      <c r="C60" s="549"/>
-      <c r="D60" s="549"/>
-      <c r="E60" s="549"/>
-      <c r="F60" s="549"/>
-      <c r="G60" s="550"/>
+      <c r="B60" s="554"/>
+      <c r="C60" s="545"/>
+      <c r="D60" s="545"/>
+      <c r="E60" s="545"/>
+      <c r="F60" s="545"/>
+      <c r="G60" s="546"/>
       <c r="H60" s="292"/>
       <c r="I60" s="292"/>
       <c r="J60" s="292"/>
@@ -65556,12 +65571,12 @@
       <c r="A71" s="292" t="s">
         <v>163</v>
       </c>
-      <c r="B71" s="555"/>
-      <c r="C71" s="549"/>
-      <c r="D71" s="549"/>
-      <c r="E71" s="549"/>
-      <c r="F71" s="549"/>
-      <c r="G71" s="550"/>
+      <c r="B71" s="554"/>
+      <c r="C71" s="545"/>
+      <c r="D71" s="545"/>
+      <c r="E71" s="545"/>
+      <c r="F71" s="545"/>
+      <c r="G71" s="546"/>
       <c r="H71" s="292"/>
       <c r="I71" s="292"/>
       <c r="J71" s="292"/>
@@ -66195,12 +66210,12 @@
       <c r="A84" s="292" t="s">
         <v>14</v>
       </c>
-      <c r="B84" s="555"/>
-      <c r="C84" s="549"/>
-      <c r="D84" s="549"/>
-      <c r="E84" s="549"/>
-      <c r="F84" s="549"/>
-      <c r="G84" s="550"/>
+      <c r="B84" s="554"/>
+      <c r="C84" s="545"/>
+      <c r="D84" s="545"/>
+      <c r="E84" s="545"/>
+      <c r="F84" s="545"/>
+      <c r="G84" s="546"/>
       <c r="H84" s="292"/>
       <c r="I84" s="292"/>
       <c r="J84" s="292"/>
@@ -66821,15 +66836,15 @@
         <v>5047</v>
       </c>
       <c r="B97" s="578"/>
-      <c r="C97" s="545"/>
-      <c r="D97" s="545"/>
-      <c r="E97" s="545"/>
-      <c r="F97" s="545"/>
+      <c r="C97" s="543"/>
+      <c r="D97" s="543"/>
+      <c r="E97" s="543"/>
+      <c r="F97" s="543"/>
       <c r="G97" s="578"/>
-      <c r="H97" s="545"/>
-      <c r="I97" s="552"/>
-      <c r="J97" s="545"/>
-      <c r="K97" s="552"/>
+      <c r="H97" s="543"/>
+      <c r="I97" s="542"/>
+      <c r="J97" s="543"/>
+      <c r="K97" s="542"/>
       <c r="L97" s="454"/>
       <c r="M97" s="455"/>
       <c r="N97" s="454"/>
@@ -68239,16 +68254,16 @@
     <row r="128" spans="1:33" ht="56.25" customHeight="1">
       <c r="A128" s="420"/>
       <c r="B128" s="420"/>
-      <c r="C128" s="571"/>
-      <c r="D128" s="543"/>
-      <c r="E128" s="543"/>
-      <c r="F128" s="543"/>
-      <c r="G128" s="543"/>
-      <c r="H128" s="543"/>
-      <c r="I128" s="543"/>
-      <c r="J128" s="543"/>
-      <c r="K128" s="543"/>
-      <c r="L128" s="543"/>
+      <c r="C128" s="572"/>
+      <c r="D128" s="552"/>
+      <c r="E128" s="552"/>
+      <c r="F128" s="552"/>
+      <c r="G128" s="552"/>
+      <c r="H128" s="552"/>
+      <c r="I128" s="552"/>
+      <c r="J128" s="552"/>
+      <c r="K128" s="552"/>
+      <c r="L128" s="552"/>
       <c r="M128" s="421"/>
       <c r="N128" s="420"/>
       <c r="O128" s="420"/>
@@ -68319,16 +68334,16 @@
     <row r="132" spans="1:33" ht="56.25" customHeight="1">
       <c r="A132" s="420"/>
       <c r="B132" s="420"/>
-      <c r="C132" s="571"/>
-      <c r="D132" s="543"/>
-      <c r="E132" s="543"/>
-      <c r="F132" s="543"/>
-      <c r="G132" s="543"/>
-      <c r="H132" s="543"/>
-      <c r="I132" s="543"/>
-      <c r="J132" s="543"/>
-      <c r="K132" s="543"/>
-      <c r="L132" s="543"/>
+      <c r="C132" s="572"/>
+      <c r="D132" s="552"/>
+      <c r="E132" s="552"/>
+      <c r="F132" s="552"/>
+      <c r="G132" s="552"/>
+      <c r="H132" s="552"/>
+      <c r="I132" s="552"/>
+      <c r="J132" s="552"/>
+      <c r="K132" s="552"/>
+      <c r="L132" s="552"/>
       <c r="M132" s="421"/>
       <c r="N132" s="420"/>
       <c r="O132" s="420"/>
@@ -68424,16 +68439,16 @@
     <row r="135" spans="1:33" ht="56.25" customHeight="1">
       <c r="A135" s="420"/>
       <c r="B135" s="420"/>
-      <c r="C135" s="571"/>
-      <c r="D135" s="568"/>
-      <c r="E135" s="569"/>
-      <c r="F135" s="568"/>
-      <c r="G135" s="566"/>
-      <c r="H135" s="544"/>
-      <c r="I135" s="566"/>
-      <c r="J135" s="568"/>
-      <c r="K135" s="566"/>
-      <c r="L135" s="568"/>
+      <c r="C135" s="572"/>
+      <c r="D135" s="569"/>
+      <c r="E135" s="570"/>
+      <c r="F135" s="569"/>
+      <c r="G135" s="560"/>
+      <c r="H135" s="553"/>
+      <c r="I135" s="560"/>
+      <c r="J135" s="569"/>
+      <c r="K135" s="560"/>
+      <c r="L135" s="569"/>
       <c r="M135" s="421"/>
       <c r="Y135" s="422"/>
       <c r="Z135" s="422"/>
@@ -68523,16 +68538,16 @@
     <row r="141" spans="1:33" ht="56.25" customHeight="1">
       <c r="A141" s="420"/>
       <c r="B141" s="420"/>
-      <c r="C141" s="571"/>
-      <c r="D141" s="568"/>
-      <c r="E141" s="569"/>
-      <c r="F141" s="568"/>
-      <c r="G141" s="566"/>
-      <c r="H141" s="544"/>
-      <c r="I141" s="566"/>
-      <c r="J141" s="568"/>
-      <c r="K141" s="566"/>
-      <c r="L141" s="568"/>
+      <c r="C141" s="572"/>
+      <c r="D141" s="569"/>
+      <c r="E141" s="570"/>
+      <c r="F141" s="569"/>
+      <c r="G141" s="560"/>
+      <c r="H141" s="553"/>
+      <c r="I141" s="560"/>
+      <c r="J141" s="569"/>
+      <c r="K141" s="560"/>
+      <c r="L141" s="569"/>
       <c r="M141" s="421"/>
       <c r="Y141" s="422"/>
       <c r="Z141" s="422"/>
@@ -68577,16 +68592,16 @@
     <row r="144" spans="1:33" ht="56.25" customHeight="1">
       <c r="A144" s="420"/>
       <c r="B144" s="420"/>
-      <c r="C144" s="571"/>
-      <c r="D144" s="568"/>
-      <c r="E144" s="569"/>
-      <c r="F144" s="568"/>
-      <c r="G144" s="566"/>
-      <c r="H144" s="544"/>
-      <c r="I144" s="566"/>
-      <c r="J144" s="568"/>
-      <c r="K144" s="566"/>
-      <c r="L144" s="568"/>
+      <c r="C144" s="572"/>
+      <c r="D144" s="569"/>
+      <c r="E144" s="570"/>
+      <c r="F144" s="569"/>
+      <c r="G144" s="560"/>
+      <c r="H144" s="553"/>
+      <c r="I144" s="560"/>
+      <c r="J144" s="569"/>
+      <c r="K144" s="560"/>
+      <c r="L144" s="569"/>
       <c r="M144" s="421"/>
       <c r="Y144" s="422"/>
       <c r="Z144" s="422"/>
@@ -68936,10 +68951,10 @@
       <c r="B166" s="328"/>
       <c r="C166" s="328"/>
       <c r="D166" s="562"/>
-      <c r="E166" s="543"/>
-      <c r="F166" s="543"/>
-      <c r="G166" s="543"/>
-      <c r="H166" s="543"/>
+      <c r="E166" s="552"/>
+      <c r="F166" s="552"/>
+      <c r="G166" s="552"/>
+      <c r="H166" s="552"/>
       <c r="I166" s="318"/>
       <c r="J166" s="328"/>
       <c r="K166" s="318"/>
@@ -68964,13 +68979,13 @@
     <row r="168" spans="1:33" ht="56.25" customHeight="1">
       <c r="A168" s="420"/>
       <c r="B168" s="420"/>
-      <c r="C168" s="571"/>
-      <c r="D168" s="543"/>
-      <c r="E168" s="543"/>
-      <c r="F168" s="543"/>
-      <c r="G168" s="543"/>
-      <c r="H168" s="543"/>
-      <c r="I168" s="543"/>
+      <c r="C168" s="572"/>
+      <c r="D168" s="552"/>
+      <c r="E168" s="552"/>
+      <c r="F168" s="552"/>
+      <c r="G168" s="552"/>
+      <c r="H168" s="552"/>
+      <c r="I168" s="552"/>
       <c r="J168" s="424"/>
       <c r="K168" s="430"/>
       <c r="L168" s="424"/>
@@ -69027,13 +69042,13 @@
     <row r="171" spans="1:33" ht="56.25" customHeight="1">
       <c r="A171" s="420"/>
       <c r="B171" s="420"/>
-      <c r="C171" s="571"/>
-      <c r="D171" s="543"/>
-      <c r="E171" s="543"/>
-      <c r="F171" s="543"/>
-      <c r="G171" s="543"/>
-      <c r="H171" s="543"/>
-      <c r="I171" s="543"/>
+      <c r="C171" s="572"/>
+      <c r="D171" s="552"/>
+      <c r="E171" s="552"/>
+      <c r="F171" s="552"/>
+      <c r="G171" s="552"/>
+      <c r="H171" s="552"/>
+      <c r="I171" s="552"/>
       <c r="J171" s="424"/>
       <c r="K171" s="430"/>
       <c r="L171" s="424"/>
@@ -69147,13 +69162,13 @@
     <row r="176" spans="1:33" ht="56.25" customHeight="1">
       <c r="A176" s="420"/>
       <c r="B176" s="420"/>
-      <c r="C176" s="571"/>
-      <c r="D176" s="543"/>
-      <c r="E176" s="543"/>
-      <c r="F176" s="543"/>
-      <c r="G176" s="543"/>
-      <c r="H176" s="543"/>
-      <c r="I176" s="543"/>
+      <c r="C176" s="572"/>
+      <c r="D176" s="552"/>
+      <c r="E176" s="552"/>
+      <c r="F176" s="552"/>
+      <c r="G176" s="552"/>
+      <c r="H176" s="552"/>
+      <c r="I176" s="552"/>
       <c r="J176" s="424"/>
       <c r="K176" s="430"/>
       <c r="L176" s="424"/>
@@ -69295,13 +69310,13 @@
     <row r="182" spans="1:33" ht="56.25" customHeight="1">
       <c r="A182" s="420"/>
       <c r="B182" s="420"/>
-      <c r="C182" s="571"/>
-      <c r="D182" s="543"/>
-      <c r="E182" s="543"/>
-      <c r="F182" s="543"/>
-      <c r="G182" s="543"/>
-      <c r="H182" s="543"/>
-      <c r="I182" s="543"/>
+      <c r="C182" s="572"/>
+      <c r="D182" s="552"/>
+      <c r="E182" s="552"/>
+      <c r="F182" s="552"/>
+      <c r="G182" s="552"/>
+      <c r="H182" s="552"/>
+      <c r="I182" s="552"/>
       <c r="J182" s="424"/>
       <c r="K182" s="430"/>
       <c r="L182" s="424"/>
@@ -69454,13 +69469,13 @@
     <row r="188" spans="1:33" ht="56.25" customHeight="1">
       <c r="A188" s="420"/>
       <c r="B188" s="420"/>
-      <c r="C188" s="571"/>
-      <c r="D188" s="543"/>
-      <c r="E188" s="543"/>
-      <c r="F188" s="543"/>
-      <c r="G188" s="543"/>
-      <c r="H188" s="543"/>
-      <c r="I188" s="543"/>
+      <c r="C188" s="572"/>
+      <c r="D188" s="552"/>
+      <c r="E188" s="552"/>
+      <c r="F188" s="552"/>
+      <c r="G188" s="552"/>
+      <c r="H188" s="552"/>
+      <c r="I188" s="552"/>
       <c r="J188" s="424"/>
       <c r="K188" s="430"/>
       <c r="L188" s="424"/>
@@ -69583,13 +69598,13 @@
     <row r="192" spans="1:33" ht="56.25" customHeight="1">
       <c r="A192" s="421"/>
       <c r="B192" s="420"/>
-      <c r="C192" s="571"/>
-      <c r="D192" s="543"/>
-      <c r="E192" s="543"/>
-      <c r="F192" s="543"/>
-      <c r="G192" s="543"/>
-      <c r="H192" s="543"/>
-      <c r="I192" s="543"/>
+      <c r="C192" s="572"/>
+      <c r="D192" s="552"/>
+      <c r="E192" s="552"/>
+      <c r="F192" s="552"/>
+      <c r="G192" s="552"/>
+      <c r="H192" s="552"/>
+      <c r="I192" s="552"/>
       <c r="J192" s="424"/>
       <c r="K192" s="430"/>
       <c r="L192" s="424"/>
@@ -69715,10 +69730,10 @@
       <c r="C196" s="328"/>
       <c r="D196" s="431"/>
       <c r="E196" s="562"/>
-      <c r="F196" s="543"/>
-      <c r="G196" s="543"/>
-      <c r="H196" s="543"/>
-      <c r="I196" s="543"/>
+      <c r="F196" s="552"/>
+      <c r="G196" s="552"/>
+      <c r="H196" s="552"/>
+      <c r="I196" s="552"/>
       <c r="J196" s="328"/>
       <c r="K196" s="425"/>
       <c r="L196" s="328"/>
@@ -69726,16 +69741,16 @@
     </row>
     <row r="197" spans="1:33" ht="45" customHeight="1">
       <c r="A197" s="328"/>
-      <c r="B197" s="572"/>
-      <c r="C197" s="573"/>
-      <c r="D197" s="573"/>
-      <c r="E197" s="573"/>
-      <c r="F197" s="573"/>
-      <c r="G197" s="544"/>
-      <c r="H197" s="573"/>
-      <c r="I197" s="573"/>
-      <c r="J197" s="573"/>
-      <c r="K197" s="573"/>
+      <c r="B197" s="573"/>
+      <c r="C197" s="574"/>
+      <c r="D197" s="574"/>
+      <c r="E197" s="574"/>
+      <c r="F197" s="574"/>
+      <c r="G197" s="553"/>
+      <c r="H197" s="574"/>
+      <c r="I197" s="574"/>
+      <c r="J197" s="574"/>
+      <c r="K197" s="574"/>
       <c r="L197" s="328"/>
       <c r="M197" s="318"/>
       <c r="N197" s="328"/>
@@ -70042,6 +70057,15 @@
     <row r="270" ht="56.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="C171:I171"/>
+    <mergeCell ref="C176:I176"/>
+    <mergeCell ref="C132:L132"/>
+    <mergeCell ref="C182:I182"/>
+    <mergeCell ref="C135:L135"/>
+    <mergeCell ref="C141:L141"/>
+    <mergeCell ref="C144:L144"/>
+    <mergeCell ref="D166:H166"/>
+    <mergeCell ref="C168:I168"/>
     <mergeCell ref="C188:I188"/>
     <mergeCell ref="C192:I192"/>
     <mergeCell ref="E196:I196"/>
@@ -70058,15 +70082,6 @@
     <mergeCell ref="B97:K97"/>
     <mergeCell ref="B120:K120"/>
     <mergeCell ref="C128:L128"/>
-    <mergeCell ref="C171:I171"/>
-    <mergeCell ref="C176:I176"/>
-    <mergeCell ref="C132:L132"/>
-    <mergeCell ref="C182:I182"/>
-    <mergeCell ref="C135:L135"/>
-    <mergeCell ref="C141:L141"/>
-    <mergeCell ref="C144:L144"/>
-    <mergeCell ref="D166:H166"/>
-    <mergeCell ref="C168:I168"/>
   </mergeCells>
   <phoneticPr fontId="73" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -70120,12 +70135,12 @@
       <c r="A2" s="292" t="s">
         <v>5192</v>
       </c>
-      <c r="B2" s="542"/>
-      <c r="C2" s="543"/>
-      <c r="D2" s="543"/>
-      <c r="E2" s="543"/>
-      <c r="F2" s="543"/>
-      <c r="G2" s="543"/>
+      <c r="B2" s="551"/>
+      <c r="C2" s="552"/>
+      <c r="D2" s="552"/>
+      <c r="E2" s="552"/>
+      <c r="F2" s="552"/>
+      <c r="G2" s="552"/>
       <c r="M2" s="295"/>
     </row>
     <row r="3" spans="1:33" ht="56.25" customHeight="1">
@@ -70715,12 +70730,12 @@
       <c r="A17" s="292" t="s">
         <v>5268</v>
       </c>
-      <c r="B17" s="542"/>
-      <c r="C17" s="543"/>
-      <c r="D17" s="543"/>
-      <c r="E17" s="543"/>
-      <c r="F17" s="543"/>
-      <c r="G17" s="543"/>
+      <c r="B17" s="551"/>
+      <c r="C17" s="552"/>
+      <c r="D17" s="552"/>
+      <c r="E17" s="552"/>
+      <c r="F17" s="552"/>
+      <c r="G17" s="552"/>
       <c r="H17" s="292"/>
       <c r="I17" s="292"/>
       <c r="J17" s="292"/>
@@ -71269,12 +71284,12 @@
       <c r="A31" s="292" t="s">
         <v>5342</v>
       </c>
-      <c r="B31" s="542"/>
-      <c r="C31" s="543"/>
-      <c r="D31" s="543"/>
-      <c r="E31" s="543"/>
-      <c r="F31" s="543"/>
-      <c r="G31" s="543"/>
+      <c r="B31" s="551"/>
+      <c r="C31" s="552"/>
+      <c r="D31" s="552"/>
+      <c r="E31" s="552"/>
+      <c r="F31" s="552"/>
+      <c r="G31" s="552"/>
       <c r="H31" s="292"/>
       <c r="I31" s="292"/>
       <c r="J31" s="292"/>
@@ -71635,12 +71650,12 @@
       <c r="A41" s="292" t="s">
         <v>5390</v>
       </c>
-      <c r="B41" s="542"/>
-      <c r="C41" s="543"/>
-      <c r="D41" s="543"/>
-      <c r="E41" s="543"/>
-      <c r="F41" s="543"/>
-      <c r="G41" s="543"/>
+      <c r="B41" s="551"/>
+      <c r="C41" s="552"/>
+      <c r="D41" s="552"/>
+      <c r="E41" s="552"/>
+      <c r="F41" s="552"/>
+      <c r="G41" s="552"/>
       <c r="H41" s="292"/>
       <c r="I41" s="292"/>
       <c r="J41" s="292"/>
@@ -72188,13 +72203,13 @@
       <c r="C55" t="s">
         <v>586</v>
       </c>
-      <c r="D55" s="552" t="s">
+      <c r="D55" s="542" t="s">
         <v>5473</v>
       </c>
-      <c r="E55" s="545"/>
-      <c r="F55" s="545"/>
-      <c r="G55" s="545"/>
-      <c r="H55" s="545"/>
+      <c r="E55" s="543"/>
+      <c r="F55" s="543"/>
+      <c r="G55" s="543"/>
+      <c r="H55" s="543"/>
       <c r="I55" s="239" t="s">
         <v>5474</v>
       </c>
@@ -72566,15 +72581,15 @@
       <c r="A64" s="479"/>
       <c r="B64" s="479"/>
       <c r="C64" s="580"/>
-      <c r="D64" s="568"/>
-      <c r="E64" s="569"/>
-      <c r="F64" s="568"/>
-      <c r="G64" s="566"/>
-      <c r="H64" s="544"/>
-      <c r="I64" s="566"/>
-      <c r="J64" s="568"/>
-      <c r="K64" s="566"/>
-      <c r="L64" s="568"/>
+      <c r="D64" s="569"/>
+      <c r="E64" s="570"/>
+      <c r="F64" s="569"/>
+      <c r="G64" s="560"/>
+      <c r="H64" s="553"/>
+      <c r="I64" s="560"/>
+      <c r="J64" s="569"/>
+      <c r="K64" s="560"/>
+      <c r="L64" s="569"/>
       <c r="M64" s="481"/>
       <c r="N64" s="367"/>
       <c r="O64" s="367"/>
@@ -72671,15 +72686,15 @@
       <c r="A67" s="479"/>
       <c r="B67" s="479"/>
       <c r="C67" s="580"/>
-      <c r="D67" s="568"/>
-      <c r="E67" s="569"/>
-      <c r="F67" s="568"/>
-      <c r="G67" s="566"/>
-      <c r="H67" s="544"/>
-      <c r="I67" s="566"/>
-      <c r="J67" s="568"/>
-      <c r="K67" s="566"/>
-      <c r="L67" s="568"/>
+      <c r="D67" s="569"/>
+      <c r="E67" s="570"/>
+      <c r="F67" s="569"/>
+      <c r="G67" s="560"/>
+      <c r="H67" s="553"/>
+      <c r="I67" s="560"/>
+      <c r="J67" s="569"/>
+      <c r="K67" s="560"/>
+      <c r="L67" s="569"/>
       <c r="M67" s="481"/>
       <c r="N67" s="367"/>
       <c r="O67" s="367"/>
@@ -72776,15 +72791,15 @@
       <c r="A70" s="479"/>
       <c r="B70" s="479"/>
       <c r="C70" s="580"/>
-      <c r="D70" s="568"/>
-      <c r="E70" s="569"/>
-      <c r="F70" s="568"/>
-      <c r="G70" s="566"/>
-      <c r="H70" s="544"/>
-      <c r="I70" s="566"/>
-      <c r="J70" s="568"/>
-      <c r="K70" s="566"/>
-      <c r="L70" s="568"/>
+      <c r="D70" s="569"/>
+      <c r="E70" s="570"/>
+      <c r="F70" s="569"/>
+      <c r="G70" s="560"/>
+      <c r="H70" s="553"/>
+      <c r="I70" s="560"/>
+      <c r="J70" s="569"/>
+      <c r="K70" s="560"/>
+      <c r="L70" s="569"/>
       <c r="M70" s="481"/>
       <c r="Y70" s="482"/>
       <c r="Z70" s="482"/>
@@ -72848,15 +72863,15 @@
       <c r="A73" s="479"/>
       <c r="B73" s="479"/>
       <c r="C73" s="580"/>
-      <c r="D73" s="568"/>
-      <c r="E73" s="569"/>
-      <c r="F73" s="568"/>
-      <c r="G73" s="566"/>
-      <c r="H73" s="544"/>
-      <c r="I73" s="566"/>
-      <c r="J73" s="568"/>
-      <c r="K73" s="566"/>
-      <c r="L73" s="568"/>
+      <c r="D73" s="569"/>
+      <c r="E73" s="570"/>
+      <c r="F73" s="569"/>
+      <c r="G73" s="560"/>
+      <c r="H73" s="553"/>
+      <c r="I73" s="560"/>
+      <c r="J73" s="569"/>
+      <c r="K73" s="560"/>
+      <c r="L73" s="569"/>
       <c r="M73" s="481"/>
       <c r="Y73" s="482"/>
       <c r="Z73" s="482"/>
@@ -72935,15 +72950,15 @@
       <c r="A77" s="479"/>
       <c r="B77" s="479"/>
       <c r="C77" s="580"/>
-      <c r="D77" s="568"/>
-      <c r="E77" s="569"/>
-      <c r="F77" s="568"/>
-      <c r="G77" s="566"/>
-      <c r="H77" s="544"/>
-      <c r="I77" s="566"/>
-      <c r="J77" s="568"/>
-      <c r="K77" s="566"/>
-      <c r="L77" s="568"/>
+      <c r="D77" s="569"/>
+      <c r="E77" s="570"/>
+      <c r="F77" s="569"/>
+      <c r="G77" s="560"/>
+      <c r="H77" s="553"/>
+      <c r="I77" s="560"/>
+      <c r="J77" s="569"/>
+      <c r="K77" s="560"/>
+      <c r="L77" s="569"/>
       <c r="M77" s="481"/>
       <c r="Y77" s="482"/>
       <c r="Z77" s="482"/>
@@ -73055,15 +73070,15 @@
       <c r="A82" s="479"/>
       <c r="B82" s="479"/>
       <c r="C82" s="580"/>
-      <c r="D82" s="568"/>
-      <c r="E82" s="569"/>
-      <c r="F82" s="568"/>
-      <c r="G82" s="566"/>
-      <c r="H82" s="544"/>
-      <c r="I82" s="566"/>
-      <c r="J82" s="568"/>
-      <c r="K82" s="566"/>
-      <c r="L82" s="568"/>
+      <c r="D82" s="569"/>
+      <c r="E82" s="570"/>
+      <c r="F82" s="569"/>
+      <c r="G82" s="560"/>
+      <c r="H82" s="553"/>
+      <c r="I82" s="560"/>
+      <c r="J82" s="569"/>
+      <c r="K82" s="560"/>
+      <c r="L82" s="569"/>
       <c r="M82" s="481"/>
       <c r="Y82" s="482"/>
       <c r="Z82" s="482"/>
@@ -73148,15 +73163,15 @@
       <c r="A87" s="479"/>
       <c r="B87" s="479"/>
       <c r="C87" s="580"/>
-      <c r="D87" s="568"/>
-      <c r="E87" s="569"/>
-      <c r="F87" s="568"/>
-      <c r="G87" s="566"/>
-      <c r="H87" s="544"/>
-      <c r="I87" s="566"/>
-      <c r="J87" s="568"/>
-      <c r="K87" s="566"/>
-      <c r="L87" s="568"/>
+      <c r="D87" s="569"/>
+      <c r="E87" s="570"/>
+      <c r="F87" s="569"/>
+      <c r="G87" s="560"/>
+      <c r="H87" s="553"/>
+      <c r="I87" s="560"/>
+      <c r="J87" s="569"/>
+      <c r="K87" s="560"/>
+      <c r="L87" s="569"/>
       <c r="M87" s="481"/>
       <c r="Y87" s="482"/>
       <c r="Z87" s="482"/>
@@ -73232,15 +73247,15 @@
       <c r="A92" s="479"/>
       <c r="B92" s="479"/>
       <c r="C92" s="580"/>
-      <c r="D92" s="568"/>
-      <c r="E92" s="569"/>
-      <c r="F92" s="568"/>
-      <c r="G92" s="566"/>
-      <c r="H92" s="544"/>
-      <c r="I92" s="566"/>
-      <c r="J92" s="568"/>
-      <c r="K92" s="566"/>
-      <c r="L92" s="568"/>
+      <c r="D92" s="569"/>
+      <c r="E92" s="570"/>
+      <c r="F92" s="569"/>
+      <c r="G92" s="560"/>
+      <c r="H92" s="553"/>
+      <c r="I92" s="560"/>
+      <c r="J92" s="569"/>
+      <c r="K92" s="560"/>
+      <c r="L92" s="569"/>
       <c r="M92" s="481"/>
       <c r="Y92" s="482"/>
       <c r="Z92" s="482"/>
@@ -73256,15 +73271,15 @@
       <c r="A93" s="479"/>
       <c r="B93" s="479"/>
       <c r="C93" s="580"/>
-      <c r="D93" s="568"/>
-      <c r="E93" s="569"/>
-      <c r="F93" s="568"/>
-      <c r="G93" s="566"/>
-      <c r="H93" s="544"/>
-      <c r="I93" s="566"/>
-      <c r="J93" s="568"/>
-      <c r="K93" s="566"/>
-      <c r="L93" s="568"/>
+      <c r="D93" s="569"/>
+      <c r="E93" s="570"/>
+      <c r="F93" s="569"/>
+      <c r="G93" s="560"/>
+      <c r="H93" s="553"/>
+      <c r="I93" s="560"/>
+      <c r="J93" s="569"/>
+      <c r="K93" s="560"/>
+      <c r="L93" s="569"/>
       <c r="M93" s="481"/>
       <c r="Y93" s="482"/>
       <c r="Z93" s="482"/>
@@ -73349,15 +73364,15 @@
       <c r="A98" s="479"/>
       <c r="B98" s="479"/>
       <c r="C98" s="580"/>
-      <c r="D98" s="568"/>
-      <c r="E98" s="569"/>
-      <c r="F98" s="568"/>
-      <c r="G98" s="566"/>
-      <c r="H98" s="544"/>
-      <c r="I98" s="566"/>
-      <c r="J98" s="568"/>
-      <c r="K98" s="566"/>
-      <c r="L98" s="568"/>
+      <c r="D98" s="569"/>
+      <c r="E98" s="570"/>
+      <c r="F98" s="569"/>
+      <c r="G98" s="560"/>
+      <c r="H98" s="553"/>
+      <c r="I98" s="560"/>
+      <c r="J98" s="569"/>
+      <c r="K98" s="560"/>
+      <c r="L98" s="569"/>
       <c r="M98" s="481"/>
       <c r="Y98" s="482"/>
       <c r="Z98" s="482"/>
@@ -73412,15 +73427,15 @@
       <c r="A101" s="479"/>
       <c r="B101" s="479"/>
       <c r="C101" s="580"/>
-      <c r="D101" s="568"/>
-      <c r="E101" s="569"/>
-      <c r="F101" s="568"/>
-      <c r="G101" s="566"/>
-      <c r="H101" s="544"/>
-      <c r="I101" s="566"/>
-      <c r="J101" s="568"/>
-      <c r="K101" s="566"/>
-      <c r="L101" s="568"/>
+      <c r="D101" s="569"/>
+      <c r="E101" s="570"/>
+      <c r="F101" s="569"/>
+      <c r="G101" s="560"/>
+      <c r="H101" s="553"/>
+      <c r="I101" s="560"/>
+      <c r="J101" s="569"/>
+      <c r="K101" s="560"/>
+      <c r="L101" s="569"/>
       <c r="M101" s="481"/>
       <c r="Y101" s="482"/>
       <c r="Z101" s="482"/>
@@ -73496,15 +73511,15 @@
       <c r="A106" s="479"/>
       <c r="B106" s="479"/>
       <c r="C106" s="580"/>
-      <c r="D106" s="568"/>
-      <c r="E106" s="569"/>
-      <c r="F106" s="568"/>
-      <c r="G106" s="566"/>
-      <c r="H106" s="544"/>
-      <c r="I106" s="566"/>
-      <c r="J106" s="568"/>
-      <c r="K106" s="566"/>
-      <c r="L106" s="568"/>
+      <c r="D106" s="569"/>
+      <c r="E106" s="570"/>
+      <c r="F106" s="569"/>
+      <c r="G106" s="560"/>
+      <c r="H106" s="553"/>
+      <c r="I106" s="560"/>
+      <c r="J106" s="569"/>
+      <c r="K106" s="560"/>
+      <c r="L106" s="569"/>
       <c r="M106" s="481"/>
       <c r="Y106" s="482"/>
       <c r="Z106" s="482"/>
@@ -73580,15 +73595,15 @@
       <c r="A111" s="479"/>
       <c r="B111" s="479"/>
       <c r="C111" s="580"/>
-      <c r="D111" s="568"/>
-      <c r="E111" s="569"/>
-      <c r="F111" s="568"/>
-      <c r="G111" s="566"/>
-      <c r="H111" s="544"/>
-      <c r="I111" s="566"/>
-      <c r="J111" s="568"/>
-      <c r="K111" s="566"/>
-      <c r="L111" s="568"/>
+      <c r="D111" s="569"/>
+      <c r="E111" s="570"/>
+      <c r="F111" s="569"/>
+      <c r="G111" s="560"/>
+      <c r="H111" s="553"/>
+      <c r="I111" s="560"/>
+      <c r="J111" s="569"/>
+      <c r="K111" s="560"/>
+      <c r="L111" s="569"/>
       <c r="M111" s="481"/>
       <c r="Y111" s="482"/>
       <c r="Z111" s="482"/>
@@ -73664,15 +73679,15 @@
       <c r="A116" s="479"/>
       <c r="B116" s="479"/>
       <c r="C116" s="580"/>
-      <c r="D116" s="568"/>
-      <c r="E116" s="569"/>
-      <c r="F116" s="568"/>
-      <c r="G116" s="566"/>
-      <c r="H116" s="544"/>
-      <c r="I116" s="566"/>
-      <c r="J116" s="568"/>
-      <c r="K116" s="566"/>
-      <c r="L116" s="568"/>
+      <c r="D116" s="569"/>
+      <c r="E116" s="570"/>
+      <c r="F116" s="569"/>
+      <c r="G116" s="560"/>
+      <c r="H116" s="553"/>
+      <c r="I116" s="560"/>
+      <c r="J116" s="569"/>
+      <c r="K116" s="560"/>
+      <c r="L116" s="569"/>
       <c r="M116" s="481"/>
       <c r="Y116" s="482"/>
       <c r="Z116" s="482"/>
@@ -73733,15 +73748,15 @@
       <c r="A120" s="479"/>
       <c r="B120" s="479"/>
       <c r="C120" s="580"/>
-      <c r="D120" s="568"/>
-      <c r="E120" s="569"/>
-      <c r="F120" s="568"/>
-      <c r="G120" s="566"/>
-      <c r="H120" s="544"/>
-      <c r="I120" s="566"/>
-      <c r="J120" s="568"/>
-      <c r="K120" s="566"/>
-      <c r="L120" s="568"/>
+      <c r="D120" s="569"/>
+      <c r="E120" s="570"/>
+      <c r="F120" s="569"/>
+      <c r="G120" s="560"/>
+      <c r="H120" s="553"/>
+      <c r="I120" s="560"/>
+      <c r="J120" s="569"/>
+      <c r="K120" s="560"/>
+      <c r="L120" s="569"/>
       <c r="M120" s="481"/>
       <c r="Y120" s="482"/>
       <c r="Z120" s="482"/>
@@ -73811,15 +73826,15 @@
       <c r="A124" s="479"/>
       <c r="B124" s="479"/>
       <c r="C124" s="580"/>
-      <c r="D124" s="543"/>
-      <c r="E124" s="543"/>
-      <c r="F124" s="543"/>
-      <c r="G124" s="543"/>
-      <c r="H124" s="543"/>
-      <c r="I124" s="543"/>
-      <c r="J124" s="543"/>
-      <c r="K124" s="543"/>
-      <c r="L124" s="543"/>
+      <c r="D124" s="552"/>
+      <c r="E124" s="552"/>
+      <c r="F124" s="552"/>
+      <c r="G124" s="552"/>
+      <c r="H124" s="552"/>
+      <c r="I124" s="552"/>
+      <c r="J124" s="552"/>
+      <c r="K124" s="552"/>
+      <c r="L124" s="552"/>
       <c r="M124" s="481"/>
       <c r="N124" s="479"/>
       <c r="O124" s="479"/>
@@ -73891,15 +73906,15 @@
       <c r="A128" s="479"/>
       <c r="B128" s="479"/>
       <c r="C128" s="580"/>
-      <c r="D128" s="543"/>
-      <c r="E128" s="543"/>
-      <c r="F128" s="543"/>
-      <c r="G128" s="543"/>
-      <c r="H128" s="543"/>
-      <c r="I128" s="543"/>
-      <c r="J128" s="543"/>
-      <c r="K128" s="543"/>
-      <c r="L128" s="543"/>
+      <c r="D128" s="552"/>
+      <c r="E128" s="552"/>
+      <c r="F128" s="552"/>
+      <c r="G128" s="552"/>
+      <c r="H128" s="552"/>
+      <c r="I128" s="552"/>
+      <c r="J128" s="552"/>
+      <c r="K128" s="552"/>
+      <c r="L128" s="552"/>
       <c r="M128" s="481"/>
       <c r="N128" s="479"/>
       <c r="O128" s="479"/>
@@ -73996,15 +74011,15 @@
       <c r="A131" s="479"/>
       <c r="B131" s="479"/>
       <c r="C131" s="580"/>
-      <c r="D131" s="568"/>
-      <c r="E131" s="569"/>
-      <c r="F131" s="568"/>
-      <c r="G131" s="566"/>
-      <c r="H131" s="544"/>
-      <c r="I131" s="566"/>
-      <c r="J131" s="568"/>
-      <c r="K131" s="566"/>
-      <c r="L131" s="568"/>
+      <c r="D131" s="569"/>
+      <c r="E131" s="570"/>
+      <c r="F131" s="569"/>
+      <c r="G131" s="560"/>
+      <c r="H131" s="553"/>
+      <c r="I131" s="560"/>
+      <c r="J131" s="569"/>
+      <c r="K131" s="560"/>
+      <c r="L131" s="569"/>
       <c r="M131" s="481"/>
       <c r="Y131" s="482"/>
       <c r="Z131" s="482"/>
@@ -74095,15 +74110,15 @@
       <c r="A137" s="479"/>
       <c r="B137" s="479"/>
       <c r="C137" s="580"/>
-      <c r="D137" s="568"/>
-      <c r="E137" s="569"/>
-      <c r="F137" s="568"/>
-      <c r="G137" s="566"/>
-      <c r="H137" s="544"/>
-      <c r="I137" s="566"/>
-      <c r="J137" s="568"/>
-      <c r="K137" s="566"/>
-      <c r="L137" s="568"/>
+      <c r="D137" s="569"/>
+      <c r="E137" s="570"/>
+      <c r="F137" s="569"/>
+      <c r="G137" s="560"/>
+      <c r="H137" s="553"/>
+      <c r="I137" s="560"/>
+      <c r="J137" s="569"/>
+      <c r="K137" s="560"/>
+      <c r="L137" s="569"/>
       <c r="M137" s="481"/>
       <c r="Y137" s="482"/>
       <c r="Z137" s="482"/>
@@ -74149,15 +74164,15 @@
       <c r="A140" s="479"/>
       <c r="B140" s="479"/>
       <c r="C140" s="580"/>
-      <c r="D140" s="568"/>
-      <c r="E140" s="569"/>
-      <c r="F140" s="568"/>
-      <c r="G140" s="566"/>
-      <c r="H140" s="544"/>
-      <c r="I140" s="566"/>
-      <c r="J140" s="568"/>
-      <c r="K140" s="566"/>
-      <c r="L140" s="568"/>
+      <c r="D140" s="569"/>
+      <c r="E140" s="570"/>
+      <c r="F140" s="569"/>
+      <c r="G140" s="560"/>
+      <c r="H140" s="553"/>
+      <c r="I140" s="560"/>
+      <c r="J140" s="569"/>
+      <c r="K140" s="560"/>
+      <c r="L140" s="569"/>
       <c r="M140" s="481"/>
       <c r="Y140" s="482"/>
       <c r="Z140" s="482"/>
@@ -74507,10 +74522,10 @@
       <c r="B162" s="248"/>
       <c r="C162" s="248"/>
       <c r="D162" s="581"/>
-      <c r="E162" s="543"/>
-      <c r="F162" s="543"/>
-      <c r="G162" s="543"/>
-      <c r="H162" s="543"/>
+      <c r="E162" s="552"/>
+      <c r="F162" s="552"/>
+      <c r="G162" s="552"/>
+      <c r="H162" s="552"/>
       <c r="I162" s="249"/>
       <c r="J162" s="248"/>
       <c r="K162" s="249"/>
@@ -74536,12 +74551,12 @@
       <c r="A164" s="479"/>
       <c r="B164" s="479"/>
       <c r="C164" s="580"/>
-      <c r="D164" s="543"/>
-      <c r="E164" s="543"/>
-      <c r="F164" s="543"/>
-      <c r="G164" s="543"/>
-      <c r="H164" s="543"/>
-      <c r="I164" s="543"/>
+      <c r="D164" s="552"/>
+      <c r="E164" s="552"/>
+      <c r="F164" s="552"/>
+      <c r="G164" s="552"/>
+      <c r="H164" s="552"/>
+      <c r="I164" s="552"/>
       <c r="J164" s="485"/>
       <c r="K164" s="480"/>
       <c r="L164" s="485"/>
@@ -74599,12 +74614,12 @@
       <c r="A167" s="479"/>
       <c r="B167" s="479"/>
       <c r="C167" s="580"/>
-      <c r="D167" s="543"/>
-      <c r="E167" s="543"/>
-      <c r="F167" s="543"/>
-      <c r="G167" s="543"/>
-      <c r="H167" s="543"/>
-      <c r="I167" s="543"/>
+      <c r="D167" s="552"/>
+      <c r="E167" s="552"/>
+      <c r="F167" s="552"/>
+      <c r="G167" s="552"/>
+      <c r="H167" s="552"/>
+      <c r="I167" s="552"/>
       <c r="J167" s="485"/>
       <c r="K167" s="480"/>
       <c r="L167" s="485"/>
@@ -74719,12 +74734,12 @@
       <c r="A172" s="479"/>
       <c r="B172" s="479"/>
       <c r="C172" s="580"/>
-      <c r="D172" s="543"/>
-      <c r="E172" s="543"/>
-      <c r="F172" s="543"/>
-      <c r="G172" s="543"/>
-      <c r="H172" s="543"/>
-      <c r="I172" s="543"/>
+      <c r="D172" s="552"/>
+      <c r="E172" s="552"/>
+      <c r="F172" s="552"/>
+      <c r="G172" s="552"/>
+      <c r="H172" s="552"/>
+      <c r="I172" s="552"/>
       <c r="J172" s="485"/>
       <c r="K172" s="480"/>
       <c r="L172" s="485"/>
@@ -74867,12 +74882,12 @@
       <c r="A178" s="479"/>
       <c r="B178" s="479"/>
       <c r="C178" s="580"/>
-      <c r="D178" s="543"/>
-      <c r="E178" s="543"/>
-      <c r="F178" s="543"/>
-      <c r="G178" s="543"/>
-      <c r="H178" s="543"/>
-      <c r="I178" s="543"/>
+      <c r="D178" s="552"/>
+      <c r="E178" s="552"/>
+      <c r="F178" s="552"/>
+      <c r="G178" s="552"/>
+      <c r="H178" s="552"/>
+      <c r="I178" s="552"/>
       <c r="J178" s="485"/>
       <c r="K178" s="480"/>
       <c r="L178" s="485"/>
@@ -75026,12 +75041,12 @@
       <c r="A184" s="479"/>
       <c r="B184" s="479"/>
       <c r="C184" s="580"/>
-      <c r="D184" s="543"/>
-      <c r="E184" s="543"/>
-      <c r="F184" s="543"/>
-      <c r="G184" s="543"/>
-      <c r="H184" s="543"/>
-      <c r="I184" s="543"/>
+      <c r="D184" s="552"/>
+      <c r="E184" s="552"/>
+      <c r="F184" s="552"/>
+      <c r="G184" s="552"/>
+      <c r="H184" s="552"/>
+      <c r="I184" s="552"/>
       <c r="J184" s="485"/>
       <c r="K184" s="480"/>
       <c r="L184" s="485"/>
@@ -75155,12 +75170,12 @@
       <c r="A188" s="481"/>
       <c r="B188" s="479"/>
       <c r="C188" s="580"/>
-      <c r="D188" s="543"/>
-      <c r="E188" s="543"/>
-      <c r="F188" s="543"/>
-      <c r="G188" s="543"/>
-      <c r="H188" s="543"/>
-      <c r="I188" s="543"/>
+      <c r="D188" s="552"/>
+      <c r="E188" s="552"/>
+      <c r="F188" s="552"/>
+      <c r="G188" s="552"/>
+      <c r="H188" s="552"/>
+      <c r="I188" s="552"/>
       <c r="J188" s="485"/>
       <c r="K188" s="480"/>
       <c r="L188" s="485"/>
@@ -75286,10 +75301,10 @@
       <c r="C192" s="248"/>
       <c r="D192" s="371"/>
       <c r="E192" s="581"/>
-      <c r="F192" s="543"/>
-      <c r="G192" s="543"/>
-      <c r="H192" s="543"/>
-      <c r="I192" s="543"/>
+      <c r="F192" s="552"/>
+      <c r="G192" s="552"/>
+      <c r="H192" s="552"/>
+      <c r="I192" s="552"/>
       <c r="J192" s="248"/>
       <c r="K192" s="486"/>
       <c r="L192" s="248"/>
@@ -75298,15 +75313,15 @@
     <row r="193" spans="1:33" ht="45" customHeight="1">
       <c r="A193" s="248"/>
       <c r="B193" s="582"/>
-      <c r="C193" s="573"/>
-      <c r="D193" s="573"/>
-      <c r="E193" s="573"/>
-      <c r="F193" s="573"/>
-      <c r="G193" s="544"/>
-      <c r="H193" s="573"/>
-      <c r="I193" s="573"/>
-      <c r="J193" s="573"/>
-      <c r="K193" s="573"/>
+      <c r="C193" s="574"/>
+      <c r="D193" s="574"/>
+      <c r="E193" s="574"/>
+      <c r="F193" s="574"/>
+      <c r="G193" s="553"/>
+      <c r="H193" s="574"/>
+      <c r="I193" s="574"/>
+      <c r="J193" s="574"/>
+      <c r="K193" s="574"/>
       <c r="L193" s="248"/>
       <c r="M193" s="249"/>
       <c r="N193" s="248"/>
@@ -75613,6 +75628,33 @@
     <row r="266" ht="56.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="C70:L70"/>
+    <mergeCell ref="C73:L73"/>
+    <mergeCell ref="C77:L77"/>
+    <mergeCell ref="C82:L82"/>
+    <mergeCell ref="C87:L87"/>
+    <mergeCell ref="C92:L92"/>
+    <mergeCell ref="C93:L93"/>
+    <mergeCell ref="C98:L98"/>
+    <mergeCell ref="C101:L101"/>
+    <mergeCell ref="C106:L106"/>
+    <mergeCell ref="C111:L111"/>
+    <mergeCell ref="C116:L116"/>
+    <mergeCell ref="C131:L131"/>
+    <mergeCell ref="C137:L137"/>
+    <mergeCell ref="C140:L140"/>
+    <mergeCell ref="C120:L120"/>
+    <mergeCell ref="D162:H162"/>
+    <mergeCell ref="C164:I164"/>
+    <mergeCell ref="C124:L124"/>
+    <mergeCell ref="C167:I167"/>
+    <mergeCell ref="C172:I172"/>
+    <mergeCell ref="C128:L128"/>
+    <mergeCell ref="C178:I178"/>
+    <mergeCell ref="C184:I184"/>
+    <mergeCell ref="C188:I188"/>
+    <mergeCell ref="E192:I192"/>
+    <mergeCell ref="B193:K193"/>
     <mergeCell ref="C67:L67"/>
     <mergeCell ref="D55:H55"/>
     <mergeCell ref="B2:G2"/>
@@ -75620,33 +75662,6 @@
     <mergeCell ref="B31:G31"/>
     <mergeCell ref="B41:G41"/>
     <mergeCell ref="C64:L64"/>
-    <mergeCell ref="C178:I178"/>
-    <mergeCell ref="C184:I184"/>
-    <mergeCell ref="C188:I188"/>
-    <mergeCell ref="E192:I192"/>
-    <mergeCell ref="B193:K193"/>
-    <mergeCell ref="D162:H162"/>
-    <mergeCell ref="C164:I164"/>
-    <mergeCell ref="C124:L124"/>
-    <mergeCell ref="C167:I167"/>
-    <mergeCell ref="C172:I172"/>
-    <mergeCell ref="C128:L128"/>
-    <mergeCell ref="C111:L111"/>
-    <mergeCell ref="C116:L116"/>
-    <mergeCell ref="C131:L131"/>
-    <mergeCell ref="C137:L137"/>
-    <mergeCell ref="C140:L140"/>
-    <mergeCell ref="C120:L120"/>
-    <mergeCell ref="C92:L92"/>
-    <mergeCell ref="C93:L93"/>
-    <mergeCell ref="C98:L98"/>
-    <mergeCell ref="C101:L101"/>
-    <mergeCell ref="C106:L106"/>
-    <mergeCell ref="C70:L70"/>
-    <mergeCell ref="C73:L73"/>
-    <mergeCell ref="C77:L77"/>
-    <mergeCell ref="C82:L82"/>
-    <mergeCell ref="C87:L87"/>
   </mergeCells>
   <phoneticPr fontId="73" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -75692,14 +75707,14 @@
     </row>
     <row r="2" spans="1:31" ht="88.5" customHeight="1">
       <c r="A2" s="292"/>
-      <c r="B2" s="542" t="s">
+      <c r="B2" s="551" t="s">
         <v>5523</v>
       </c>
-      <c r="C2" s="549"/>
-      <c r="D2" s="549"/>
-      <c r="E2" s="549"/>
-      <c r="F2" s="549"/>
-      <c r="G2" s="550"/>
+      <c r="C2" s="545"/>
+      <c r="D2" s="545"/>
+      <c r="E2" s="545"/>
+      <c r="F2" s="545"/>
+      <c r="G2" s="546"/>
       <c r="K2" s="295"/>
     </row>
     <row r="3" spans="1:31" ht="76.5" customHeight="1">
@@ -75743,10 +75758,10 @@
       <c r="C4" s="248" t="s">
         <v>5533</v>
       </c>
-      <c r="D4" s="560" t="s">
+      <c r="D4" s="565" t="s">
         <v>5534</v>
       </c>
-      <c r="E4" s="550"/>
+      <c r="E4" s="546"/>
       <c r="F4" s="248"/>
       <c r="G4" s="249" t="s">
         <v>5535</v>
@@ -75810,10 +75825,10 @@
       <c r="C6" s="248" t="s">
         <v>5546</v>
       </c>
-      <c r="D6" s="560" t="s">
+      <c r="D6" s="565" t="s">
         <v>5547</v>
       </c>
-      <c r="E6" s="550"/>
+      <c r="E6" s="546"/>
       <c r="F6" s="248"/>
       <c r="G6" s="249" t="s">
         <v>5548</v>
@@ -75868,10 +75883,10 @@
       <c r="C8" s="248" t="s">
         <v>5560</v>
       </c>
-      <c r="D8" s="560" t="s">
+      <c r="D8" s="565" t="s">
         <v>5561</v>
       </c>
-      <c r="E8" s="550"/>
+      <c r="E8" s="546"/>
       <c r="G8" s="249" t="s">
         <v>5562</v>
       </c>
@@ -75935,10 +75950,10 @@
       <c r="C10" s="248" t="s">
         <v>5574</v>
       </c>
-      <c r="D10" s="560" t="s">
+      <c r="D10" s="565" t="s">
         <v>5575</v>
       </c>
-      <c r="E10" s="550"/>
+      <c r="E10" s="546"/>
       <c r="F10" s="128"/>
       <c r="G10" s="249" t="s">
         <v>5576</v>
@@ -76024,10 +76039,10 @@
       <c r="C12" s="248" t="s">
         <v>5588</v>
       </c>
-      <c r="D12" s="560" t="s">
+      <c r="D12" s="565" t="s">
         <v>5589</v>
       </c>
-      <c r="E12" s="550"/>
+      <c r="E12" s="546"/>
       <c r="F12" s="265"/>
       <c r="G12" s="249" t="s">
         <v>5590</v>
@@ -76082,10 +76097,10 @@
       <c r="C14" t="s">
         <v>5602</v>
       </c>
-      <c r="D14" s="551" t="s">
+      <c r="D14" s="544" t="s">
         <v>5603</v>
       </c>
-      <c r="E14" s="550"/>
+      <c r="E14" s="546"/>
       <c r="G14" s="239" t="s">
         <v>5604</v>
       </c>
@@ -76148,10 +76163,10 @@
       <c r="C16" t="s">
         <v>5616</v>
       </c>
-      <c r="D16" s="551" t="s">
+      <c r="D16" s="544" t="s">
         <v>5617</v>
       </c>
-      <c r="E16" s="550"/>
+      <c r="E16" s="546"/>
       <c r="G16" s="239" t="s">
         <v>5618</v>
       </c>
@@ -76214,10 +76229,10 @@
       <c r="C18" t="s">
         <v>5630</v>
       </c>
-      <c r="D18" s="551" t="s">
+      <c r="D18" s="544" t="s">
         <v>5631</v>
       </c>
-      <c r="E18" s="550"/>
+      <c r="E18" s="546"/>
       <c r="G18" s="239" t="s">
         <v>5632</v>
       </c>
@@ -76266,10 +76281,10 @@
       <c r="C20" s="248" t="s">
         <v>5643</v>
       </c>
-      <c r="D20" s="560" t="s">
+      <c r="D20" s="565" t="s">
         <v>5644</v>
       </c>
-      <c r="E20" s="550"/>
+      <c r="E20" s="546"/>
       <c r="F20" s="248"/>
       <c r="G20" s="249" t="s">
         <v>5645</v>
@@ -76338,10 +76353,10 @@
       <c r="C22" t="s">
         <v>5657</v>
       </c>
-      <c r="D22" s="551" t="s">
+      <c r="D22" s="544" t="s">
         <v>5658</v>
       </c>
-      <c r="E22" s="550"/>
+      <c r="E22" s="546"/>
       <c r="G22" s="239" t="s">
         <v>5659</v>
       </c>
@@ -76400,10 +76415,10 @@
       <c r="C24" s="248" t="s">
         <v>5671</v>
       </c>
-      <c r="D24" s="560" t="s">
+      <c r="D24" s="565" t="s">
         <v>5672</v>
       </c>
-      <c r="E24" s="550"/>
+      <c r="E24" s="546"/>
       <c r="F24" s="248"/>
       <c r="G24" s="249" t="s">
         <v>5673</v>
@@ -76469,10 +76484,10 @@
       <c r="C26" s="248" t="s">
         <v>5685</v>
       </c>
-      <c r="D26" s="560" t="s">
+      <c r="D26" s="565" t="s">
         <v>5686</v>
       </c>
-      <c r="E26" s="550"/>
+      <c r="E26" s="546"/>
       <c r="F26" s="248"/>
       <c r="G26" s="250" t="s">
         <v>5687</v>
@@ -76497,14 +76512,14 @@
     </row>
     <row r="27" spans="1:31" ht="43.5" customHeight="1">
       <c r="A27" s="292"/>
-      <c r="B27" s="542" t="s">
+      <c r="B27" s="551" t="s">
         <v>5689</v>
       </c>
-      <c r="C27" s="549"/>
-      <c r="D27" s="549"/>
-      <c r="E27" s="549"/>
-      <c r="F27" s="549"/>
-      <c r="G27" s="550"/>
+      <c r="C27" s="545"/>
+      <c r="D27" s="545"/>
+      <c r="E27" s="545"/>
+      <c r="F27" s="545"/>
+      <c r="G27" s="546"/>
       <c r="H27" s="292"/>
       <c r="I27" s="292"/>
       <c r="J27" s="292"/>
@@ -76609,10 +76624,10 @@
       <c r="C30" t="s">
         <v>5697</v>
       </c>
-      <c r="D30" s="551" t="s">
+      <c r="D30" s="544" t="s">
         <v>5698</v>
       </c>
-      <c r="E30" s="550"/>
+      <c r="E30" s="546"/>
       <c r="G30" s="239" t="s">
         <v>5702</v>
       </c>
@@ -76645,14 +76660,14 @@
     </row>
     <row r="31" spans="1:31" ht="43.5" customHeight="1">
       <c r="A31" s="292"/>
-      <c r="B31" s="542" t="s">
+      <c r="B31" s="551" t="s">
         <v>5705</v>
       </c>
-      <c r="C31" s="549"/>
-      <c r="D31" s="549"/>
-      <c r="E31" s="549"/>
-      <c r="F31" s="549"/>
-      <c r="G31" s="550"/>
+      <c r="C31" s="545"/>
+      <c r="D31" s="545"/>
+      <c r="E31" s="545"/>
+      <c r="F31" s="545"/>
+      <c r="G31" s="546"/>
       <c r="H31" s="292"/>
       <c r="I31" s="292"/>
       <c r="J31" s="292"/>
@@ -76754,9 +76769,9 @@
     <row r="35" spans="1:31" ht="43.5" customHeight="1">
       <c r="A35" s="248"/>
       <c r="B35" s="581"/>
-      <c r="C35" s="543"/>
-      <c r="D35" s="543"/>
-      <c r="E35" s="543"/>
+      <c r="C35" s="552"/>
+      <c r="D35" s="552"/>
+      <c r="E35" s="552"/>
       <c r="F35" s="248"/>
       <c r="G35" s="248"/>
       <c r="H35" s="248"/>
@@ -76919,8 +76934,8 @@
       <c r="B42" s="248"/>
       <c r="C42" s="248"/>
       <c r="D42" s="581"/>
-      <c r="E42" s="543"/>
-      <c r="F42" s="543"/>
+      <c r="E42" s="552"/>
+      <c r="F42" s="552"/>
       <c r="G42" s="249"/>
       <c r="H42" s="248"/>
       <c r="I42" s="249"/>
@@ -77140,14 +77155,14 @@
     <row r="49" spans="1:31" ht="56.25" customHeight="1">
       <c r="A49" s="420"/>
       <c r="B49" s="420"/>
-      <c r="C49" s="571"/>
-      <c r="D49" s="568"/>
-      <c r="E49" s="569"/>
-      <c r="F49" s="544"/>
-      <c r="G49" s="566"/>
-      <c r="H49" s="568"/>
-      <c r="I49" s="566"/>
-      <c r="J49" s="568"/>
+      <c r="C49" s="572"/>
+      <c r="D49" s="569"/>
+      <c r="E49" s="570"/>
+      <c r="F49" s="553"/>
+      <c r="G49" s="560"/>
+      <c r="H49" s="569"/>
+      <c r="I49" s="560"/>
+      <c r="J49" s="569"/>
       <c r="K49" s="421"/>
       <c r="W49" s="422"/>
       <c r="X49" s="422"/>
@@ -77201,14 +77216,14 @@
     <row r="53" spans="1:31" ht="56.25" customHeight="1">
       <c r="A53" s="420"/>
       <c r="B53" s="420"/>
-      <c r="C53" s="571"/>
-      <c r="D53" s="568"/>
-      <c r="E53" s="569"/>
-      <c r="F53" s="544"/>
-      <c r="G53" s="566"/>
-      <c r="H53" s="568"/>
-      <c r="I53" s="566"/>
-      <c r="J53" s="568"/>
+      <c r="C53" s="572"/>
+      <c r="D53" s="569"/>
+      <c r="E53" s="570"/>
+      <c r="F53" s="553"/>
+      <c r="G53" s="560"/>
+      <c r="H53" s="569"/>
+      <c r="I53" s="560"/>
+      <c r="J53" s="569"/>
       <c r="K53" s="421"/>
       <c r="W53" s="422"/>
       <c r="X53" s="422"/>
@@ -77267,14 +77282,14 @@
     <row r="56" spans="1:31" ht="56.25" customHeight="1">
       <c r="A56" s="420"/>
       <c r="B56" s="420"/>
-      <c r="C56" s="571"/>
-      <c r="D56" s="568"/>
-      <c r="E56" s="569"/>
-      <c r="F56" s="544"/>
-      <c r="G56" s="566"/>
-      <c r="H56" s="568"/>
-      <c r="I56" s="566"/>
-      <c r="J56" s="568"/>
+      <c r="C56" s="572"/>
+      <c r="D56" s="569"/>
+      <c r="E56" s="570"/>
+      <c r="F56" s="553"/>
+      <c r="G56" s="560"/>
+      <c r="H56" s="569"/>
+      <c r="I56" s="560"/>
+      <c r="J56" s="569"/>
       <c r="K56" s="421"/>
       <c r="W56" s="422"/>
       <c r="X56" s="422"/>
@@ -77346,14 +77361,14 @@
     <row r="60" spans="1:31" ht="56.25" customHeight="1">
       <c r="A60" s="420"/>
       <c r="B60" s="420"/>
-      <c r="C60" s="571"/>
-      <c r="D60" s="568"/>
-      <c r="E60" s="569"/>
-      <c r="F60" s="544"/>
-      <c r="G60" s="566"/>
-      <c r="H60" s="568"/>
-      <c r="I60" s="566"/>
-      <c r="J60" s="568"/>
+      <c r="C60" s="572"/>
+      <c r="D60" s="569"/>
+      <c r="E60" s="570"/>
+      <c r="F60" s="553"/>
+      <c r="G60" s="560"/>
+      <c r="H60" s="569"/>
+      <c r="I60" s="560"/>
+      <c r="J60" s="569"/>
       <c r="K60" s="421"/>
       <c r="W60" s="422"/>
       <c r="X60" s="422"/>
@@ -77456,14 +77471,14 @@
     <row r="65" spans="1:31" ht="56.25" customHeight="1">
       <c r="A65" s="420"/>
       <c r="B65" s="420"/>
-      <c r="C65" s="571"/>
-      <c r="D65" s="568"/>
-      <c r="E65" s="569"/>
-      <c r="F65" s="544"/>
-      <c r="G65" s="566"/>
-      <c r="H65" s="568"/>
-      <c r="I65" s="566"/>
-      <c r="J65" s="568"/>
+      <c r="C65" s="572"/>
+      <c r="D65" s="569"/>
+      <c r="E65" s="570"/>
+      <c r="F65" s="553"/>
+      <c r="G65" s="560"/>
+      <c r="H65" s="569"/>
+      <c r="I65" s="560"/>
+      <c r="J65" s="569"/>
       <c r="K65" s="421"/>
       <c r="W65" s="422"/>
       <c r="X65" s="422"/>
@@ -77539,14 +77554,14 @@
     <row r="70" spans="1:31" ht="56.25" customHeight="1">
       <c r="A70" s="420"/>
       <c r="B70" s="420"/>
-      <c r="C70" s="571"/>
-      <c r="D70" s="568"/>
-      <c r="E70" s="569"/>
-      <c r="F70" s="544"/>
-      <c r="G70" s="566"/>
-      <c r="H70" s="568"/>
-      <c r="I70" s="566"/>
-      <c r="J70" s="568"/>
+      <c r="C70" s="572"/>
+      <c r="D70" s="569"/>
+      <c r="E70" s="570"/>
+      <c r="F70" s="553"/>
+      <c r="G70" s="560"/>
+      <c r="H70" s="569"/>
+      <c r="I70" s="560"/>
+      <c r="J70" s="569"/>
       <c r="K70" s="421"/>
       <c r="W70" s="422"/>
       <c r="X70" s="422"/>
@@ -77613,14 +77628,14 @@
     <row r="75" spans="1:31" ht="56.25" customHeight="1">
       <c r="A75" s="420"/>
       <c r="B75" s="420"/>
-      <c r="C75" s="571"/>
-      <c r="D75" s="568"/>
-      <c r="E75" s="569"/>
-      <c r="F75" s="544"/>
-      <c r="G75" s="566"/>
-      <c r="H75" s="568"/>
-      <c r="I75" s="566"/>
-      <c r="J75" s="568"/>
+      <c r="C75" s="572"/>
+      <c r="D75" s="569"/>
+      <c r="E75" s="570"/>
+      <c r="F75" s="553"/>
+      <c r="G75" s="560"/>
+      <c r="H75" s="569"/>
+      <c r="I75" s="560"/>
+      <c r="J75" s="569"/>
       <c r="K75" s="421"/>
       <c r="W75" s="422"/>
       <c r="X75" s="422"/>
@@ -77635,14 +77650,14 @@
     <row r="76" spans="1:31" ht="56.25" customHeight="1">
       <c r="A76" s="420"/>
       <c r="B76" s="420"/>
-      <c r="C76" s="571"/>
-      <c r="D76" s="568"/>
-      <c r="E76" s="569"/>
-      <c r="F76" s="544"/>
-      <c r="G76" s="566"/>
-      <c r="H76" s="568"/>
-      <c r="I76" s="566"/>
-      <c r="J76" s="568"/>
+      <c r="C76" s="572"/>
+      <c r="D76" s="569"/>
+      <c r="E76" s="570"/>
+      <c r="F76" s="553"/>
+      <c r="G76" s="560"/>
+      <c r="H76" s="569"/>
+      <c r="I76" s="560"/>
+      <c r="J76" s="569"/>
       <c r="K76" s="421"/>
       <c r="W76" s="422"/>
       <c r="X76" s="422"/>
@@ -77718,14 +77733,14 @@
     <row r="81" spans="1:31" ht="56.25" customHeight="1">
       <c r="A81" s="420"/>
       <c r="B81" s="420"/>
-      <c r="C81" s="571"/>
-      <c r="D81" s="568"/>
-      <c r="E81" s="569"/>
-      <c r="F81" s="544"/>
-      <c r="G81" s="566"/>
-      <c r="H81" s="568"/>
-      <c r="I81" s="566"/>
-      <c r="J81" s="568"/>
+      <c r="C81" s="572"/>
+      <c r="D81" s="569"/>
+      <c r="E81" s="570"/>
+      <c r="F81" s="553"/>
+      <c r="G81" s="560"/>
+      <c r="H81" s="569"/>
+      <c r="I81" s="560"/>
+      <c r="J81" s="569"/>
       <c r="K81" s="421"/>
       <c r="W81" s="422"/>
       <c r="X81" s="422"/>
@@ -77775,14 +77790,14 @@
     <row r="84" spans="1:31" ht="56.25" customHeight="1">
       <c r="A84" s="420"/>
       <c r="B84" s="420"/>
-      <c r="C84" s="571"/>
-      <c r="D84" s="568"/>
-      <c r="E84" s="569"/>
-      <c r="F84" s="544"/>
-      <c r="G84" s="566"/>
-      <c r="H84" s="568"/>
-      <c r="I84" s="566"/>
-      <c r="J84" s="568"/>
+      <c r="C84" s="572"/>
+      <c r="D84" s="569"/>
+      <c r="E84" s="570"/>
+      <c r="F84" s="553"/>
+      <c r="G84" s="560"/>
+      <c r="H84" s="569"/>
+      <c r="I84" s="560"/>
+      <c r="J84" s="569"/>
       <c r="K84" s="421"/>
       <c r="W84" s="422"/>
       <c r="X84" s="422"/>
@@ -77849,14 +77864,14 @@
     <row r="89" spans="1:31" ht="56.25" customHeight="1">
       <c r="A89" s="420"/>
       <c r="B89" s="420"/>
-      <c r="C89" s="571"/>
-      <c r="D89" s="568"/>
-      <c r="E89" s="569"/>
-      <c r="F89" s="544"/>
-      <c r="G89" s="566"/>
-      <c r="H89" s="568"/>
-      <c r="I89" s="566"/>
-      <c r="J89" s="568"/>
+      <c r="C89" s="572"/>
+      <c r="D89" s="569"/>
+      <c r="E89" s="570"/>
+      <c r="F89" s="553"/>
+      <c r="G89" s="560"/>
+      <c r="H89" s="569"/>
+      <c r="I89" s="560"/>
+      <c r="J89" s="569"/>
       <c r="K89" s="421"/>
       <c r="W89" s="422"/>
       <c r="X89" s="422"/>
@@ -77923,14 +77938,14 @@
     <row r="94" spans="1:31" ht="56.25" customHeight="1">
       <c r="A94" s="420"/>
       <c r="B94" s="420"/>
-      <c r="C94" s="571"/>
-      <c r="D94" s="568"/>
-      <c r="E94" s="569"/>
-      <c r="F94" s="544"/>
-      <c r="G94" s="566"/>
-      <c r="H94" s="568"/>
-      <c r="I94" s="566"/>
-      <c r="J94" s="568"/>
+      <c r="C94" s="572"/>
+      <c r="D94" s="569"/>
+      <c r="E94" s="570"/>
+      <c r="F94" s="553"/>
+      <c r="G94" s="560"/>
+      <c r="H94" s="569"/>
+      <c r="I94" s="560"/>
+      <c r="J94" s="569"/>
       <c r="K94" s="421"/>
       <c r="W94" s="422"/>
       <c r="X94" s="422"/>
@@ -77997,14 +78012,14 @@
     <row r="99" spans="1:31" ht="56.25" customHeight="1">
       <c r="A99" s="420"/>
       <c r="B99" s="420"/>
-      <c r="C99" s="571"/>
-      <c r="D99" s="568"/>
-      <c r="E99" s="569"/>
-      <c r="F99" s="544"/>
-      <c r="G99" s="566"/>
-      <c r="H99" s="568"/>
-      <c r="I99" s="566"/>
-      <c r="J99" s="568"/>
+      <c r="C99" s="572"/>
+      <c r="D99" s="569"/>
+      <c r="E99" s="570"/>
+      <c r="F99" s="553"/>
+      <c r="G99" s="560"/>
+      <c r="H99" s="569"/>
+      <c r="I99" s="560"/>
+      <c r="J99" s="569"/>
       <c r="K99" s="421"/>
       <c r="W99" s="422"/>
       <c r="X99" s="422"/>
@@ -78058,14 +78073,14 @@
     <row r="103" spans="1:31" ht="56.25" customHeight="1">
       <c r="A103" s="420"/>
       <c r="B103" s="420"/>
-      <c r="C103" s="571"/>
-      <c r="D103" s="568"/>
-      <c r="E103" s="569"/>
-      <c r="F103" s="544"/>
-      <c r="G103" s="566"/>
-      <c r="H103" s="568"/>
-      <c r="I103" s="566"/>
-      <c r="J103" s="568"/>
+      <c r="C103" s="572"/>
+      <c r="D103" s="569"/>
+      <c r="E103" s="570"/>
+      <c r="F103" s="553"/>
+      <c r="G103" s="560"/>
+      <c r="H103" s="569"/>
+      <c r="I103" s="560"/>
+      <c r="J103" s="569"/>
       <c r="K103" s="421"/>
       <c r="W103" s="422"/>
       <c r="X103" s="422"/>
@@ -78128,14 +78143,14 @@
     <row r="107" spans="1:31" ht="56.25" customHeight="1">
       <c r="A107" s="420"/>
       <c r="B107" s="420"/>
-      <c r="C107" s="571"/>
-      <c r="D107" s="543"/>
-      <c r="E107" s="543"/>
-      <c r="F107" s="543"/>
-      <c r="G107" s="543"/>
-      <c r="H107" s="543"/>
-      <c r="I107" s="543"/>
-      <c r="J107" s="543"/>
+      <c r="C107" s="572"/>
+      <c r="D107" s="552"/>
+      <c r="E107" s="552"/>
+      <c r="F107" s="552"/>
+      <c r="G107" s="552"/>
+      <c r="H107" s="552"/>
+      <c r="I107" s="552"/>
+      <c r="J107" s="552"/>
       <c r="K107" s="421"/>
       <c r="L107" s="420"/>
       <c r="M107" s="420"/>
@@ -78200,14 +78215,14 @@
     <row r="111" spans="1:31" ht="56.25" customHeight="1">
       <c r="A111" s="420"/>
       <c r="B111" s="420"/>
-      <c r="C111" s="571"/>
-      <c r="D111" s="543"/>
-      <c r="E111" s="543"/>
-      <c r="F111" s="543"/>
-      <c r="G111" s="543"/>
-      <c r="H111" s="543"/>
-      <c r="I111" s="543"/>
-      <c r="J111" s="543"/>
+      <c r="C111" s="572"/>
+      <c r="D111" s="552"/>
+      <c r="E111" s="552"/>
+      <c r="F111" s="552"/>
+      <c r="G111" s="552"/>
+      <c r="H111" s="552"/>
+      <c r="I111" s="552"/>
+      <c r="J111" s="552"/>
       <c r="K111" s="421"/>
       <c r="L111" s="420"/>
       <c r="M111" s="420"/>
@@ -78299,14 +78314,14 @@
     <row r="114" spans="1:31" ht="56.25" customHeight="1">
       <c r="A114" s="420"/>
       <c r="B114" s="420"/>
-      <c r="C114" s="571"/>
-      <c r="D114" s="568"/>
-      <c r="E114" s="569"/>
-      <c r="F114" s="544"/>
-      <c r="G114" s="566"/>
-      <c r="H114" s="568"/>
-      <c r="I114" s="566"/>
-      <c r="J114" s="568"/>
+      <c r="C114" s="572"/>
+      <c r="D114" s="569"/>
+      <c r="E114" s="570"/>
+      <c r="F114" s="553"/>
+      <c r="G114" s="560"/>
+      <c r="H114" s="569"/>
+      <c r="I114" s="560"/>
+      <c r="J114" s="569"/>
       <c r="K114" s="421"/>
       <c r="W114" s="422"/>
       <c r="X114" s="422"/>
@@ -78386,14 +78401,14 @@
     <row r="120" spans="1:31" ht="56.25" customHeight="1">
       <c r="A120" s="420"/>
       <c r="B120" s="420"/>
-      <c r="C120" s="571"/>
-      <c r="D120" s="568"/>
-      <c r="E120" s="569"/>
-      <c r="F120" s="544"/>
-      <c r="G120" s="566"/>
-      <c r="H120" s="568"/>
-      <c r="I120" s="566"/>
-      <c r="J120" s="568"/>
+      <c r="C120" s="572"/>
+      <c r="D120" s="569"/>
+      <c r="E120" s="570"/>
+      <c r="F120" s="553"/>
+      <c r="G120" s="560"/>
+      <c r="H120" s="569"/>
+      <c r="I120" s="560"/>
+      <c r="J120" s="569"/>
       <c r="K120" s="421"/>
       <c r="W120" s="422"/>
       <c r="X120" s="422"/>
@@ -78434,14 +78449,14 @@
     <row r="123" spans="1:31" ht="56.25" customHeight="1">
       <c r="A123" s="420"/>
       <c r="B123" s="420"/>
-      <c r="C123" s="571"/>
-      <c r="D123" s="568"/>
-      <c r="E123" s="569"/>
-      <c r="F123" s="544"/>
-      <c r="G123" s="566"/>
-      <c r="H123" s="568"/>
-      <c r="I123" s="566"/>
-      <c r="J123" s="568"/>
+      <c r="C123" s="572"/>
+      <c r="D123" s="569"/>
+      <c r="E123" s="570"/>
+      <c r="F123" s="553"/>
+      <c r="G123" s="560"/>
+      <c r="H123" s="569"/>
+      <c r="I123" s="560"/>
+      <c r="J123" s="569"/>
       <c r="K123" s="421"/>
       <c r="W123" s="422"/>
       <c r="X123" s="422"/>
@@ -78749,8 +78764,8 @@
       <c r="B145" s="328"/>
       <c r="C145" s="328"/>
       <c r="D145" s="562"/>
-      <c r="E145" s="543"/>
-      <c r="F145" s="543"/>
+      <c r="E145" s="552"/>
+      <c r="F145" s="552"/>
       <c r="G145" s="318"/>
       <c r="H145" s="328"/>
       <c r="I145" s="318"/>
@@ -78773,11 +78788,11 @@
     <row r="147" spans="1:31" ht="56.25" customHeight="1">
       <c r="A147" s="420"/>
       <c r="B147" s="420"/>
-      <c r="C147" s="571"/>
-      <c r="D147" s="543"/>
-      <c r="E147" s="543"/>
-      <c r="F147" s="543"/>
-      <c r="G147" s="543"/>
+      <c r="C147" s="572"/>
+      <c r="D147" s="552"/>
+      <c r="E147" s="552"/>
+      <c r="F147" s="552"/>
+      <c r="G147" s="552"/>
       <c r="H147" s="424"/>
       <c r="I147" s="430"/>
       <c r="J147" s="424"/>
@@ -78830,11 +78845,11 @@
     <row r="150" spans="1:31" ht="56.25" customHeight="1">
       <c r="A150" s="420"/>
       <c r="B150" s="420"/>
-      <c r="C150" s="571"/>
-      <c r="D150" s="543"/>
-      <c r="E150" s="543"/>
-      <c r="F150" s="543"/>
-      <c r="G150" s="543"/>
+      <c r="C150" s="572"/>
+      <c r="D150" s="552"/>
+      <c r="E150" s="552"/>
+      <c r="F150" s="552"/>
+      <c r="G150" s="552"/>
       <c r="H150" s="424"/>
       <c r="I150" s="430"/>
       <c r="J150" s="424"/>
@@ -78940,11 +78955,11 @@
     <row r="155" spans="1:31" ht="56.25" customHeight="1">
       <c r="A155" s="420"/>
       <c r="B155" s="420"/>
-      <c r="C155" s="571"/>
-      <c r="D155" s="543"/>
-      <c r="E155" s="543"/>
-      <c r="F155" s="543"/>
-      <c r="G155" s="543"/>
+      <c r="C155" s="572"/>
+      <c r="D155" s="552"/>
+      <c r="E155" s="552"/>
+      <c r="F155" s="552"/>
+      <c r="G155" s="552"/>
       <c r="H155" s="424"/>
       <c r="I155" s="430"/>
       <c r="J155" s="424"/>
@@ -79076,11 +79091,11 @@
     <row r="161" spans="1:31" ht="56.25" customHeight="1">
       <c r="A161" s="420"/>
       <c r="B161" s="420"/>
-      <c r="C161" s="571"/>
-      <c r="D161" s="543"/>
-      <c r="E161" s="543"/>
-      <c r="F161" s="543"/>
-      <c r="G161" s="543"/>
+      <c r="C161" s="572"/>
+      <c r="D161" s="552"/>
+      <c r="E161" s="552"/>
+      <c r="F161" s="552"/>
+      <c r="G161" s="552"/>
       <c r="H161" s="424"/>
       <c r="I161" s="430"/>
       <c r="J161" s="424"/>
@@ -79223,11 +79238,11 @@
     <row r="167" spans="1:31" ht="56.25" customHeight="1">
       <c r="A167" s="420"/>
       <c r="B167" s="420"/>
-      <c r="C167" s="571"/>
-      <c r="D167" s="543"/>
-      <c r="E167" s="543"/>
-      <c r="F167" s="543"/>
-      <c r="G167" s="543"/>
+      <c r="C167" s="572"/>
+      <c r="D167" s="552"/>
+      <c r="E167" s="552"/>
+      <c r="F167" s="552"/>
+      <c r="G167" s="552"/>
       <c r="H167" s="424"/>
       <c r="I167" s="430"/>
       <c r="J167" s="424"/>
@@ -79344,11 +79359,11 @@
     <row r="171" spans="1:31" ht="56.25" customHeight="1">
       <c r="A171" s="421"/>
       <c r="B171" s="420"/>
-      <c r="C171" s="571"/>
-      <c r="D171" s="543"/>
-      <c r="E171" s="543"/>
-      <c r="F171" s="543"/>
-      <c r="G171" s="543"/>
+      <c r="C171" s="572"/>
+      <c r="D171" s="552"/>
+      <c r="E171" s="552"/>
+      <c r="F171" s="552"/>
+      <c r="G171" s="552"/>
       <c r="H171" s="424"/>
       <c r="I171" s="430"/>
       <c r="J171" s="424"/>
@@ -79468,8 +79483,8 @@
       <c r="C175" s="328"/>
       <c r="D175" s="431"/>
       <c r="E175" s="562"/>
-      <c r="F175" s="543"/>
-      <c r="G175" s="543"/>
+      <c r="F175" s="552"/>
+      <c r="G175" s="552"/>
       <c r="H175" s="328"/>
       <c r="I175" s="425"/>
       <c r="J175" s="328"/>
@@ -79477,14 +79492,14 @@
     </row>
     <row r="176" spans="1:31" ht="45" customHeight="1">
       <c r="A176" s="328"/>
-      <c r="B176" s="572"/>
-      <c r="C176" s="573"/>
-      <c r="D176" s="573"/>
-      <c r="E176" s="573"/>
-      <c r="F176" s="573"/>
-      <c r="G176" s="573"/>
-      <c r="H176" s="573"/>
-      <c r="I176" s="573"/>
+      <c r="B176" s="573"/>
+      <c r="C176" s="574"/>
+      <c r="D176" s="574"/>
+      <c r="E176" s="574"/>
+      <c r="F176" s="574"/>
+      <c r="G176" s="574"/>
+      <c r="H176" s="574"/>
+      <c r="I176" s="574"/>
       <c r="J176" s="328"/>
       <c r="K176" s="318"/>
       <c r="L176" s="328"/>
@@ -79764,23 +79779,20 @@
     <row r="249" ht="56.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="C53:J53"/>
+    <mergeCell ref="C49:J49"/>
+    <mergeCell ref="C56:J56"/>
+    <mergeCell ref="C60:J60"/>
+    <mergeCell ref="C65:J65"/>
+    <mergeCell ref="C94:J94"/>
+    <mergeCell ref="C99:J99"/>
+    <mergeCell ref="C114:J114"/>
+    <mergeCell ref="C120:J120"/>
+    <mergeCell ref="C70:J70"/>
+    <mergeCell ref="C75:J75"/>
+    <mergeCell ref="C76:J76"/>
+    <mergeCell ref="C81:J81"/>
+    <mergeCell ref="C84:J84"/>
     <mergeCell ref="C171:G171"/>
     <mergeCell ref="E175:G175"/>
     <mergeCell ref="B176:I176"/>
@@ -79797,20 +79809,23 @@
     <mergeCell ref="C147:G147"/>
     <mergeCell ref="C107:J107"/>
     <mergeCell ref="C89:J89"/>
-    <mergeCell ref="C94:J94"/>
-    <mergeCell ref="C99:J99"/>
-    <mergeCell ref="C114:J114"/>
-    <mergeCell ref="C120:J120"/>
-    <mergeCell ref="C70:J70"/>
-    <mergeCell ref="C75:J75"/>
-    <mergeCell ref="C76:J76"/>
-    <mergeCell ref="C81:J81"/>
-    <mergeCell ref="C84:J84"/>
-    <mergeCell ref="C53:J53"/>
-    <mergeCell ref="C49:J49"/>
-    <mergeCell ref="C56:J56"/>
-    <mergeCell ref="C60:J60"/>
-    <mergeCell ref="C65:J65"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D18:E18"/>
   </mergeCells>
   <phoneticPr fontId="73" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
